--- a/要件定義書（カレンダーアプリ）.xlsx
+++ b/要件定義書（カレンダーアプリ）.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\my_application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3959D2F8-94F0-4A17-A630-A42657187864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5CAA7D6-B3A2-4FCC-B7C3-F6BA00242A93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="3" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="189">
   <si>
     <t>要件定義</t>
   </si>
@@ -312,23 +312,6 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>優先度・期限・完了日の登録</t>
-    <rPh sb="11" eb="13">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>自身のTOPページへ表示</t>
-    <rPh sb="0" eb="2">
-      <t>ジシン</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
     <t>タスクのリマインド機能</t>
     <rPh sb="9" eb="11">
       <t>キノウ</t>
@@ -336,230 +319,6 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <r>
-      <t>w</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>タスクは個々の管理</t>
-    </r>
-    <rPh sb="6" eb="8">
-      <t>ココ</t>
-    </rPh>
-    <rPh sb="9" eb="11">
-      <t>カンリ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <r>
-      <t>w</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>上長の把握は個々への確認となる</t>
-    </r>
-    <rPh sb="2" eb="4">
-      <t>ジョウチョウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ハアク</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ココ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>カクニン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>上長（管理者権限）からの登録・閲覧可</t>
-    <rPh sb="0" eb="2">
-      <t>ジョウチョウ</t>
-    </rPh>
-    <rPh sb="3" eb="6">
-      <t>カンリシャ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ケンゲン</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="15" eb="18">
-      <t>エツランカ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <r>
-      <t>w</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>業務遅延や漏れがある</t>
-    </r>
-    <rPh sb="1" eb="5">
-      <t>ギョウムチエン</t>
-    </rPh>
-    <rPh sb="6" eb="7">
-      <t>モ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <r>
-      <t>w</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>タスクを個々での管理＋上長での管理</t>
-    </r>
-    <rPh sb="6" eb="8">
-      <t>ココ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>カンリ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ジョウチョウ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>カンリ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <r>
-      <t>w</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Yu Gothic"/>
-        <charset val="128"/>
-      </rPr>
-      <t>優先順位・期限等を見える化することで業務の遅延を防止（これらは上長からの変更も可）</t>
-    </r>
-    <rPh sb="1" eb="3">
-      <t>ユウセン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ジュンイ</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="8" eb="9">
-      <t>トウ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ミ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>ギョウム</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>チエン</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>ボウシ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>ジョウチョウ</t>
-    </rPh>
-    <rPh sb="37" eb="39">
-      <t>ヘンコウ</t>
-    </rPh>
-    <rPh sb="40" eb="41">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <r>
-      <t>w</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>業務完了が早くなるかつ漏れをなくす</t>
-    </r>
-    <rPh sb="2" eb="4">
-      <t>ギョウム</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ハヤ</t>
-    </rPh>
-    <rPh sb="13" eb="14">
-      <t>モ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
     <t>一般</t>
     <rPh sb="0" eb="2">
       <t>イッパン</t>
@@ -570,44 +329,6 @@
     <t>役割・権限</t>
     <rPh sb="3" eb="5">
       <t>ケンゲン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>タスク登録・更新</t>
-    <rPh sb="3" eb="5">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>コウシン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>社員登録、タスク登録・更新（一般社員分も可）、社員のタスク閲覧</t>
-    <rPh sb="0" eb="4">
-      <t>シャイントウロク</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="14" eb="18">
-      <t>イッパンシャイン</t>
-    </rPh>
-    <rPh sb="18" eb="19">
-      <t>ブン</t>
-    </rPh>
-    <rPh sb="20" eb="21">
-      <t>カ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>エツラン</t>
     </rPh>
     <phoneticPr fontId="13"/>
   </si>
@@ -1635,6 +1356,295 @@
   </si>
   <si>
     <t>また、時には立て込んでいる時間帯等は外して接点をつくることで、お互いに業務の円滑化を図る。</t>
+  </si>
+  <si>
+    <t>タスク・スケジュール登録</t>
+    <rPh sb="10" eb="12">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>カレンダー表示</t>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>カレンダー表示閲覧</t>
+    <rPh sb="5" eb="7">
+      <t>ヒョウジ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>エツラン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <r>
+      <t>w</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>タスク・スケジュールは個々での管理</t>
+    </r>
+    <rPh sb="13" eb="15">
+      <t>ココ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カンリ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <r>
+      <t>w</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
+      <t>周りとのスケジュールの相互確認がしづらい</t>
+    </r>
+    <rPh sb="1" eb="2">
+      <t>マワ</t>
+    </rPh>
+    <rPh sb="12" eb="16">
+      <t>ソウゴカクニン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <r>
+      <t>w</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
+      <t>互いの</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>業務の兼ね合いにより接点・コミュニケーションの減少</t>
+    </r>
+    <rPh sb="1" eb="2">
+      <t>タガ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ギョウム</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>セッテン</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>ゲンショウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <r>
+      <t>w</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>タスク・スケジュールをカレンダーアプリとして管理し、相互確認ができる</t>
+    </r>
+    <rPh sb="24" eb="26">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>ソウゴ</t>
+    </rPh>
+    <rPh sb="30" eb="32">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <r>
+      <t>w</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <charset val="128"/>
+      </rPr>
+      <t>相互確認できることで自身のタスク管理の見直しにもつながる</t>
+    </r>
+    <rPh sb="1" eb="5">
+      <t>ソウゴカクニン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ジシン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カンリ</t>
+    </rPh>
+    <rPh sb="20" eb="22">
+      <t>ミナオ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <r>
+      <t>w</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>互いのスケジュールを確認して電話・メールなど用途・緊急性に応じて接点を作ることができる</t>
+    </r>
+    <rPh sb="2" eb="3">
+      <t>タガ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>デンワ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ヨウト</t>
+    </rPh>
+    <rPh sb="27" eb="30">
+      <t>キンキュウセイ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>オウ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>セッテン</t>
+    </rPh>
+    <rPh sb="37" eb="38">
+      <t>ツク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <r>
+      <t>w</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>時間が合わなかった・都合が悪いタイミングだった等の理由での行き違いが発生しにくくなる</t>
+    </r>
+    <rPh sb="2" eb="4">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>ア</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ツゴウ</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>ワル</t>
+    </rPh>
+    <rPh sb="25" eb="26">
+      <t>トウ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>リユウ</t>
+    </rPh>
+    <rPh sb="31" eb="32">
+      <t>イ</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>チガ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>ハッセイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>社員登録</t>
+    <rPh sb="0" eb="4">
+      <t>シャイントウロク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>スケジュール登録・更新、カレンダー閲覧</t>
+    <rPh sb="6" eb="8">
+      <t>トウロク</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>コウシン</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>エツラン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
   </si>
 </sst>
 </file>
@@ -2385,53 +2395,128 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="56" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="56" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2471,57 +2556,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="56" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2530,30 +2564,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3017,44 +3027,44 @@
       <c r="P5" s="8"/>
     </row>
     <row r="6" spans="1:16" ht="39" customHeight="1">
-      <c r="A6" s="85"/>
-      <c r="B6" s="86"/>
-      <c r="C6" s="87"/>
-      <c r="D6" s="88" t="s">
-        <v>181</v>
-      </c>
-      <c r="E6" s="88"/>
-      <c r="F6" s="88"/>
-      <c r="G6" s="88"/>
-      <c r="H6" s="88"/>
-      <c r="I6" s="88"/>
-      <c r="J6" s="88"/>
-      <c r="K6" s="88"/>
-      <c r="L6" s="88"/>
-      <c r="M6" s="88"/>
-      <c r="N6" s="86"/>
-      <c r="O6" s="87"/>
-      <c r="P6" s="85"/>
+      <c r="A6" s="104"/>
+      <c r="B6" s="105"/>
+      <c r="C6" s="103"/>
+      <c r="D6" s="106" t="s">
+        <v>170</v>
+      </c>
+      <c r="E6" s="106"/>
+      <c r="F6" s="106"/>
+      <c r="G6" s="106"/>
+      <c r="H6" s="106"/>
+      <c r="I6" s="106"/>
+      <c r="J6" s="106"/>
+      <c r="K6" s="106"/>
+      <c r="L6" s="106"/>
+      <c r="M6" s="106"/>
+      <c r="N6" s="105"/>
+      <c r="O6" s="103"/>
+      <c r="P6" s="104"/>
     </row>
     <row r="7" spans="1:16" ht="39" customHeight="1">
-      <c r="A7" s="85"/>
-      <c r="B7" s="86"/>
-      <c r="C7" s="87"/>
-      <c r="D7" s="88" t="s">
+      <c r="A7" s="104"/>
+      <c r="B7" s="105"/>
+      <c r="C7" s="103"/>
+      <c r="D7" s="106" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="88"/>
-      <c r="F7" s="88"/>
-      <c r="G7" s="88"/>
-      <c r="H7" s="88"/>
-      <c r="I7" s="88"/>
-      <c r="J7" s="88"/>
-      <c r="K7" s="88"/>
-      <c r="L7" s="88"/>
-      <c r="M7" s="88"/>
-      <c r="N7" s="86"/>
-      <c r="O7" s="87"/>
-      <c r="P7" s="85"/>
+      <c r="E7" s="106"/>
+      <c r="F7" s="106"/>
+      <c r="G7" s="106"/>
+      <c r="H7" s="106"/>
+      <c r="I7" s="106"/>
+      <c r="J7" s="106"/>
+      <c r="K7" s="106"/>
+      <c r="L7" s="106"/>
+      <c r="M7" s="106"/>
+      <c r="N7" s="105"/>
+      <c r="O7" s="103"/>
+      <c r="P7" s="104"/>
     </row>
     <row r="8" spans="1:16" ht="18.5" thickBot="1">
       <c r="A8" s="8"/>
@@ -3116,16 +3126,16 @@
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
-      <c r="F11" s="89" t="s">
+      <c r="F11" s="97" t="s">
         <v>2</v>
       </c>
-      <c r="G11" s="90"/>
-      <c r="H11" s="91" t="s">
+      <c r="G11" s="98"/>
+      <c r="H11" s="101" t="s">
         <v>58</v>
       </c>
-      <c r="I11" s="92"/>
-      <c r="J11" s="92"/>
-      <c r="K11" s="92"/>
+      <c r="I11" s="102"/>
+      <c r="J11" s="102"/>
+      <c r="K11" s="102"/>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
@@ -3138,14 +3148,14 @@
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
-      <c r="F12" s="89" t="s">
+      <c r="F12" s="97" t="s">
         <v>3</v>
       </c>
-      <c r="G12" s="90"/>
-      <c r="H12" s="93"/>
-      <c r="I12" s="94"/>
-      <c r="J12" s="94"/>
-      <c r="K12" s="94"/>
+      <c r="G12" s="98"/>
+      <c r="H12" s="99"/>
+      <c r="I12" s="100"/>
+      <c r="J12" s="100"/>
+      <c r="K12" s="100"/>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
@@ -3158,14 +3168,14 @@
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
-      <c r="F13" s="89" t="s">
+      <c r="F13" s="97" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="90"/>
-      <c r="H13" s="93"/>
-      <c r="I13" s="94"/>
-      <c r="J13" s="94"/>
-      <c r="K13" s="94"/>
+      <c r="G13" s="98"/>
+      <c r="H13" s="99"/>
+      <c r="I13" s="100"/>
+      <c r="J13" s="100"/>
+      <c r="K13" s="100"/>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
@@ -3178,14 +3188,14 @@
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
-      <c r="F14" s="89" t="s">
+      <c r="F14" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="90"/>
-      <c r="H14" s="91"/>
-      <c r="I14" s="92"/>
-      <c r="J14" s="92"/>
-      <c r="K14" s="92"/>
+      <c r="G14" s="98"/>
+      <c r="H14" s="101"/>
+      <c r="I14" s="102"/>
+      <c r="J14" s="102"/>
+      <c r="K14" s="102"/>
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
@@ -3322,22 +3332,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H13:K13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H14:K14"/>
-    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:M6"/>
+    <mergeCell ref="D7:M7"/>
     <mergeCell ref="P6:P7"/>
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="H11:K11"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="H12:K12"/>
     <mergeCell ref="N6:N7"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:M6"/>
-    <mergeCell ref="D7:M7"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="H13:K13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H14:K14"/>
+    <mergeCell ref="O6:O7"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3350,54 +3360,54 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="87" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="96"/>
-      <c r="C1" s="97"/>
-      <c r="D1" s="101" t="s">
+      <c r="B1" s="124"/>
+      <c r="C1" s="88"/>
+      <c r="D1" s="126" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="102"/>
-      <c r="F1" s="102"/>
-      <c r="G1" s="102"/>
-      <c r="H1" s="102"/>
-      <c r="I1" s="102"/>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="103"/>
+      <c r="E1" s="127"/>
+      <c r="F1" s="127"/>
+      <c r="G1" s="127"/>
+      <c r="H1" s="127"/>
+      <c r="I1" s="127"/>
+      <c r="J1" s="127"/>
+      <c r="K1" s="127"/>
+      <c r="L1" s="127"/>
+      <c r="M1" s="127"/>
+      <c r="N1" s="127"/>
+      <c r="O1" s="128"/>
       <c r="P1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="107" t="s">
-        <v>142</v>
-      </c>
-      <c r="R1" s="108"/>
+      <c r="Q1" s="132" t="s">
+        <v>131</v>
+      </c>
+      <c r="R1" s="133"/>
     </row>
     <row r="2" spans="1:18">
-      <c r="A2" s="98"/>
-      <c r="B2" s="99"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="104"/>
-      <c r="E2" s="105"/>
-      <c r="F2" s="105"/>
-      <c r="G2" s="105"/>
-      <c r="H2" s="105"/>
-      <c r="I2" s="105"/>
-      <c r="J2" s="105"/>
-      <c r="K2" s="105"/>
-      <c r="L2" s="105"/>
-      <c r="M2" s="105"/>
-      <c r="N2" s="105"/>
-      <c r="O2" s="106"/>
+      <c r="A2" s="89"/>
+      <c r="B2" s="125"/>
+      <c r="C2" s="90"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="130"/>
+      <c r="F2" s="130"/>
+      <c r="G2" s="130"/>
+      <c r="H2" s="130"/>
+      <c r="I2" s="130"/>
+      <c r="J2" s="130"/>
+      <c r="K2" s="130"/>
+      <c r="L2" s="130"/>
+      <c r="M2" s="130"/>
+      <c r="N2" s="130"/>
+      <c r="O2" s="131"/>
       <c r="P2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="Q2" s="109"/>
-      <c r="R2" s="110"/>
+      <c r="Q2" s="134"/>
+      <c r="R2" s="135"/>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="2"/>
@@ -3423,427 +3433,427 @@
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="111" t="s">
+      <c r="B4" s="136" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="112"/>
-      <c r="D4" s="111" t="s">
+      <c r="C4" s="137"/>
+      <c r="D4" s="136" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="112"/>
-      <c r="F4" s="111" t="s">
+      <c r="E4" s="137"/>
+      <c r="F4" s="136" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="113"/>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113"/>
-      <c r="J4" s="112"/>
-      <c r="K4" s="111" t="s">
+      <c r="G4" s="138"/>
+      <c r="H4" s="138"/>
+      <c r="I4" s="138"/>
+      <c r="J4" s="137"/>
+      <c r="K4" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="113"/>
-      <c r="M4" s="113"/>
-      <c r="N4" s="113"/>
-      <c r="O4" s="113"/>
-      <c r="P4" s="113"/>
-      <c r="Q4" s="113"/>
-      <c r="R4" s="112"/>
+      <c r="L4" s="138"/>
+      <c r="M4" s="138"/>
+      <c r="N4" s="138"/>
+      <c r="O4" s="138"/>
+      <c r="P4" s="138"/>
+      <c r="Q4" s="138"/>
+      <c r="R4" s="137"/>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="4">
         <v>1</v>
       </c>
-      <c r="B5" s="114"/>
-      <c r="C5" s="115"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="115"/>
-      <c r="F5" s="117"/>
-      <c r="G5" s="118"/>
-      <c r="H5" s="118"/>
-      <c r="I5" s="118"/>
-      <c r="J5" s="119"/>
-      <c r="K5" s="117"/>
-      <c r="L5" s="118"/>
-      <c r="M5" s="118"/>
-      <c r="N5" s="118"/>
-      <c r="O5" s="118"/>
-      <c r="P5" s="118"/>
-      <c r="Q5" s="118"/>
-      <c r="R5" s="119"/>
+      <c r="B5" s="117"/>
+      <c r="C5" s="118"/>
+      <c r="D5" s="119"/>
+      <c r="E5" s="118"/>
+      <c r="F5" s="120"/>
+      <c r="G5" s="121"/>
+      <c r="H5" s="121"/>
+      <c r="I5" s="121"/>
+      <c r="J5" s="122"/>
+      <c r="K5" s="120"/>
+      <c r="L5" s="121"/>
+      <c r="M5" s="121"/>
+      <c r="N5" s="121"/>
+      <c r="O5" s="121"/>
+      <c r="P5" s="121"/>
+      <c r="Q5" s="121"/>
+      <c r="R5" s="122"/>
     </row>
     <row r="6" spans="1:18" ht="54" customHeight="1">
       <c r="A6" s="6">
         <v>2</v>
       </c>
-      <c r="B6" s="120"/>
-      <c r="C6" s="121"/>
-      <c r="D6" s="122"/>
-      <c r="E6" s="121"/>
+      <c r="B6" s="113"/>
+      <c r="C6" s="108"/>
+      <c r="D6" s="107"/>
+      <c r="E6" s="108"/>
       <c r="F6" s="123"/>
-      <c r="G6" s="124"/>
-      <c r="H6" s="124"/>
-      <c r="I6" s="124"/>
-      <c r="J6" s="125"/>
-      <c r="K6" s="126"/>
-      <c r="L6" s="124"/>
-      <c r="M6" s="124"/>
-      <c r="N6" s="124"/>
-      <c r="O6" s="124"/>
-      <c r="P6" s="124"/>
-      <c r="Q6" s="124"/>
-      <c r="R6" s="125"/>
+      <c r="G6" s="111"/>
+      <c r="H6" s="111"/>
+      <c r="I6" s="111"/>
+      <c r="J6" s="112"/>
+      <c r="K6" s="110"/>
+      <c r="L6" s="111"/>
+      <c r="M6" s="111"/>
+      <c r="N6" s="111"/>
+      <c r="O6" s="111"/>
+      <c r="P6" s="111"/>
+      <c r="Q6" s="111"/>
+      <c r="R6" s="112"/>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="6">
         <v>3</v>
       </c>
-      <c r="B7" s="120"/>
-      <c r="C7" s="121"/>
-      <c r="D7" s="122"/>
-      <c r="E7" s="121"/>
-      <c r="F7" s="126"/>
-      <c r="G7" s="124"/>
-      <c r="H7" s="124"/>
-      <c r="I7" s="124"/>
-      <c r="J7" s="125"/>
-      <c r="K7" s="126"/>
-      <c r="L7" s="124"/>
-      <c r="M7" s="124"/>
-      <c r="N7" s="124"/>
-      <c r="O7" s="124"/>
-      <c r="P7" s="124"/>
-      <c r="Q7" s="124"/>
-      <c r="R7" s="125"/>
+      <c r="B7" s="113"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="107"/>
+      <c r="E7" s="108"/>
+      <c r="F7" s="110"/>
+      <c r="G7" s="111"/>
+      <c r="H7" s="111"/>
+      <c r="I7" s="111"/>
+      <c r="J7" s="112"/>
+      <c r="K7" s="110"/>
+      <c r="L7" s="111"/>
+      <c r="M7" s="111"/>
+      <c r="N7" s="111"/>
+      <c r="O7" s="111"/>
+      <c r="P7" s="111"/>
+      <c r="Q7" s="111"/>
+      <c r="R7" s="112"/>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="6">
         <v>4</v>
       </c>
-      <c r="B8" s="120"/>
-      <c r="C8" s="121"/>
-      <c r="D8" s="122"/>
-      <c r="E8" s="121"/>
-      <c r="F8" s="126"/>
-      <c r="G8" s="124"/>
-      <c r="H8" s="124"/>
-      <c r="I8" s="124"/>
-      <c r="J8" s="125"/>
-      <c r="K8" s="126"/>
-      <c r="L8" s="124"/>
-      <c r="M8" s="124"/>
-      <c r="N8" s="124"/>
-      <c r="O8" s="124"/>
-      <c r="P8" s="124"/>
-      <c r="Q8" s="124"/>
-      <c r="R8" s="125"/>
+      <c r="B8" s="113"/>
+      <c r="C8" s="108"/>
+      <c r="D8" s="107"/>
+      <c r="E8" s="108"/>
+      <c r="F8" s="110"/>
+      <c r="G8" s="111"/>
+      <c r="H8" s="111"/>
+      <c r="I8" s="111"/>
+      <c r="J8" s="112"/>
+      <c r="K8" s="110"/>
+      <c r="L8" s="111"/>
+      <c r="M8" s="111"/>
+      <c r="N8" s="111"/>
+      <c r="O8" s="111"/>
+      <c r="P8" s="111"/>
+      <c r="Q8" s="111"/>
+      <c r="R8" s="112"/>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="6">
         <v>5</v>
       </c>
-      <c r="B9" s="120"/>
-      <c r="C9" s="121"/>
-      <c r="D9" s="122"/>
-      <c r="E9" s="121"/>
-      <c r="F9" s="127"/>
-      <c r="G9" s="128"/>
-      <c r="H9" s="128"/>
-      <c r="I9" s="128"/>
-      <c r="J9" s="129"/>
-      <c r="K9" s="126"/>
-      <c r="L9" s="124"/>
-      <c r="M9" s="124"/>
-      <c r="N9" s="124"/>
-      <c r="O9" s="124"/>
-      <c r="P9" s="124"/>
-      <c r="Q9" s="124"/>
-      <c r="R9" s="125"/>
+      <c r="B9" s="113"/>
+      <c r="C9" s="108"/>
+      <c r="D9" s="107"/>
+      <c r="E9" s="108"/>
+      <c r="F9" s="114"/>
+      <c r="G9" s="115"/>
+      <c r="H9" s="115"/>
+      <c r="I9" s="115"/>
+      <c r="J9" s="116"/>
+      <c r="K9" s="110"/>
+      <c r="L9" s="111"/>
+      <c r="M9" s="111"/>
+      <c r="N9" s="111"/>
+      <c r="O9" s="111"/>
+      <c r="P9" s="111"/>
+      <c r="Q9" s="111"/>
+      <c r="R9" s="112"/>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="6">
         <v>6</v>
       </c>
-      <c r="B10" s="122"/>
-      <c r="C10" s="121"/>
-      <c r="D10" s="122"/>
-      <c r="E10" s="121"/>
-      <c r="F10" s="122"/>
-      <c r="G10" s="130"/>
-      <c r="H10" s="130"/>
-      <c r="I10" s="130"/>
-      <c r="J10" s="121"/>
-      <c r="K10" s="126"/>
-      <c r="L10" s="124"/>
-      <c r="M10" s="124"/>
-      <c r="N10" s="124"/>
-      <c r="O10" s="124"/>
-      <c r="P10" s="124"/>
-      <c r="Q10" s="124"/>
-      <c r="R10" s="125"/>
+      <c r="B10" s="107"/>
+      <c r="C10" s="108"/>
+      <c r="D10" s="107"/>
+      <c r="E10" s="108"/>
+      <c r="F10" s="107"/>
+      <c r="G10" s="109"/>
+      <c r="H10" s="109"/>
+      <c r="I10" s="109"/>
+      <c r="J10" s="108"/>
+      <c r="K10" s="110"/>
+      <c r="L10" s="111"/>
+      <c r="M10" s="111"/>
+      <c r="N10" s="111"/>
+      <c r="O10" s="111"/>
+      <c r="P10" s="111"/>
+      <c r="Q10" s="111"/>
+      <c r="R10" s="112"/>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="6">
         <v>7</v>
       </c>
-      <c r="B11" s="122"/>
-      <c r="C11" s="121"/>
-      <c r="D11" s="122"/>
-      <c r="E11" s="121"/>
-      <c r="F11" s="122"/>
-      <c r="G11" s="130"/>
-      <c r="H11" s="130"/>
-      <c r="I11" s="130"/>
-      <c r="J11" s="121"/>
-      <c r="K11" s="126"/>
-      <c r="L11" s="124"/>
-      <c r="M11" s="124"/>
-      <c r="N11" s="124"/>
-      <c r="O11" s="124"/>
-      <c r="P11" s="124"/>
-      <c r="Q11" s="124"/>
-      <c r="R11" s="125"/>
+      <c r="B11" s="107"/>
+      <c r="C11" s="108"/>
+      <c r="D11" s="107"/>
+      <c r="E11" s="108"/>
+      <c r="F11" s="107"/>
+      <c r="G11" s="109"/>
+      <c r="H11" s="109"/>
+      <c r="I11" s="109"/>
+      <c r="J11" s="108"/>
+      <c r="K11" s="110"/>
+      <c r="L11" s="111"/>
+      <c r="M11" s="111"/>
+      <c r="N11" s="111"/>
+      <c r="O11" s="111"/>
+      <c r="P11" s="111"/>
+      <c r="Q11" s="111"/>
+      <c r="R11" s="112"/>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="6">
         <v>8</v>
       </c>
-      <c r="B12" s="122"/>
-      <c r="C12" s="121"/>
-      <c r="D12" s="122"/>
-      <c r="E12" s="121"/>
-      <c r="F12" s="122"/>
-      <c r="G12" s="130"/>
-      <c r="H12" s="130"/>
-      <c r="I12" s="130"/>
-      <c r="J12" s="121"/>
-      <c r="K12" s="126"/>
-      <c r="L12" s="124"/>
-      <c r="M12" s="124"/>
-      <c r="N12" s="124"/>
-      <c r="O12" s="124"/>
-      <c r="P12" s="124"/>
-      <c r="Q12" s="124"/>
-      <c r="R12" s="125"/>
+      <c r="B12" s="107"/>
+      <c r="C12" s="108"/>
+      <c r="D12" s="107"/>
+      <c r="E12" s="108"/>
+      <c r="F12" s="107"/>
+      <c r="G12" s="109"/>
+      <c r="H12" s="109"/>
+      <c r="I12" s="109"/>
+      <c r="J12" s="108"/>
+      <c r="K12" s="110"/>
+      <c r="L12" s="111"/>
+      <c r="M12" s="111"/>
+      <c r="N12" s="111"/>
+      <c r="O12" s="111"/>
+      <c r="P12" s="111"/>
+      <c r="Q12" s="111"/>
+      <c r="R12" s="112"/>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="6">
         <v>9</v>
       </c>
-      <c r="B13" s="122"/>
-      <c r="C13" s="121"/>
-      <c r="D13" s="122"/>
-      <c r="E13" s="121"/>
-      <c r="F13" s="122"/>
-      <c r="G13" s="130"/>
-      <c r="H13" s="130"/>
-      <c r="I13" s="130"/>
-      <c r="J13" s="121"/>
-      <c r="K13" s="126"/>
-      <c r="L13" s="124"/>
-      <c r="M13" s="124"/>
-      <c r="N13" s="124"/>
-      <c r="O13" s="124"/>
-      <c r="P13" s="124"/>
-      <c r="Q13" s="124"/>
-      <c r="R13" s="125"/>
+      <c r="B13" s="107"/>
+      <c r="C13" s="108"/>
+      <c r="D13" s="107"/>
+      <c r="E13" s="108"/>
+      <c r="F13" s="107"/>
+      <c r="G13" s="109"/>
+      <c r="H13" s="109"/>
+      <c r="I13" s="109"/>
+      <c r="J13" s="108"/>
+      <c r="K13" s="110"/>
+      <c r="L13" s="111"/>
+      <c r="M13" s="111"/>
+      <c r="N13" s="111"/>
+      <c r="O13" s="111"/>
+      <c r="P13" s="111"/>
+      <c r="Q13" s="111"/>
+      <c r="R13" s="112"/>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="6">
         <v>10</v>
       </c>
-      <c r="B14" s="122"/>
-      <c r="C14" s="121"/>
-      <c r="D14" s="122"/>
-      <c r="E14" s="121"/>
-      <c r="F14" s="122"/>
-      <c r="G14" s="130"/>
-      <c r="H14" s="130"/>
-      <c r="I14" s="130"/>
-      <c r="J14" s="121"/>
-      <c r="K14" s="126"/>
-      <c r="L14" s="124"/>
-      <c r="M14" s="124"/>
-      <c r="N14" s="124"/>
-      <c r="O14" s="124"/>
-      <c r="P14" s="124"/>
-      <c r="Q14" s="124"/>
-      <c r="R14" s="125"/>
+      <c r="B14" s="107"/>
+      <c r="C14" s="108"/>
+      <c r="D14" s="107"/>
+      <c r="E14" s="108"/>
+      <c r="F14" s="107"/>
+      <c r="G14" s="109"/>
+      <c r="H14" s="109"/>
+      <c r="I14" s="109"/>
+      <c r="J14" s="108"/>
+      <c r="K14" s="110"/>
+      <c r="L14" s="111"/>
+      <c r="M14" s="111"/>
+      <c r="N14" s="111"/>
+      <c r="O14" s="111"/>
+      <c r="P14" s="111"/>
+      <c r="Q14" s="111"/>
+      <c r="R14" s="112"/>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="6">
         <v>11</v>
       </c>
-      <c r="B15" s="122"/>
-      <c r="C15" s="121"/>
-      <c r="D15" s="122"/>
-      <c r="E15" s="121"/>
-      <c r="F15" s="122"/>
-      <c r="G15" s="130"/>
-      <c r="H15" s="130"/>
-      <c r="I15" s="130"/>
-      <c r="J15" s="121"/>
-      <c r="K15" s="126"/>
-      <c r="L15" s="124"/>
-      <c r="M15" s="124"/>
-      <c r="N15" s="124"/>
-      <c r="O15" s="124"/>
-      <c r="P15" s="124"/>
-      <c r="Q15" s="124"/>
-      <c r="R15" s="125"/>
+      <c r="B15" s="107"/>
+      <c r="C15" s="108"/>
+      <c r="D15" s="107"/>
+      <c r="E15" s="108"/>
+      <c r="F15" s="107"/>
+      <c r="G15" s="109"/>
+      <c r="H15" s="109"/>
+      <c r="I15" s="109"/>
+      <c r="J15" s="108"/>
+      <c r="K15" s="110"/>
+      <c r="L15" s="111"/>
+      <c r="M15" s="111"/>
+      <c r="N15" s="111"/>
+      <c r="O15" s="111"/>
+      <c r="P15" s="111"/>
+      <c r="Q15" s="111"/>
+      <c r="R15" s="112"/>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="6">
         <v>12</v>
       </c>
-      <c r="B16" s="122"/>
-      <c r="C16" s="121"/>
-      <c r="D16" s="122"/>
-      <c r="E16" s="121"/>
-      <c r="F16" s="122"/>
-      <c r="G16" s="130"/>
-      <c r="H16" s="130"/>
-      <c r="I16" s="130"/>
-      <c r="J16" s="121"/>
-      <c r="K16" s="126"/>
-      <c r="L16" s="124"/>
-      <c r="M16" s="124"/>
-      <c r="N16" s="124"/>
-      <c r="O16" s="124"/>
-      <c r="P16" s="124"/>
-      <c r="Q16" s="124"/>
-      <c r="R16" s="125"/>
+      <c r="B16" s="107"/>
+      <c r="C16" s="108"/>
+      <c r="D16" s="107"/>
+      <c r="E16" s="108"/>
+      <c r="F16" s="107"/>
+      <c r="G16" s="109"/>
+      <c r="H16" s="109"/>
+      <c r="I16" s="109"/>
+      <c r="J16" s="108"/>
+      <c r="K16" s="110"/>
+      <c r="L16" s="111"/>
+      <c r="M16" s="111"/>
+      <c r="N16" s="111"/>
+      <c r="O16" s="111"/>
+      <c r="P16" s="111"/>
+      <c r="Q16" s="111"/>
+      <c r="R16" s="112"/>
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="6">
         <v>13</v>
       </c>
-      <c r="B17" s="122"/>
-      <c r="C17" s="121"/>
-      <c r="D17" s="122"/>
-      <c r="E17" s="121"/>
-      <c r="F17" s="122"/>
-      <c r="G17" s="130"/>
-      <c r="H17" s="130"/>
-      <c r="I17" s="130"/>
-      <c r="J17" s="121"/>
-      <c r="K17" s="126"/>
-      <c r="L17" s="124"/>
-      <c r="M17" s="124"/>
-      <c r="N17" s="124"/>
-      <c r="O17" s="124"/>
-      <c r="P17" s="124"/>
-      <c r="Q17" s="124"/>
-      <c r="R17" s="125"/>
+      <c r="B17" s="107"/>
+      <c r="C17" s="108"/>
+      <c r="D17" s="107"/>
+      <c r="E17" s="108"/>
+      <c r="F17" s="107"/>
+      <c r="G17" s="109"/>
+      <c r="H17" s="109"/>
+      <c r="I17" s="109"/>
+      <c r="J17" s="108"/>
+      <c r="K17" s="110"/>
+      <c r="L17" s="111"/>
+      <c r="M17" s="111"/>
+      <c r="N17" s="111"/>
+      <c r="O17" s="111"/>
+      <c r="P17" s="111"/>
+      <c r="Q17" s="111"/>
+      <c r="R17" s="112"/>
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="6">
         <v>14</v>
       </c>
-      <c r="B18" s="122"/>
-      <c r="C18" s="121"/>
-      <c r="D18" s="122"/>
-      <c r="E18" s="121"/>
-      <c r="F18" s="122"/>
-      <c r="G18" s="130"/>
-      <c r="H18" s="130"/>
-      <c r="I18" s="130"/>
-      <c r="J18" s="121"/>
-      <c r="K18" s="126"/>
-      <c r="L18" s="124"/>
-      <c r="M18" s="124"/>
-      <c r="N18" s="124"/>
-      <c r="O18" s="124"/>
-      <c r="P18" s="124"/>
-      <c r="Q18" s="124"/>
-      <c r="R18" s="125"/>
+      <c r="B18" s="107"/>
+      <c r="C18" s="108"/>
+      <c r="D18" s="107"/>
+      <c r="E18" s="108"/>
+      <c r="F18" s="107"/>
+      <c r="G18" s="109"/>
+      <c r="H18" s="109"/>
+      <c r="I18" s="109"/>
+      <c r="J18" s="108"/>
+      <c r="K18" s="110"/>
+      <c r="L18" s="111"/>
+      <c r="M18" s="111"/>
+      <c r="N18" s="111"/>
+      <c r="O18" s="111"/>
+      <c r="P18" s="111"/>
+      <c r="Q18" s="111"/>
+      <c r="R18" s="112"/>
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="6">
         <v>15</v>
       </c>
-      <c r="B19" s="122"/>
-      <c r="C19" s="121"/>
-      <c r="D19" s="122"/>
-      <c r="E19" s="121"/>
-      <c r="F19" s="122"/>
-      <c r="G19" s="130"/>
-      <c r="H19" s="130"/>
-      <c r="I19" s="130"/>
-      <c r="J19" s="121"/>
-      <c r="K19" s="126"/>
-      <c r="L19" s="124"/>
-      <c r="M19" s="124"/>
-      <c r="N19" s="124"/>
-      <c r="O19" s="124"/>
-      <c r="P19" s="124"/>
-      <c r="Q19" s="124"/>
-      <c r="R19" s="125"/>
+      <c r="B19" s="107"/>
+      <c r="C19" s="108"/>
+      <c r="D19" s="107"/>
+      <c r="E19" s="108"/>
+      <c r="F19" s="107"/>
+      <c r="G19" s="109"/>
+      <c r="H19" s="109"/>
+      <c r="I19" s="109"/>
+      <c r="J19" s="108"/>
+      <c r="K19" s="110"/>
+      <c r="L19" s="111"/>
+      <c r="M19" s="111"/>
+      <c r="N19" s="111"/>
+      <c r="O19" s="111"/>
+      <c r="P19" s="111"/>
+      <c r="Q19" s="111"/>
+      <c r="R19" s="112"/>
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="6">
         <v>16</v>
       </c>
-      <c r="B20" s="122"/>
-      <c r="C20" s="121"/>
-      <c r="D20" s="122"/>
-      <c r="E20" s="121"/>
-      <c r="F20" s="122"/>
-      <c r="G20" s="130"/>
-      <c r="H20" s="130"/>
-      <c r="I20" s="130"/>
-      <c r="J20" s="121"/>
-      <c r="K20" s="126"/>
-      <c r="L20" s="124"/>
-      <c r="M20" s="124"/>
-      <c r="N20" s="124"/>
-      <c r="O20" s="124"/>
-      <c r="P20" s="124"/>
-      <c r="Q20" s="124"/>
-      <c r="R20" s="125"/>
+      <c r="B20" s="107"/>
+      <c r="C20" s="108"/>
+      <c r="D20" s="107"/>
+      <c r="E20" s="108"/>
+      <c r="F20" s="107"/>
+      <c r="G20" s="109"/>
+      <c r="H20" s="109"/>
+      <c r="I20" s="109"/>
+      <c r="J20" s="108"/>
+      <c r="K20" s="110"/>
+      <c r="L20" s="111"/>
+      <c r="M20" s="111"/>
+      <c r="N20" s="111"/>
+      <c r="O20" s="111"/>
+      <c r="P20" s="111"/>
+      <c r="Q20" s="111"/>
+      <c r="R20" s="112"/>
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="6">
         <v>17</v>
       </c>
-      <c r="B21" s="122"/>
-      <c r="C21" s="121"/>
-      <c r="D21" s="122"/>
-      <c r="E21" s="121"/>
-      <c r="F21" s="122"/>
-      <c r="G21" s="130"/>
-      <c r="H21" s="130"/>
-      <c r="I21" s="130"/>
-      <c r="J21" s="121"/>
-      <c r="K21" s="126"/>
-      <c r="L21" s="124"/>
-      <c r="M21" s="124"/>
-      <c r="N21" s="124"/>
-      <c r="O21" s="124"/>
-      <c r="P21" s="124"/>
-      <c r="Q21" s="124"/>
-      <c r="R21" s="125"/>
+      <c r="B21" s="107"/>
+      <c r="C21" s="108"/>
+      <c r="D21" s="107"/>
+      <c r="E21" s="108"/>
+      <c r="F21" s="107"/>
+      <c r="G21" s="109"/>
+      <c r="H21" s="109"/>
+      <c r="I21" s="109"/>
+      <c r="J21" s="108"/>
+      <c r="K21" s="110"/>
+      <c r="L21" s="111"/>
+      <c r="M21" s="111"/>
+      <c r="N21" s="111"/>
+      <c r="O21" s="111"/>
+      <c r="P21" s="111"/>
+      <c r="Q21" s="111"/>
+      <c r="R21" s="112"/>
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="6">
         <v>18</v>
       </c>
-      <c r="B22" s="122"/>
-      <c r="C22" s="121"/>
-      <c r="D22" s="122"/>
-      <c r="E22" s="121"/>
-      <c r="F22" s="122"/>
-      <c r="G22" s="130"/>
-      <c r="H22" s="130"/>
-      <c r="I22" s="130"/>
-      <c r="J22" s="121"/>
-      <c r="K22" s="126"/>
-      <c r="L22" s="124"/>
-      <c r="M22" s="124"/>
-      <c r="N22" s="124"/>
-      <c r="O22" s="124"/>
-      <c r="P22" s="124"/>
-      <c r="Q22" s="124"/>
-      <c r="R22" s="125"/>
+      <c r="B22" s="107"/>
+      <c r="C22" s="108"/>
+      <c r="D22" s="107"/>
+      <c r="E22" s="108"/>
+      <c r="F22" s="107"/>
+      <c r="G22" s="109"/>
+      <c r="H22" s="109"/>
+      <c r="I22" s="109"/>
+      <c r="J22" s="108"/>
+      <c r="K22" s="110"/>
+      <c r="L22" s="111"/>
+      <c r="M22" s="111"/>
+      <c r="N22" s="111"/>
+      <c r="O22" s="111"/>
+      <c r="P22" s="111"/>
+      <c r="Q22" s="111"/>
+      <c r="R22" s="112"/>
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="5"/>
@@ -3987,6 +3997,78 @@
     </row>
   </sheetData>
   <mergeCells count="80">
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="D1:O2"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="D4:E4"/>
+    <mergeCell ref="F4:J4"/>
+    <mergeCell ref="K4:R4"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:J5"/>
+    <mergeCell ref="K5:R5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:J6"/>
+    <mergeCell ref="K6:R6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:J7"/>
+    <mergeCell ref="K7:R7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:J8"/>
+    <mergeCell ref="K8:R8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:J9"/>
+    <mergeCell ref="K9:R9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:J10"/>
+    <mergeCell ref="K10:R10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:J11"/>
+    <mergeCell ref="K11:R11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:J12"/>
+    <mergeCell ref="K12:R12"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="K13:R13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:J14"/>
+    <mergeCell ref="K14:R14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:J15"/>
+    <mergeCell ref="K15:R15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="K16:R16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:J17"/>
+    <mergeCell ref="K17:R17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:J18"/>
+    <mergeCell ref="K18:R18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:J19"/>
+    <mergeCell ref="K19:R19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:J20"/>
+    <mergeCell ref="K20:R20"/>
     <mergeCell ref="B21:C21"/>
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="F21:J21"/>
@@ -3995,78 +4077,6 @@
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="F22:J22"/>
     <mergeCell ref="K22:R22"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:J19"/>
-    <mergeCell ref="K19:R19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:J20"/>
-    <mergeCell ref="K20:R20"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:J17"/>
-    <mergeCell ref="K17:R17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:J18"/>
-    <mergeCell ref="K18:R18"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:J15"/>
-    <mergeCell ref="K15:R15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="K16:R16"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="K13:R13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:J14"/>
-    <mergeCell ref="K14:R14"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:J11"/>
-    <mergeCell ref="K11:R11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="K12:R12"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:J9"/>
-    <mergeCell ref="K9:R9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:J10"/>
-    <mergeCell ref="K10:R10"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:J7"/>
-    <mergeCell ref="K7:R7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:J8"/>
-    <mergeCell ref="K8:R8"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:J5"/>
-    <mergeCell ref="K5:R5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:J6"/>
-    <mergeCell ref="K6:R6"/>
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="D1:O2"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="D4:E4"/>
-    <mergeCell ref="F4:J4"/>
-    <mergeCell ref="K4:R4"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4082,27 +4092,27 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="95" t="s">
+      <c r="B1" s="88"/>
+      <c r="C1" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="96"/>
-      <c r="E1" s="96"/>
-      <c r="F1" s="96"/>
-      <c r="G1" s="96"/>
-      <c r="H1" s="96"/>
-      <c r="I1" s="96"/>
-      <c r="J1" s="96"/>
-      <c r="K1" s="96"/>
-      <c r="L1" s="96"/>
+      <c r="D1" s="124"/>
+      <c r="E1" s="124"/>
+      <c r="F1" s="124"/>
+      <c r="G1" s="124"/>
+      <c r="H1" s="124"/>
+      <c r="I1" s="124"/>
+      <c r="J1" s="124"/>
+      <c r="K1" s="124"/>
+      <c r="L1" s="124"/>
       <c r="M1" s="24" t="s">
         <v>2</v>
       </c>
       <c r="N1" s="22" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="O1" s="25" t="s">
         <v>3</v>
@@ -4110,18 +4120,18 @@
       <c r="P1" s="83"/>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="98"/>
-      <c r="B2" s="100"/>
-      <c r="C2" s="98"/>
-      <c r="D2" s="99"/>
-      <c r="E2" s="99"/>
-      <c r="F2" s="99"/>
-      <c r="G2" s="99"/>
-      <c r="H2" s="99"/>
-      <c r="I2" s="99"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
+      <c r="A2" s="89"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="89"/>
+      <c r="D2" s="125"/>
+      <c r="E2" s="125"/>
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="125"/>
+      <c r="I2" s="125"/>
+      <c r="J2" s="125"/>
+      <c r="K2" s="125"/>
+      <c r="L2" s="125"/>
       <c r="M2" s="27" t="s">
         <v>14</v>
       </c>
@@ -4152,26 +4162,26 @@
       <c r="A4" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="131" t="s">
+      <c r="B4" s="139" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="132"/>
-      <c r="D4" s="132"/>
-      <c r="E4" s="132"/>
-      <c r="F4" s="132"/>
-      <c r="G4" s="133"/>
+      <c r="C4" s="140"/>
+      <c r="D4" s="140"/>
+      <c r="E4" s="140"/>
+      <c r="F4" s="140"/>
+      <c r="G4" s="141"/>
       <c r="H4" s="30"/>
       <c r="I4" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="131" t="s">
+      <c r="J4" s="139" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="132"/>
-      <c r="L4" s="132"/>
-      <c r="M4" s="132"/>
-      <c r="N4" s="132"/>
-      <c r="O4" s="133"/>
+      <c r="K4" s="140"/>
+      <c r="L4" s="140"/>
+      <c r="M4" s="140"/>
+      <c r="N4" s="140"/>
+      <c r="O4" s="141"/>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="16"/>
@@ -4195,7 +4205,7 @@
         <v>18</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="C6" s="30"/>
       <c r="D6" s="30"/>
@@ -4203,7 +4213,7 @@
       <c r="F6" s="30"/>
       <c r="G6" s="30"/>
       <c r="I6" s="35" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="J6" s="30" t="s">
         <v>70</v>
@@ -4216,10 +4226,10 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="81" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="C7" s="30"/>
       <c r="D7" s="30"/>
@@ -4227,10 +4237,10 @@
       <c r="F7" s="30"/>
       <c r="G7" s="30"/>
       <c r="I7" s="81" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="J7" s="30" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="K7" s="30"/>
       <c r="L7" s="30"/>
@@ -4240,10 +4250,10 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="81" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="C8" s="34"/>
       <c r="D8" s="34"/>
@@ -4251,10 +4261,10 @@
       <c r="F8" s="34"/>
       <c r="G8" s="34"/>
       <c r="I8" s="81" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="J8" s="34" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="K8" s="34"/>
       <c r="L8" s="34"/>
@@ -4264,10 +4274,10 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="81" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="C9" s="30"/>
       <c r="D9" s="30"/>
@@ -4275,10 +4285,10 @@
       <c r="F9" s="30"/>
       <c r="G9" s="30"/>
       <c r="I9" s="81" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="K9" s="30"/>
       <c r="L9" s="30"/>
@@ -4288,10 +4298,10 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="81" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="C10" s="30"/>
       <c r="D10" s="30"/>
@@ -4308,7 +4318,7 @@
         <v>1.5</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="C11" s="30"/>
       <c r="D11" s="30"/>
@@ -4316,7 +4326,7 @@
       <c r="F11" s="30"/>
       <c r="G11" s="30"/>
       <c r="I11" s="35" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="J11" s="30"/>
       <c r="K11" s="30"/>
@@ -4334,10 +4344,10 @@
       <c r="F12" s="30"/>
       <c r="G12" s="30"/>
       <c r="I12" s="82" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="J12" s="30" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="K12" s="30"/>
       <c r="L12" s="30"/>
@@ -4350,7 +4360,7 @@
         <v>22</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="C13" s="30"/>
       <c r="D13" s="30"/>
@@ -4359,7 +4369,7 @@
       <c r="G13" s="30"/>
       <c r="I13" s="35"/>
       <c r="J13" s="30" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="K13" s="30"/>
       <c r="L13" s="30"/>
@@ -4369,10 +4379,10 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="82" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="C14" s="30"/>
       <c r="D14" s="30"/>
@@ -4380,7 +4390,7 @@
       <c r="F14" s="30"/>
       <c r="G14" s="30"/>
       <c r="J14" s="30" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="K14" s="30"/>
       <c r="L14" s="30"/>
@@ -4408,7 +4418,7 @@
         <v>23</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="C16" s="30"/>
       <c r="D16" s="30"/>
@@ -4417,7 +4427,7 @@
       <c r="G16" s="30"/>
       <c r="H16" s="7"/>
       <c r="I16" s="16" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="J16" s="30"/>
       <c r="K16" s="30"/>
@@ -4428,10 +4438,10 @@
     </row>
     <row r="17" spans="1:15" ht="26.5">
       <c r="A17" s="82" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="B17" s="30" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="C17" s="30"/>
       <c r="D17" s="30"/>
@@ -4440,10 +4450,10 @@
       <c r="G17" s="30"/>
       <c r="H17" s="7"/>
       <c r="I17" s="82" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="J17" s="30" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="K17" s="36"/>
       <c r="L17" s="36"/>
@@ -4453,10 +4463,10 @@
     </row>
     <row r="18" spans="1:15" ht="26.5">
       <c r="A18" s="82" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="C18" s="34"/>
       <c r="D18" s="34"/>
@@ -4603,23 +4613,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="20">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="135" t="s">
+      <c r="B1" s="88"/>
+      <c r="C1" s="91" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="136"/>
-      <c r="E1" s="137" t="s">
+      <c r="D1" s="92"/>
+      <c r="E1" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
-      <c r="I1" s="138"/>
-      <c r="J1" s="138"/>
-      <c r="K1" s="139"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
+      <c r="H1" s="94"/>
+      <c r="I1" s="94"/>
+      <c r="J1" s="94"/>
+      <c r="K1" s="95"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
@@ -4634,17 +4644,17 @@
       </c>
     </row>
     <row r="2" spans="1:18" ht="20">
-      <c r="A2" s="98"/>
-      <c r="B2" s="100"/>
-      <c r="C2" s="135"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="137"/>
-      <c r="F2" s="138"/>
-      <c r="G2" s="138"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
-      <c r="K2" s="139"/>
+      <c r="A2" s="89"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
+      <c r="H2" s="94"/>
+      <c r="I2" s="94"/>
+      <c r="J2" s="94"/>
+      <c r="K2" s="95"/>
       <c r="L2" s="29" t="s">
         <v>14</v>
       </c>
@@ -4692,27 +4702,27 @@
     </row>
     <row r="5" spans="1:18" ht="18" customHeight="1">
       <c r="A5" s="8"/>
-      <c r="B5" s="140" t="s">
-        <v>182</v>
-      </c>
-      <c r="C5" s="140"/>
-      <c r="D5" s="140"/>
-      <c r="E5" s="140"/>
-      <c r="F5" s="140"/>
-      <c r="G5" s="140"/>
-      <c r="H5" s="140"/>
-      <c r="I5" s="140"/>
-      <c r="J5" s="140"/>
-      <c r="K5" s="140"/>
-      <c r="L5" s="140"/>
-      <c r="M5" s="140"/>
-      <c r="N5" s="140"/>
+      <c r="B5" s="96" t="s">
+        <v>171</v>
+      </c>
+      <c r="C5" s="96"/>
+      <c r="D5" s="96"/>
+      <c r="E5" s="96"/>
+      <c r="F5" s="96"/>
+      <c r="G5" s="96"/>
+      <c r="H5" s="96"/>
+      <c r="I5" s="96"/>
+      <c r="J5" s="96"/>
+      <c r="K5" s="96"/>
+      <c r="L5" s="96"/>
+      <c r="M5" s="96"/>
+      <c r="N5" s="96"/>
       <c r="O5" s="8"/>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="34"/>
       <c r="B6" s="34" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="C6" s="34"/>
       <c r="D6" s="34"/>
@@ -4766,78 +4776,78 @@
     </row>
     <row r="9" spans="1:18" ht="18" customHeight="1">
       <c r="A9" s="34"/>
-      <c r="B9" s="141" t="s">
-        <v>184</v>
-      </c>
-      <c r="C9" s="141"/>
-      <c r="D9" s="141"/>
-      <c r="E9" s="141"/>
-      <c r="F9" s="141"/>
-      <c r="G9" s="141"/>
-      <c r="H9" s="141"/>
-      <c r="I9" s="141"/>
-      <c r="J9" s="141"/>
-      <c r="K9" s="141"/>
-      <c r="L9" s="141"/>
-      <c r="M9" s="141"/>
-      <c r="N9" s="141"/>
+      <c r="B9" s="85" t="s">
+        <v>173</v>
+      </c>
+      <c r="C9" s="85"/>
+      <c r="D9" s="85"/>
+      <c r="E9" s="85"/>
+      <c r="F9" s="85"/>
+      <c r="G9" s="85"/>
+      <c r="H9" s="85"/>
+      <c r="I9" s="85"/>
+      <c r="J9" s="85"/>
+      <c r="K9" s="85"/>
+      <c r="L9" s="85"/>
+      <c r="M9" s="85"/>
+      <c r="N9" s="85"/>
       <c r="O9" s="34"/>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="34"/>
-      <c r="B10" s="141" t="s">
-        <v>185</v>
-      </c>
-      <c r="C10" s="141"/>
-      <c r="D10" s="141"/>
-      <c r="E10" s="141"/>
-      <c r="F10" s="141"/>
-      <c r="G10" s="141"/>
-      <c r="H10" s="141"/>
-      <c r="I10" s="141"/>
-      <c r="J10" s="141"/>
-      <c r="K10" s="141"/>
-      <c r="L10" s="141"/>
-      <c r="M10" s="141"/>
-      <c r="N10" s="141"/>
+      <c r="B10" s="85" t="s">
+        <v>174</v>
+      </c>
+      <c r="C10" s="85"/>
+      <c r="D10" s="85"/>
+      <c r="E10" s="85"/>
+      <c r="F10" s="85"/>
+      <c r="G10" s="85"/>
+      <c r="H10" s="85"/>
+      <c r="I10" s="85"/>
+      <c r="J10" s="85"/>
+      <c r="K10" s="85"/>
+      <c r="L10" s="85"/>
+      <c r="M10" s="85"/>
+      <c r="N10" s="85"/>
       <c r="O10" s="34"/>
     </row>
     <row r="11" spans="1:18" ht="18" customHeight="1">
       <c r="A11" s="34"/>
-      <c r="B11" s="141" t="s">
-        <v>186</v>
-      </c>
-      <c r="C11" s="141"/>
-      <c r="D11" s="141"/>
-      <c r="E11" s="141"/>
-      <c r="F11" s="141"/>
-      <c r="G11" s="141"/>
-      <c r="H11" s="141"/>
-      <c r="I11" s="141"/>
-      <c r="J11" s="141"/>
-      <c r="K11" s="141"/>
-      <c r="L11" s="141"/>
-      <c r="M11" s="141"/>
-      <c r="N11" s="141"/>
-      <c r="O11" s="141"/>
+      <c r="B11" s="85" t="s">
+        <v>175</v>
+      </c>
+      <c r="C11" s="85"/>
+      <c r="D11" s="85"/>
+      <c r="E11" s="85"/>
+      <c r="F11" s="85"/>
+      <c r="G11" s="85"/>
+      <c r="H11" s="85"/>
+      <c r="I11" s="85"/>
+      <c r="J11" s="85"/>
+      <c r="K11" s="85"/>
+      <c r="L11" s="85"/>
+      <c r="M11" s="85"/>
+      <c r="N11" s="85"/>
+      <c r="O11" s="85"/>
     </row>
     <row r="12" spans="1:18" ht="18" customHeight="1">
       <c r="A12" s="34"/>
-      <c r="B12" s="141" t="s">
-        <v>187</v>
-      </c>
-      <c r="C12" s="141"/>
-      <c r="D12" s="141"/>
-      <c r="E12" s="141"/>
-      <c r="F12" s="141"/>
-      <c r="G12" s="141"/>
-      <c r="H12" s="141"/>
-      <c r="I12" s="141"/>
-      <c r="J12" s="141"/>
-      <c r="K12" s="141"/>
-      <c r="L12" s="141"/>
-      <c r="M12" s="141"/>
-      <c r="N12" s="141"/>
+      <c r="B12" s="85" t="s">
+        <v>176</v>
+      </c>
+      <c r="C12" s="85"/>
+      <c r="D12" s="85"/>
+      <c r="E12" s="85"/>
+      <c r="F12" s="85"/>
+      <c r="G12" s="85"/>
+      <c r="H12" s="85"/>
+      <c r="I12" s="85"/>
+      <c r="J12" s="85"/>
+      <c r="K12" s="85"/>
+      <c r="L12" s="85"/>
+      <c r="M12" s="85"/>
+      <c r="N12" s="85"/>
       <c r="O12" s="47"/>
       <c r="P12" s="47"/>
       <c r="Q12" s="47"/>
@@ -4884,115 +4894,115 @@
     </row>
     <row r="15" spans="1:18" ht="18" customHeight="1">
       <c r="A15" s="34"/>
-      <c r="B15" s="134" t="s">
+      <c r="B15" s="86" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="134"/>
-      <c r="D15" s="134"/>
-      <c r="E15" s="134"/>
-      <c r="F15" s="134"/>
-      <c r="G15" s="134"/>
-      <c r="H15" s="134"/>
-      <c r="I15" s="134"/>
-      <c r="J15" s="134"/>
-      <c r="K15" s="134"/>
-      <c r="L15" s="134"/>
-      <c r="M15" s="134"/>
-      <c r="N15" s="134"/>
-      <c r="O15" s="134"/>
+      <c r="C15" s="86"/>
+      <c r="D15" s="86"/>
+      <c r="E15" s="86"/>
+      <c r="F15" s="86"/>
+      <c r="G15" s="86"/>
+      <c r="H15" s="86"/>
+      <c r="I15" s="86"/>
+      <c r="J15" s="86"/>
+      <c r="K15" s="86"/>
+      <c r="L15" s="86"/>
+      <c r="M15" s="86"/>
+      <c r="N15" s="86"/>
+      <c r="O15" s="86"/>
     </row>
     <row r="16" spans="1:18" ht="18" customHeight="1">
       <c r="A16" s="34"/>
-      <c r="B16" s="134" t="s">
-        <v>71</v>
-      </c>
-      <c r="C16" s="134"/>
-      <c r="D16" s="134"/>
-      <c r="E16" s="134"/>
-      <c r="F16" s="134"/>
-      <c r="G16" s="134"/>
-      <c r="H16" s="134"/>
-      <c r="I16" s="134"/>
-      <c r="J16" s="134"/>
-      <c r="K16" s="134"/>
-      <c r="L16" s="134"/>
-      <c r="M16" s="134"/>
-      <c r="N16" s="134"/>
-      <c r="O16" s="134"/>
+      <c r="B16" s="86" t="s">
+        <v>75</v>
+      </c>
+      <c r="C16" s="86"/>
+      <c r="D16" s="86"/>
+      <c r="E16" s="86"/>
+      <c r="F16" s="86"/>
+      <c r="G16" s="86"/>
+      <c r="H16" s="86"/>
+      <c r="I16" s="86"/>
+      <c r="J16" s="86"/>
+      <c r="K16" s="86"/>
+      <c r="L16" s="86"/>
+      <c r="M16" s="86"/>
+      <c r="N16" s="86"/>
+      <c r="O16" s="86"/>
     </row>
     <row r="17" spans="1:15" ht="18" customHeight="1">
       <c r="A17" s="34"/>
-      <c r="B17" s="134" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" s="134"/>
-      <c r="D17" s="134"/>
-      <c r="E17" s="134"/>
-      <c r="F17" s="134"/>
-      <c r="G17" s="134"/>
-      <c r="H17" s="134"/>
-      <c r="I17" s="134"/>
-      <c r="J17" s="134"/>
-      <c r="K17" s="134"/>
-      <c r="L17" s="134"/>
-      <c r="M17" s="134"/>
-      <c r="N17" s="134"/>
-      <c r="O17" s="134"/>
+      <c r="B17" s="86" t="s">
+        <v>177</v>
+      </c>
+      <c r="C17" s="86"/>
+      <c r="D17" s="86"/>
+      <c r="E17" s="86"/>
+      <c r="F17" s="86"/>
+      <c r="G17" s="86"/>
+      <c r="H17" s="86"/>
+      <c r="I17" s="86"/>
+      <c r="J17" s="86"/>
+      <c r="K17" s="86"/>
+      <c r="L17" s="86"/>
+      <c r="M17" s="86"/>
+      <c r="N17" s="86"/>
+      <c r="O17" s="86"/>
     </row>
     <row r="18" spans="1:15" ht="18" customHeight="1">
       <c r="A18" s="34"/>
-      <c r="B18" s="134" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" s="134"/>
-      <c r="D18" s="134"/>
-      <c r="E18" s="134"/>
-      <c r="F18" s="134"/>
-      <c r="G18" s="134"/>
-      <c r="H18" s="134"/>
-      <c r="I18" s="134"/>
-      <c r="J18" s="134"/>
-      <c r="K18" s="134"/>
-      <c r="L18" s="134"/>
-      <c r="M18" s="134"/>
-      <c r="N18" s="134"/>
-      <c r="O18" s="134"/>
+      <c r="B18" s="86" t="s">
+        <v>178</v>
+      </c>
+      <c r="C18" s="86"/>
+      <c r="D18" s="86"/>
+      <c r="E18" s="86"/>
+      <c r="F18" s="86"/>
+      <c r="G18" s="86"/>
+      <c r="H18" s="86"/>
+      <c r="I18" s="86"/>
+      <c r="J18" s="86"/>
+      <c r="K18" s="86"/>
+      <c r="L18" s="86"/>
+      <c r="M18" s="86"/>
+      <c r="N18" s="86"/>
+      <c r="O18" s="86"/>
     </row>
     <row r="19" spans="1:15" ht="18" customHeight="1">
       <c r="A19" s="34"/>
-      <c r="B19" s="134" t="s">
-        <v>73</v>
-      </c>
-      <c r="C19" s="134"/>
-      <c r="D19" s="134"/>
-      <c r="E19" s="134"/>
-      <c r="F19" s="134"/>
-      <c r="G19" s="134"/>
-      <c r="H19" s="134"/>
-      <c r="I19" s="134"/>
-      <c r="J19" s="134"/>
-      <c r="K19" s="134"/>
-      <c r="L19" s="134"/>
-      <c r="M19" s="134"/>
-      <c r="N19" s="134"/>
-      <c r="O19" s="134"/>
+      <c r="B19" s="86" t="s">
+        <v>179</v>
+      </c>
+      <c r="C19" s="86"/>
+      <c r="D19" s="86"/>
+      <c r="E19" s="86"/>
+      <c r="F19" s="86"/>
+      <c r="G19" s="86"/>
+      <c r="H19" s="86"/>
+      <c r="I19" s="86"/>
+      <c r="J19" s="86"/>
+      <c r="K19" s="86"/>
+      <c r="L19" s="86"/>
+      <c r="M19" s="86"/>
+      <c r="N19" s="86"/>
+      <c r="O19" s="86"/>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="34"/>
-      <c r="B20" s="134"/>
-      <c r="C20" s="134"/>
-      <c r="D20" s="134"/>
-      <c r="E20" s="134"/>
-      <c r="F20" s="134"/>
-      <c r="G20" s="134"/>
-      <c r="H20" s="134"/>
-      <c r="I20" s="134"/>
-      <c r="J20" s="134"/>
-      <c r="K20" s="134"/>
-      <c r="L20" s="134"/>
-      <c r="M20" s="134"/>
-      <c r="N20" s="134"/>
-      <c r="O20" s="134"/>
+      <c r="B20" s="86"/>
+      <c r="C20" s="86"/>
+      <c r="D20" s="86"/>
+      <c r="E20" s="86"/>
+      <c r="F20" s="86"/>
+      <c r="G20" s="86"/>
+      <c r="H20" s="86"/>
+      <c r="I20" s="86"/>
+      <c r="J20" s="86"/>
+      <c r="K20" s="86"/>
+      <c r="L20" s="86"/>
+      <c r="M20" s="86"/>
+      <c r="N20" s="86"/>
+      <c r="O20" s="86"/>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="34"/>
@@ -5033,7 +5043,7 @@
     <row r="23" spans="1:15">
       <c r="A23" s="34"/>
       <c r="B23" s="41" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C23" s="42"/>
       <c r="D23" s="42"/>
@@ -5105,7 +5115,7 @@
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="44" t="s">
-        <v>75</v>
+        <v>180</v>
       </c>
       <c r="C27" s="45"/>
       <c r="D27" s="45"/>
@@ -5124,7 +5134,7 @@
     <row r="28" spans="1:15">
       <c r="A28" s="8"/>
       <c r="B28" s="44" t="s">
-        <v>76</v>
+        <v>181</v>
       </c>
       <c r="C28" s="45"/>
       <c r="D28" s="45"/>
@@ -5143,7 +5153,7 @@
     <row r="29" spans="1:15">
       <c r="A29" s="8"/>
       <c r="B29" s="44" t="s">
-        <v>78</v>
+        <v>182</v>
       </c>
       <c r="C29" s="45"/>
       <c r="D29" s="45"/>
@@ -5197,7 +5207,7 @@
     <row r="32" spans="1:15">
       <c r="A32" s="8"/>
       <c r="B32" s="46" t="s">
-        <v>79</v>
+        <v>183</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -5216,7 +5226,7 @@
     <row r="33" spans="1:15">
       <c r="A33" s="8"/>
       <c r="B33" s="46" t="s">
-        <v>80</v>
+        <v>184</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
@@ -5235,7 +5245,7 @@
     <row r="34" spans="1:15">
       <c r="A34" s="8"/>
       <c r="B34" s="46" t="s">
-        <v>81</v>
+        <v>185</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
@@ -5253,7 +5263,9 @@
     </row>
     <row r="35" spans="1:15">
       <c r="A35" s="8"/>
-      <c r="B35" s="46"/>
+      <c r="B35" s="46" t="s">
+        <v>186</v>
+      </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
       <c r="E35" s="8"/>
@@ -5270,6 +5282,7 @@
     </row>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B16:O16"/>
     <mergeCell ref="B11:O11"/>
     <mergeCell ref="B12:N12"/>
     <mergeCell ref="B20:O20"/>
@@ -5280,7 +5293,6 @@
     <mergeCell ref="E2:K2"/>
     <mergeCell ref="B5:N5"/>
     <mergeCell ref="B15:O15"/>
-    <mergeCell ref="B16:O16"/>
     <mergeCell ref="B17:O17"/>
     <mergeCell ref="B18:O18"/>
     <mergeCell ref="B19:O19"/>
@@ -5301,23 +5313,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="135" t="s">
+      <c r="B1" s="88"/>
+      <c r="C1" s="91" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="136"/>
-      <c r="E1" s="137" t="s">
+      <c r="D1" s="92"/>
+      <c r="E1" s="93" t="s">
         <v>32</v>
       </c>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
-      <c r="I1" s="138"/>
-      <c r="J1" s="138"/>
-      <c r="K1" s="139"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
+      <c r="H1" s="94"/>
+      <c r="I1" s="94"/>
+      <c r="J1" s="94"/>
+      <c r="K1" s="95"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
@@ -5327,20 +5339,22 @@
       <c r="N1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="38"/>
+      <c r="O1" s="38">
+        <v>46289</v>
+      </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="98"/>
-      <c r="B2" s="100"/>
-      <c r="C2" s="135"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="137"/>
-      <c r="F2" s="138"/>
-      <c r="G2" s="138"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
-      <c r="K2" s="139"/>
+      <c r="A2" s="89"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
+      <c r="H2" s="94"/>
+      <c r="I2" s="94"/>
+      <c r="J2" s="94"/>
+      <c r="K2" s="95"/>
       <c r="L2" s="29" t="s">
         <v>14</v>
       </c>
@@ -5410,7 +5424,7 @@
       </c>
       <c r="C6" s="145"/>
       <c r="D6" s="74" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="E6" s="49"/>
       <c r="F6" s="49"/>
@@ -5427,11 +5441,11 @@
     <row r="7" spans="1:15">
       <c r="A7" s="34"/>
       <c r="B7" s="142" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="C7" s="143"/>
       <c r="D7" s="17" t="s">
-        <v>84</v>
+        <v>188</v>
       </c>
       <c r="E7" s="53"/>
       <c r="F7" s="53"/>
@@ -5452,7 +5466,7 @@
       </c>
       <c r="C8" s="143"/>
       <c r="D8" s="17" t="s">
-        <v>85</v>
+        <v>187</v>
       </c>
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
@@ -5916,14 +5930,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="135" t="s">
+      <c r="B1" s="88"/>
+      <c r="C1" s="91" t="s">
         <v>23</v>
       </c>
-      <c r="D1" s="136"/>
+      <c r="D1" s="92"/>
       <c r="E1" s="70" t="s">
         <v>60</v>
       </c>
@@ -5945,16 +5959,16 @@
       <c r="O1" s="149"/>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="98"/>
-      <c r="B2" s="100"/>
-      <c r="C2" s="135"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="138"/>
-      <c r="F2" s="138"/>
-      <c r="G2" s="138"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="139"/>
+      <c r="A2" s="89"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="94"/>
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
+      <c r="H2" s="94"/>
+      <c r="I2" s="94"/>
+      <c r="J2" s="95"/>
       <c r="K2" s="29" t="s">
         <v>14</v>
       </c>
@@ -6044,12 +6058,12 @@
     <row r="7" spans="1:15">
       <c r="A7" s="34"/>
       <c r="B7" s="52" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="C7" s="53"/>
       <c r="D7" s="53"/>
       <c r="E7" s="67" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="F7" s="23"/>
       <c r="G7" s="53"/>
@@ -6057,7 +6071,7 @@
       <c r="I7" s="53"/>
       <c r="J7" s="54"/>
       <c r="K7" s="68" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="L7" s="54"/>
       <c r="M7" s="30"/>
@@ -6067,7 +6081,7 @@
     <row r="8" spans="1:15">
       <c r="A8" s="34"/>
       <c r="B8" s="52" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="C8" s="53"/>
       <c r="D8" s="53"/>
@@ -6080,7 +6094,7 @@
       <c r="I8" s="53"/>
       <c r="J8" s="54"/>
       <c r="K8" s="68" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="L8" s="54"/>
       <c r="M8" s="30"/>
@@ -6090,12 +6104,12 @@
     <row r="9" spans="1:15">
       <c r="A9" s="34"/>
       <c r="B9" s="52" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="C9" s="53"/>
       <c r="D9" s="53"/>
       <c r="E9" s="67" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="F9" s="23"/>
       <c r="G9" s="53"/>
@@ -6103,7 +6117,7 @@
       <c r="I9" s="53"/>
       <c r="J9" s="54"/>
       <c r="K9" s="68" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="L9" s="54"/>
       <c r="M9" s="30"/>
@@ -6113,12 +6127,12 @@
     <row r="10" spans="1:15">
       <c r="A10" s="34"/>
       <c r="B10" s="17" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
       <c r="E10" s="146" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="F10" s="147"/>
       <c r="G10" s="147"/>
@@ -6126,7 +6140,7 @@
       <c r="I10" s="147"/>
       <c r="J10" s="148"/>
       <c r="K10" s="68" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="L10" s="54"/>
       <c r="M10" s="30"/>
@@ -6136,12 +6150,12 @@
     <row r="11" spans="1:15">
       <c r="A11" s="34"/>
       <c r="B11" s="146" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="C11" s="147"/>
       <c r="D11" s="148"/>
       <c r="E11" s="67" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="F11" s="23"/>
       <c r="G11" s="53"/>
@@ -6149,7 +6163,7 @@
       <c r="I11" s="53"/>
       <c r="J11" s="54"/>
       <c r="K11" s="68" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="L11" s="54"/>
       <c r="M11" s="30"/>
@@ -6184,7 +6198,7 @@
     <row r="14" spans="1:15">
       <c r="A14" s="34"/>
       <c r="B14" s="41" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="C14" s="41"/>
       <c r="D14" s="41"/>
@@ -6203,7 +6217,7 @@
     <row r="15" spans="1:15">
       <c r="A15" s="34"/>
       <c r="B15" s="7" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="C15" s="56"/>
       <c r="D15" s="56"/>
@@ -6211,7 +6225,7 @@
       <c r="F15" s="56"/>
       <c r="G15" s="56"/>
       <c r="H15" s="56" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="I15" s="56"/>
       <c r="J15" s="41"/>
@@ -6260,7 +6274,7 @@
     <row r="18" spans="1:15">
       <c r="A18" s="34"/>
       <c r="B18" s="7" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="C18" s="56"/>
       <c r="D18" s="56"/>
@@ -6279,7 +6293,7 @@
     <row r="19" spans="1:15">
       <c r="A19" s="34"/>
       <c r="B19" s="56" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="C19" s="41"/>
       <c r="D19" s="41"/>
@@ -6298,7 +6312,7 @@
     <row r="20" spans="1:15">
       <c r="A20" s="34"/>
       <c r="B20" s="7" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="C20" s="41"/>
       <c r="D20" s="41"/>
@@ -6334,7 +6348,7 @@
     <row r="22" spans="1:15">
       <c r="A22" s="34"/>
       <c r="B22" s="7" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="C22" s="41"/>
       <c r="D22" s="41"/>
@@ -6372,7 +6386,7 @@
     <row r="24" spans="1:15" ht="18" customHeight="1">
       <c r="A24" s="8"/>
       <c r="B24" s="56" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
@@ -6407,7 +6421,7 @@
     <row r="26" spans="1:15">
       <c r="A26" s="8"/>
       <c r="B26" s="41" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="C26" s="45"/>
       <c r="D26" s="45"/>
@@ -6426,7 +6440,7 @@
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="56" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="C27" s="45"/>
       <c r="D27" s="45"/>
@@ -6445,7 +6459,7 @@
     <row r="28" spans="1:15">
       <c r="A28" s="8"/>
       <c r="B28" s="56" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="C28" s="45"/>
       <c r="D28" s="45"/>
@@ -6464,7 +6478,7 @@
     <row r="29" spans="1:15">
       <c r="A29" s="8"/>
       <c r="B29" s="56" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="C29" s="45"/>
       <c r="D29" s="45"/>
@@ -6483,7 +6497,7 @@
     <row r="30" spans="1:15">
       <c r="A30" s="8"/>
       <c r="B30" s="56" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="C30" s="45"/>
       <c r="D30" s="45"/>
@@ -6519,7 +6533,7 @@
     <row r="32" spans="1:15">
       <c r="A32" s="8"/>
       <c r="B32" s="56" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="C32" s="45"/>
       <c r="D32" s="45"/>
@@ -6538,7 +6552,7 @@
     <row r="33" spans="1:15">
       <c r="A33" s="8"/>
       <c r="B33" s="8" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
@@ -6647,28 +6661,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="135" t="s">
+      <c r="B1" s="88"/>
+      <c r="C1" s="91" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="136"/>
-      <c r="E1" s="137" t="s">
+      <c r="D1" s="92"/>
+      <c r="E1" s="93" t="s">
         <v>36</v>
       </c>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
-      <c r="I1" s="138"/>
-      <c r="J1" s="138"/>
-      <c r="K1" s="139"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
+      <c r="H1" s="94"/>
+      <c r="I1" s="94"/>
+      <c r="J1" s="94"/>
+      <c r="K1" s="95"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -6676,17 +6690,17 @@
       <c r="O1" s="38"/>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="98"/>
-      <c r="B2" s="100"/>
-      <c r="C2" s="135"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="137"/>
-      <c r="F2" s="138"/>
-      <c r="G2" s="138"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
-      <c r="K2" s="139"/>
+      <c r="A2" s="89"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
+      <c r="H2" s="94"/>
+      <c r="I2" s="94"/>
+      <c r="J2" s="94"/>
+      <c r="K2" s="95"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
@@ -6735,7 +6749,7 @@
     <row r="5" spans="1:15">
       <c r="A5" s="8"/>
       <c r="B5" s="30" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="C5" s="30"/>
       <c r="D5" s="30"/>
@@ -6790,7 +6804,7 @@
     <row r="8" spans="1:15">
       <c r="A8" s="34"/>
       <c r="B8" s="34" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="C8" s="34"/>
       <c r="D8" s="34"/>
@@ -6826,7 +6840,7 @@
     <row r="10" spans="1:15">
       <c r="A10" s="34"/>
       <c r="B10" s="7" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -6845,7 +6859,7 @@
     <row r="11" spans="1:15">
       <c r="A11" s="34"/>
       <c r="B11" s="41" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="C11" s="41"/>
       <c r="D11" s="41"/>
@@ -7189,23 +7203,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="135" t="s">
+      <c r="B1" s="88"/>
+      <c r="C1" s="91" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="136"/>
-      <c r="E1" s="137" t="s">
+      <c r="D1" s="92"/>
+      <c r="E1" s="93" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
-      <c r="I1" s="138"/>
-      <c r="J1" s="138"/>
-      <c r="K1" s="139"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
+      <c r="H1" s="94"/>
+      <c r="I1" s="94"/>
+      <c r="J1" s="94"/>
+      <c r="K1" s="95"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
@@ -7218,17 +7232,17 @@
       <c r="O1" s="38"/>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="98"/>
-      <c r="B2" s="100"/>
-      <c r="C2" s="135"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="137"/>
-      <c r="F2" s="138"/>
-      <c r="G2" s="138"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
-      <c r="K2" s="139"/>
+      <c r="A2" s="89"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
+      <c r="H2" s="94"/>
+      <c r="I2" s="94"/>
+      <c r="J2" s="94"/>
+      <c r="K2" s="95"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
@@ -7258,7 +7272,7 @@
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="34" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -7304,11 +7318,11 @@
     <row r="6" spans="1:15">
       <c r="A6" s="8"/>
       <c r="B6" s="52" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="C6" s="60"/>
       <c r="D6" s="52" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="E6" s="55"/>
       <c r="F6" s="52">
@@ -7316,11 +7330,11 @@
       </c>
       <c r="G6" s="55"/>
       <c r="H6" s="52" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="I6" s="55"/>
       <c r="J6" s="52" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="K6" s="53"/>
       <c r="L6" s="61"/>
@@ -7401,7 +7415,7 @@
       </c>
       <c r="I9" s="55"/>
       <c r="J9" s="154" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="K9" s="155"/>
       <c r="L9" s="155"/>
@@ -7412,7 +7426,7 @@
     <row r="10" spans="1:15">
       <c r="A10" s="34"/>
       <c r="B10" s="52" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="C10" s="55"/>
       <c r="D10" s="52" t="s">
@@ -7424,11 +7438,11 @@
       </c>
       <c r="G10" s="55"/>
       <c r="H10" s="52" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="I10" s="23"/>
       <c r="J10" s="75" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="K10" s="23"/>
       <c r="L10" s="53"/>
@@ -7439,7 +7453,7 @@
     <row r="11" spans="1:15" ht="54" customHeight="1">
       <c r="A11" s="34"/>
       <c r="B11" s="67" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="C11" s="55"/>
       <c r="D11" s="52" t="s">
@@ -7455,7 +7469,7 @@
       </c>
       <c r="I11" s="23"/>
       <c r="J11" s="151" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="K11" s="152"/>
       <c r="L11" s="152"/>
@@ -7466,23 +7480,23 @@
     <row r="12" spans="1:15">
       <c r="A12" s="34"/>
       <c r="B12" s="17" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="C12" s="55"/>
       <c r="D12" s="52" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E12" s="55"/>
       <c r="F12" s="17" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="G12" s="55"/>
       <c r="H12" s="17" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="I12" s="55"/>
       <c r="J12" s="17" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="K12" s="23"/>
       <c r="L12" s="23"/>
@@ -7493,23 +7507,23 @@
     <row r="13" spans="1:15">
       <c r="A13" s="34"/>
       <c r="B13" s="17" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="C13" s="54"/>
       <c r="D13" s="52" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E13" s="55"/>
       <c r="F13" s="17" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="G13" s="55"/>
       <c r="H13" s="17" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="I13" s="55"/>
       <c r="J13" s="17" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="K13" s="23"/>
       <c r="L13" s="23"/>
@@ -7520,7 +7534,7 @@
     <row r="14" spans="1:15" ht="36" customHeight="1">
       <c r="A14" s="34"/>
       <c r="B14" s="52" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C14" s="73"/>
       <c r="D14" s="52" t="s">
@@ -7536,7 +7550,7 @@
       </c>
       <c r="I14" s="55"/>
       <c r="J14" s="146" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="K14" s="147"/>
       <c r="L14" s="147"/>
@@ -7581,7 +7595,7 @@
     <row r="17" spans="1:15">
       <c r="A17" s="34"/>
       <c r="B17" s="41" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="C17" s="41"/>
       <c r="D17" s="41"/>
@@ -7627,7 +7641,7 @@
     <row r="19" spans="1:15">
       <c r="A19" s="34"/>
       <c r="B19" s="52" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="C19" s="55"/>
       <c r="D19" s="52" t="s">
@@ -7654,7 +7668,7 @@
     <row r="20" spans="1:15">
       <c r="A20" s="34"/>
       <c r="B20" s="52" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C20" s="55"/>
       <c r="D20" s="52" t="s">
@@ -7666,7 +7680,7 @@
       </c>
       <c r="G20" s="55"/>
       <c r="H20" s="52" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="I20" s="55"/>
       <c r="J20" s="52" t="s">
@@ -7681,7 +7695,7 @@
     <row r="21" spans="1:15" ht="36" customHeight="1">
       <c r="A21" s="34"/>
       <c r="B21" s="52" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="C21" s="55"/>
       <c r="D21" s="52" t="s">
@@ -7697,7 +7711,7 @@
       </c>
       <c r="I21" s="55"/>
       <c r="J21" s="52" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="K21" s="23"/>
       <c r="L21" s="53"/>
@@ -7708,11 +7722,11 @@
     <row r="22" spans="1:15" ht="18" customHeight="1">
       <c r="A22" s="43"/>
       <c r="B22" s="52" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="C22" s="55"/>
       <c r="D22" s="52" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E22" s="55"/>
       <c r="F22" s="52">
@@ -7720,7 +7734,7 @@
       </c>
       <c r="G22" s="55"/>
       <c r="H22" s="52" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="I22" s="23"/>
       <c r="J22" s="75"/>
@@ -7733,7 +7747,7 @@
     <row r="23" spans="1:15" ht="36" customHeight="1">
       <c r="A23" s="8"/>
       <c r="B23" s="67" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="C23" s="55"/>
       <c r="D23" s="52" t="s">
@@ -7749,7 +7763,7 @@
       </c>
       <c r="I23" s="23"/>
       <c r="J23" s="151" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="K23" s="152"/>
       <c r="L23" s="152"/>
@@ -7760,23 +7774,23 @@
     <row r="24" spans="1:15">
       <c r="A24" s="8"/>
       <c r="B24" s="17" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="C24" s="55"/>
       <c r="D24" s="52" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E24" s="55"/>
       <c r="F24" s="17" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="G24" s="55"/>
       <c r="H24" s="17" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="I24" s="55"/>
       <c r="J24" s="17" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="K24" s="23"/>
       <c r="L24" s="23"/>
@@ -7787,23 +7801,23 @@
     <row r="25" spans="1:15" ht="18" customHeight="1">
       <c r="A25" s="8"/>
       <c r="B25" s="17" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="C25" s="54"/>
       <c r="D25" s="52" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="E25" s="55"/>
       <c r="F25" s="17" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="G25" s="55"/>
       <c r="H25" s="17" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="I25" s="55"/>
       <c r="J25" s="17" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="K25" s="23"/>
       <c r="L25" s="23"/>
@@ -7814,7 +7828,7 @@
     <row r="26" spans="1:15" ht="36" customHeight="1">
       <c r="A26" s="8"/>
       <c r="B26" s="52" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="C26" s="73"/>
       <c r="D26" s="52" t="s">
@@ -7830,7 +7844,7 @@
       </c>
       <c r="I26" s="55"/>
       <c r="J26" s="146" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="K26" s="147"/>
       <c r="L26" s="147"/>
@@ -7999,23 +8013,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="20">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="87" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="97"/>
-      <c r="C1" s="135" t="s">
+      <c r="B1" s="88"/>
+      <c r="C1" s="91" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="136"/>
-      <c r="E1" s="137" t="s">
+      <c r="D1" s="92"/>
+      <c r="E1" s="93" t="s">
         <v>47</v>
       </c>
-      <c r="F1" s="138"/>
-      <c r="G1" s="138"/>
-      <c r="H1" s="138"/>
-      <c r="I1" s="138"/>
-      <c r="J1" s="138"/>
-      <c r="K1" s="139"/>
+      <c r="F1" s="94"/>
+      <c r="G1" s="94"/>
+      <c r="H1" s="94"/>
+      <c r="I1" s="94"/>
+      <c r="J1" s="94"/>
+      <c r="K1" s="95"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
@@ -8028,17 +8042,17 @@
       <c r="O1" s="38"/>
     </row>
     <row r="2" spans="1:16" ht="20">
-      <c r="A2" s="98"/>
-      <c r="B2" s="100"/>
-      <c r="C2" s="135"/>
-      <c r="D2" s="136"/>
-      <c r="E2" s="137"/>
-      <c r="F2" s="138"/>
-      <c r="G2" s="138"/>
-      <c r="H2" s="138"/>
-      <c r="I2" s="138"/>
-      <c r="J2" s="138"/>
-      <c r="K2" s="139"/>
+      <c r="A2" s="89"/>
+      <c r="B2" s="90"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="92"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="94"/>
+      <c r="G2" s="94"/>
+      <c r="H2" s="94"/>
+      <c r="I2" s="94"/>
+      <c r="J2" s="94"/>
+      <c r="K2" s="95"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
@@ -8113,21 +8127,21 @@
         <v>1</v>
       </c>
       <c r="C6" s="75" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="D6" s="77"/>
       <c r="E6" s="78"/>
       <c r="F6" s="77"/>
       <c r="G6" s="76"/>
       <c r="H6" s="75" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="I6" s="78"/>
       <c r="J6" s="77"/>
       <c r="K6" s="77"/>
       <c r="L6" s="79"/>
       <c r="M6" s="151" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="N6" s="152"/>
       <c r="O6" s="153"/>
@@ -8139,21 +8153,21 @@
         <v>2</v>
       </c>
       <c r="C7" s="75" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="D7" s="77"/>
       <c r="E7" s="78"/>
       <c r="F7" s="77"/>
       <c r="G7" s="76"/>
       <c r="H7" s="75" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="I7" s="78"/>
       <c r="J7" s="77"/>
       <c r="K7" s="77"/>
       <c r="L7" s="79"/>
       <c r="M7" s="157" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="N7" s="158"/>
       <c r="O7" s="159"/>

--- a/要件定義書（カレンダーアプリ）.xlsx
+++ b/要件定義書（カレンダーアプリ）.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\my_application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5CAA7D6-B3A2-4FCC-B7C3-F6BA00242A93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F96DD44A-7C7D-4580-820D-F2180240CAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="4" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="5" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="184">
   <si>
     <t>要件定義</t>
   </si>
@@ -239,22 +239,6 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>・更新ボタンより変更・登録が可能</t>
-    <rPh sb="1" eb="3">
-      <t>コウシン</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ヘンコウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>カノウ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
     <t>氏名</t>
     <rPh sb="0" eb="2">
       <t>シメイ</t>
@@ -305,13 +289,6 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>タスクの登録</t>
-    <rPh sb="4" eb="6">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
     <t>タスクのリマインド機能</t>
     <rPh sb="9" eb="11">
       <t>キノウ</t>
@@ -343,20 +320,6 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>タスク登録</t>
-    <rPh sb="3" eb="5">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>タスク更新</t>
-    <rPh sb="3" eb="5">
-      <t>コウシン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
     <t>社員情報の登録</t>
     <rPh sb="0" eb="2">
       <t>シャイン</t>
@@ -400,127 +363,6 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>■タスク登録</t>
-    <rPh sb="4" eb="6">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>■タスク更新</t>
-    <rPh sb="4" eb="6">
-      <t>コウシン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>■タスクのTOPページ表示</t>
-    <rPh sb="11" eb="13">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>タスクの状況を更新</t>
-    <rPh sb="4" eb="6">
-      <t>ジョウキョウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>コウシン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・一般社員は自身のタスクのみ閲覧可能
-</t>
-    <rPh sb="1" eb="3">
-      <t>イッパン</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>シャイン</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ジシン</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>エツラン</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>カノウ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>・管理者（上長）は全社員のタスクが閲覧可能</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>タスクの検索・閲覧</t>
-    <rPh sb="4" eb="6">
-      <t>ケンサク</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>エツラン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>TOPページへのタスク表示</t>
-    <rPh sb="11" eb="13">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <r>
-      <t>自身のタスクの中で、</t>
-    </r>
-    <r>
-      <rPr>
-        <u val="double"/>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>当日・翌日が期限のものを</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="游ゴシック"/>
-        <family val="3"/>
-        <charset val="128"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>TOPページへ表示</t>
-    </r>
-    <rPh sb="0" eb="2">
-      <t>ジシン</t>
-    </rPh>
-    <rPh sb="7" eb="8">
-      <t>ナカ</t>
-    </rPh>
-    <rPh sb="10" eb="12">
-      <t>トウジツ</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ヨクジツ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>ヒョウジ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>・自身のタスクの中で、当日・翌日が期限のものをTOPページへ表示</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
     <t>・社員情報（氏名・カナ・性別・メールアドレス・部署）の入力</t>
     <rPh sb="1" eb="3">
       <t>シャイン</t>
@@ -549,116 +391,6 @@
     </rPh>
     <rPh sb="28" eb="32">
       <t>ジドウハンエイ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>※登録者（社員ID）・登録日時・更新日時はDB登録時に自動反映</t>
-  </si>
-  <si>
-    <t>■タスクの検索・閲覧</t>
-    <rPh sb="5" eb="7">
-      <t>ケンサク</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>エツラン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>・タスク情報（タスク名・タスク詳細・優先度（★、★★、★★★）・期限・ステータス（未着手、対応中、確認中、完了、保留）を登録　</t>
-    <rPh sb="4" eb="6">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>ショウサイ</t>
-    </rPh>
-    <rPh sb="18" eb="21">
-      <t>ユウセンド</t>
-    </rPh>
-    <rPh sb="41" eb="44">
-      <t>ミチャクシュ</t>
-    </rPh>
-    <rPh sb="45" eb="48">
-      <t>タイオウチュウ</t>
-    </rPh>
-    <rPh sb="49" eb="52">
-      <t>カクニンチュウ</t>
-    </rPh>
-    <rPh sb="56" eb="58">
-      <t>ホリュウ</t>
-    </rPh>
-    <rPh sb="60" eb="62">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>・タスクの状況（期限・優先度・ステータス・完了日）を更新</t>
-    <rPh sb="5" eb="7">
-      <t>ジョウキョウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="11" eb="14">
-      <t>ユウセンド</t>
-    </rPh>
-    <rPh sb="21" eb="24">
-      <t>カンリョウビ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>コウシン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>・タスクの検索（名前・タスク名・優先度・期限（当日、翌日、今週中）、ステータス）できるように</t>
-    <rPh sb="5" eb="7">
-      <t>ケンサク</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ナマエ</t>
-    </rPh>
-    <rPh sb="14" eb="15">
-      <t>メイ</t>
-    </rPh>
-    <rPh sb="16" eb="19">
-      <t>ユウセンド</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>キゲン</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>トウジツ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>ヨクジツ</t>
-    </rPh>
-    <rPh sb="29" eb="32">
-      <t>コンシュウチュウ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>※管理者での検索画面のみ「名前」の入力欄を作成するか。</t>
-    <rPh sb="1" eb="4">
-      <t>カンリシャ</t>
-    </rPh>
-    <rPh sb="6" eb="10">
-      <t>ケンサクガメン</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>ナマエ</t>
-    </rPh>
-    <rPh sb="17" eb="20">
-      <t>ニュウリョクラン</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>サクセイ</t>
     </rPh>
     <phoneticPr fontId="13"/>
   </si>
@@ -1356,6 +1088,20 @@
   </si>
   <si>
     <t>また、時には立て込んでいる時間帯等は外して接点をつくることで、お互いに業務の円滑化を図る。</t>
+  </si>
+  <si>
+    <t>スケジュールの登録</t>
+    <rPh sb="7" eb="9">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>スケジュール登録</t>
+    <rPh sb="6" eb="8">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
   </si>
   <si>
     <t>タスク・スケジュール登録</t>
@@ -1646,6 +1392,131 @@
     </rPh>
     <phoneticPr fontId="13"/>
   </si>
+  <si>
+    <t>スケジュール更新</t>
+    <rPh sb="6" eb="8">
+      <t>コウシン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>カレンダー閲覧</t>
+    <rPh sb="5" eb="7">
+      <t>エツラン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>スケジュールの変更</t>
+    <rPh sb="7" eb="9">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>カレンダーの閲覧（ほかの人のも可）</t>
+    <rPh sb="6" eb="8">
+      <t>エツラン</t>
+    </rPh>
+    <rPh sb="12" eb="13">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="15" eb="16">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>■スケジュール登録</t>
+    <rPh sb="7" eb="9">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>■スケジュール変更</t>
+    <rPh sb="7" eb="9">
+      <t>ヘンコウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・スケジュール（タイトル・時間・内容詳細・登録者）を登録　</t>
+    <rPh sb="13" eb="15">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>トウロクシャ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>※更新日時はDB登録時に自動反映</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>※登録者（社員ID）・登録日時はDB登録時に自動反映</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・登録済みのスケジュールより変更・加筆可能</t>
+    <rPh sb="1" eb="4">
+      <t>トウロクズ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>カヒツ</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>カノウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>■カレンダー閲覧</t>
+    <rPh sb="6" eb="8">
+      <t>エツラン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・スケジュールを時系列で表示</t>
+    <rPh sb="8" eb="11">
+      <t>ジケイレツ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヒョウジ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・ほかの人のスケジュールも検索・閲覧可能
+</t>
+    <rPh sb="4" eb="5">
+      <t>ヒト</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ケンサク</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>エツラン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>カノウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
 </sst>
 </file>
 
@@ -1654,7 +1525,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1764,14 +1635,6 @@
       <sz val="10"/>
       <name val="Yu Gothic"/>
       <charset val="128"/>
-    </font>
-    <font>
-      <u val="double"/>
-      <sz val="10"/>
-      <name val="游ゴシック"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
@@ -2379,7 +2242,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -3031,7 +2894,7 @@
       <c r="B6" s="105"/>
       <c r="C6" s="103"/>
       <c r="D6" s="106" t="s">
-        <v>170</v>
+        <v>150</v>
       </c>
       <c r="E6" s="106"/>
       <c r="F6" s="106"/>
@@ -3383,7 +3246,7 @@
         <v>2</v>
       </c>
       <c r="Q1" s="132" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="R1" s="133"/>
     </row>
@@ -4112,7 +3975,7 @@
         <v>2</v>
       </c>
       <c r="N1" s="22" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="O1" s="25" t="s">
         <v>3</v>
@@ -4205,7 +4068,7 @@
         <v>18</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="C6" s="30"/>
       <c r="D6" s="30"/>
@@ -4213,10 +4076,10 @@
       <c r="F6" s="30"/>
       <c r="G6" s="30"/>
       <c r="I6" s="35" t="s">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="J6" s="30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="K6" s="30"/>
       <c r="L6" s="30"/>
@@ -4226,10 +4089,10 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="81" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="C7" s="30"/>
       <c r="D7" s="30"/>
@@ -4237,10 +4100,10 @@
       <c r="F7" s="30"/>
       <c r="G7" s="30"/>
       <c r="I7" s="81" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="J7" s="30" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="K7" s="30"/>
       <c r="L7" s="30"/>
@@ -4250,10 +4113,10 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="81" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>145</v>
+        <v>125</v>
       </c>
       <c r="C8" s="34"/>
       <c r="D8" s="34"/>
@@ -4261,10 +4124,10 @@
       <c r="F8" s="34"/>
       <c r="G8" s="34"/>
       <c r="I8" s="81" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="J8" s="34" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="K8" s="34"/>
       <c r="L8" s="34"/>
@@ -4274,10 +4137,10 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="81" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="C9" s="30"/>
       <c r="D9" s="30"/>
@@ -4285,10 +4148,10 @@
       <c r="F9" s="30"/>
       <c r="G9" s="30"/>
       <c r="I9" s="81" t="s">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="K9" s="30"/>
       <c r="L9" s="30"/>
@@ -4298,10 +4161,10 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="81" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="C10" s="30"/>
       <c r="D10" s="30"/>
@@ -4318,7 +4181,7 @@
         <v>1.5</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>153</v>
+        <v>133</v>
       </c>
       <c r="C11" s="30"/>
       <c r="D11" s="30"/>
@@ -4326,7 +4189,7 @@
       <c r="F11" s="30"/>
       <c r="G11" s="30"/>
       <c r="I11" s="35" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="J11" s="30"/>
       <c r="K11" s="30"/>
@@ -4344,10 +4207,10 @@
       <c r="F12" s="30"/>
       <c r="G12" s="30"/>
       <c r="I12" s="82" t="s">
-        <v>154</v>
+        <v>134</v>
       </c>
       <c r="J12" s="30" t="s">
-        <v>155</v>
+        <v>135</v>
       </c>
       <c r="K12" s="30"/>
       <c r="L12" s="30"/>
@@ -4360,7 +4223,7 @@
         <v>22</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>156</v>
+        <v>136</v>
       </c>
       <c r="C13" s="30"/>
       <c r="D13" s="30"/>
@@ -4369,7 +4232,7 @@
       <c r="G13" s="30"/>
       <c r="I13" s="35"/>
       <c r="J13" s="30" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="K13" s="30"/>
       <c r="L13" s="30"/>
@@ -4379,10 +4242,10 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="82" t="s">
-        <v>158</v>
+        <v>138</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="C14" s="30"/>
       <c r="D14" s="30"/>
@@ -4390,7 +4253,7 @@
       <c r="F14" s="30"/>
       <c r="G14" s="30"/>
       <c r="J14" s="30" t="s">
-        <v>169</v>
+        <v>149</v>
       </c>
       <c r="K14" s="30"/>
       <c r="L14" s="30"/>
@@ -4418,7 +4281,7 @@
         <v>23</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="C16" s="30"/>
       <c r="D16" s="30"/>
@@ -4427,7 +4290,7 @@
       <c r="G16" s="30"/>
       <c r="H16" s="7"/>
       <c r="I16" s="16" t="s">
-        <v>157</v>
+        <v>137</v>
       </c>
       <c r="J16" s="30"/>
       <c r="K16" s="30"/>
@@ -4438,10 +4301,10 @@
     </row>
     <row r="17" spans="1:15" ht="26.5">
       <c r="A17" s="82" t="s">
-        <v>163</v>
+        <v>143</v>
       </c>
       <c r="B17" s="30" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="C17" s="30"/>
       <c r="D17" s="30"/>
@@ -4450,10 +4313,10 @@
       <c r="G17" s="30"/>
       <c r="H17" s="7"/>
       <c r="I17" s="82" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="J17" s="30" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="K17" s="36"/>
       <c r="L17" s="36"/>
@@ -4463,10 +4326,10 @@
     </row>
     <row r="18" spans="1:15" ht="26.5">
       <c r="A18" s="82" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="C18" s="34"/>
       <c r="D18" s="34"/>
@@ -4703,7 +4566,7 @@
     <row r="5" spans="1:18" ht="18" customHeight="1">
       <c r="A5" s="8"/>
       <c r="B5" s="96" t="s">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="C5" s="96"/>
       <c r="D5" s="96"/>
@@ -4722,7 +4585,7 @@
     <row r="6" spans="1:18">
       <c r="A6" s="34"/>
       <c r="B6" s="34" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="C6" s="34"/>
       <c r="D6" s="34"/>
@@ -4777,7 +4640,7 @@
     <row r="9" spans="1:18" ht="18" customHeight="1">
       <c r="A9" s="34"/>
       <c r="B9" s="85" t="s">
-        <v>173</v>
+        <v>153</v>
       </c>
       <c r="C9" s="85"/>
       <c r="D9" s="85"/>
@@ -4796,7 +4659,7 @@
     <row r="10" spans="1:18">
       <c r="A10" s="34"/>
       <c r="B10" s="85" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="C10" s="85"/>
       <c r="D10" s="85"/>
@@ -4815,7 +4678,7 @@
     <row r="11" spans="1:18" ht="18" customHeight="1">
       <c r="A11" s="34"/>
       <c r="B11" s="85" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="C11" s="85"/>
       <c r="D11" s="85"/>
@@ -4834,7 +4697,7 @@
     <row r="12" spans="1:18" ht="18" customHeight="1">
       <c r="A12" s="34"/>
       <c r="B12" s="85" t="s">
-        <v>176</v>
+        <v>156</v>
       </c>
       <c r="C12" s="85"/>
       <c r="D12" s="85"/>
@@ -4914,7 +4777,7 @@
     <row r="16" spans="1:18" ht="18" customHeight="1">
       <c r="A16" s="34"/>
       <c r="B16" s="86" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C16" s="86"/>
       <c r="D16" s="86"/>
@@ -4933,7 +4796,7 @@
     <row r="17" spans="1:15" ht="18" customHeight="1">
       <c r="A17" s="34"/>
       <c r="B17" s="86" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="C17" s="86"/>
       <c r="D17" s="86"/>
@@ -4952,7 +4815,7 @@
     <row r="18" spans="1:15" ht="18" customHeight="1">
       <c r="A18" s="34"/>
       <c r="B18" s="86" t="s">
-        <v>178</v>
+        <v>160</v>
       </c>
       <c r="C18" s="86"/>
       <c r="D18" s="86"/>
@@ -4971,7 +4834,7 @@
     <row r="19" spans="1:15" ht="18" customHeight="1">
       <c r="A19" s="34"/>
       <c r="B19" s="86" t="s">
-        <v>179</v>
+        <v>161</v>
       </c>
       <c r="C19" s="86"/>
       <c r="D19" s="86"/>
@@ -5043,7 +4906,7 @@
     <row r="23" spans="1:15">
       <c r="A23" s="34"/>
       <c r="B23" s="41" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C23" s="42"/>
       <c r="D23" s="42"/>
@@ -5115,7 +4978,7 @@
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="44" t="s">
-        <v>180</v>
+        <v>162</v>
       </c>
       <c r="C27" s="45"/>
       <c r="D27" s="45"/>
@@ -5134,7 +4997,7 @@
     <row r="28" spans="1:15">
       <c r="A28" s="8"/>
       <c r="B28" s="44" t="s">
-        <v>181</v>
+        <v>163</v>
       </c>
       <c r="C28" s="45"/>
       <c r="D28" s="45"/>
@@ -5153,7 +5016,7 @@
     <row r="29" spans="1:15">
       <c r="A29" s="8"/>
       <c r="B29" s="44" t="s">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="C29" s="45"/>
       <c r="D29" s="45"/>
@@ -5207,7 +5070,7 @@
     <row r="32" spans="1:15">
       <c r="A32" s="8"/>
       <c r="B32" s="46" t="s">
-        <v>183</v>
+        <v>165</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -5226,7 +5089,7 @@
     <row r="33" spans="1:15">
       <c r="A33" s="8"/>
       <c r="B33" s="46" t="s">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
@@ -5245,7 +5108,7 @@
     <row r="34" spans="1:15">
       <c r="A34" s="8"/>
       <c r="B34" s="46" t="s">
-        <v>185</v>
+        <v>167</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
@@ -5264,7 +5127,7 @@
     <row r="35" spans="1:15">
       <c r="A35" s="8"/>
       <c r="B35" s="46" t="s">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
@@ -5424,7 +5287,7 @@
       </c>
       <c r="C6" s="145"/>
       <c r="D6" s="74" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E6" s="49"/>
       <c r="F6" s="49"/>
@@ -5441,11 +5304,11 @@
     <row r="7" spans="1:15">
       <c r="A7" s="34"/>
       <c r="B7" s="142" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C7" s="143"/>
       <c r="D7" s="17" t="s">
-        <v>188</v>
+        <v>170</v>
       </c>
       <c r="E7" s="53"/>
       <c r="F7" s="53"/>
@@ -5466,7 +5329,7 @@
       </c>
       <c r="C8" s="143"/>
       <c r="D8" s="17" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
@@ -5923,7 +5786,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C8D2F9E-DCA9-4610-96AE-118D7871E7D7}">
-  <dimension ref="A1:O37"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="10" max="10" width="10.4140625" customWidth="1"/>
@@ -5955,7 +5818,9 @@
       <c r="M1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="149"/>
+      <c r="N1" s="149">
+        <v>46289</v>
+      </c>
       <c r="O1" s="149"/>
     </row>
     <row r="2" spans="1:15" ht="20">
@@ -6058,12 +5923,12 @@
     <row r="7" spans="1:15">
       <c r="A7" s="34"/>
       <c r="B7" s="52" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C7" s="53"/>
       <c r="D7" s="53"/>
       <c r="E7" s="67" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F7" s="23"/>
       <c r="G7" s="53"/>
@@ -6071,7 +5936,7 @@
       <c r="I7" s="53"/>
       <c r="J7" s="54"/>
       <c r="K7" s="68" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="L7" s="54"/>
       <c r="M7" s="30"/>
@@ -6081,12 +5946,12 @@
     <row r="8" spans="1:15">
       <c r="A8" s="34"/>
       <c r="B8" s="52" t="s">
-        <v>76</v>
+        <v>158</v>
       </c>
       <c r="C8" s="53"/>
       <c r="D8" s="53"/>
       <c r="E8" s="67" t="s">
-        <v>71</v>
+        <v>157</v>
       </c>
       <c r="F8" s="23"/>
       <c r="G8" s="53"/>
@@ -6094,7 +5959,7 @@
       <c r="I8" s="53"/>
       <c r="J8" s="54"/>
       <c r="K8" s="68" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="L8" s="54"/>
       <c r="M8" s="30"/>
@@ -6104,12 +5969,12 @@
     <row r="9" spans="1:15">
       <c r="A9" s="34"/>
       <c r="B9" s="52" t="s">
-        <v>77</v>
+        <v>171</v>
       </c>
       <c r="C9" s="53"/>
       <c r="D9" s="53"/>
       <c r="E9" s="67" t="s">
-        <v>85</v>
+        <v>173</v>
       </c>
       <c r="F9" s="23"/>
       <c r="G9" s="53"/>
@@ -6117,7 +5982,7 @@
       <c r="I9" s="53"/>
       <c r="J9" s="54"/>
       <c r="K9" s="68" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="L9" s="54"/>
       <c r="M9" s="30"/>
@@ -6126,13 +5991,13 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="34"/>
-      <c r="B10" s="17" t="s">
-        <v>88</v>
+      <c r="B10" s="52" t="s">
+        <v>172</v>
       </c>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
       <c r="E10" s="146" t="s">
-        <v>88</v>
+        <v>174</v>
       </c>
       <c r="F10" s="147"/>
       <c r="G10" s="147"/>
@@ -6140,7 +6005,7 @@
       <c r="I10" s="147"/>
       <c r="J10" s="148"/>
       <c r="K10" s="68" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="L10" s="54"/>
       <c r="M10" s="30"/>
@@ -6149,64 +6014,62 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="34"/>
-      <c r="B11" s="146" t="s">
-        <v>89</v>
-      </c>
-      <c r="C11" s="147"/>
-      <c r="D11" s="148"/>
-      <c r="E11" s="67" t="s">
-        <v>90</v>
-      </c>
-      <c r="F11" s="23"/>
-      <c r="G11" s="53"/>
-      <c r="H11" s="53"/>
-      <c r="I11" s="53"/>
-      <c r="J11" s="54"/>
-      <c r="K11" s="68" t="s">
-        <v>79</v>
-      </c>
-      <c r="L11" s="54"/>
-      <c r="M11" s="30"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
       <c r="N11" s="34"/>
       <c r="O11" s="7"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="34"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="8"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="34"/>
-      <c r="O12" s="7"/>
+      <c r="B12" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C12" s="34"/>
+      <c r="D12" s="34"/>
     </row>
     <row r="13" spans="1:15">
       <c r="A13" s="34"/>
-      <c r="B13" s="34" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" s="34"/>
-      <c r="D13" s="34"/>
+      <c r="B13" s="41" t="s">
+        <v>77</v>
+      </c>
+      <c r="C13" s="41"/>
+      <c r="D13" s="41"/>
+      <c r="E13" s="41"/>
+      <c r="F13" s="41"/>
+      <c r="G13" s="41"/>
+      <c r="H13" s="41"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="41"/>
+      <c r="K13" s="41"/>
+      <c r="L13" s="41"/>
+      <c r="M13" s="41"/>
+      <c r="N13" s="41"/>
+      <c r="O13" s="7"/>
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="34"/>
-      <c r="B14" s="41" t="s">
-        <v>81</v>
-      </c>
-      <c r="C14" s="41"/>
-      <c r="D14" s="41"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="41"/>
-      <c r="G14" s="41"/>
-      <c r="H14" s="41"/>
-      <c r="I14" s="41"/>
+      <c r="B14" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C14" s="56"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
+      <c r="F14" s="56"/>
+      <c r="G14" s="56"/>
+      <c r="H14" s="56" t="s">
+        <v>79</v>
+      </c>
+      <c r="I14" s="56"/>
       <c r="J14" s="41"/>
       <c r="K14" s="41"/>
       <c r="L14" s="41"/>
@@ -6217,16 +6080,14 @@
     <row r="15" spans="1:15">
       <c r="A15" s="34"/>
       <c r="B15" s="7" t="s">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c r="C15" s="56"/>
       <c r="D15" s="56"/>
       <c r="E15" s="56"/>
       <c r="F15" s="56"/>
       <c r="G15" s="56"/>
-      <c r="H15" s="56" t="s">
-        <v>93</v>
-      </c>
+      <c r="H15" s="56"/>
       <c r="I15" s="56"/>
       <c r="J15" s="41"/>
       <c r="K15" s="41"/>
@@ -6237,9 +6098,7 @@
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="34"/>
-      <c r="B16" s="7" t="s">
-        <v>61</v>
-      </c>
+      <c r="B16" s="7"/>
       <c r="C16" s="56"/>
       <c r="D16" s="56"/>
       <c r="E16" s="56"/>
@@ -6256,7 +6115,9 @@
     </row>
     <row r="17" spans="1:15">
       <c r="A17" s="34"/>
-      <c r="B17" s="7"/>
+      <c r="B17" s="7" t="s">
+        <v>175</v>
+      </c>
       <c r="C17" s="56"/>
       <c r="D17" s="56"/>
       <c r="E17" s="56"/>
@@ -6273,15 +6134,15 @@
     </row>
     <row r="18" spans="1:15">
       <c r="A18" s="34"/>
-      <c r="B18" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="C18" s="56"/>
-      <c r="D18" s="56"/>
-      <c r="E18" s="56"/>
-      <c r="F18" s="56"/>
-      <c r="G18" s="56"/>
-      <c r="H18" s="56"/>
+      <c r="B18" s="56" t="s">
+        <v>177</v>
+      </c>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
       <c r="I18" s="56"/>
       <c r="J18" s="41"/>
       <c r="K18" s="41"/>
@@ -6292,8 +6153,8 @@
     </row>
     <row r="19" spans="1:15">
       <c r="A19" s="34"/>
-      <c r="B19" s="56" t="s">
-        <v>96</v>
+      <c r="B19" s="7" t="s">
+        <v>179</v>
       </c>
       <c r="C19" s="41"/>
       <c r="D19" s="41"/>
@@ -6301,7 +6162,7 @@
       <c r="F19" s="41"/>
       <c r="G19" s="41"/>
       <c r="H19" s="41"/>
-      <c r="I19" s="56"/>
+      <c r="I19" s="41"/>
       <c r="J19" s="41"/>
       <c r="K19" s="41"/>
       <c r="L19" s="41"/>
@@ -6311,9 +6172,7 @@
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="34"/>
-      <c r="B20" s="7" t="s">
-        <v>94</v>
-      </c>
+      <c r="B20" s="7"/>
       <c r="C20" s="41"/>
       <c r="D20" s="41"/>
       <c r="E20" s="41"/>
@@ -6330,7 +6189,9 @@
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="34"/>
-      <c r="B21" s="7"/>
+      <c r="B21" s="7" t="s">
+        <v>176</v>
+      </c>
       <c r="C21" s="41"/>
       <c r="D21" s="41"/>
       <c r="E21" s="41"/>
@@ -6345,69 +6206,69 @@
       <c r="N21" s="41"/>
       <c r="O21" s="7"/>
     </row>
-    <row r="22" spans="1:15">
-      <c r="A22" s="34"/>
+    <row r="22" spans="1:15" ht="18" customHeight="1">
+      <c r="A22" s="43"/>
       <c r="B22" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C22" s="41"/>
-      <c r="D22" s="41"/>
-      <c r="E22" s="41"/>
-      <c r="F22" s="41"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="41"/>
-      <c r="I22" s="41"/>
-      <c r="J22" s="41"/>
-      <c r="K22" s="41"/>
-      <c r="L22" s="41"/>
-      <c r="M22" s="41"/>
-      <c r="N22" s="41"/>
+        <v>180</v>
+      </c>
+      <c r="C22" s="43"/>
+      <c r="D22" s="43"/>
+      <c r="E22" s="43"/>
+      <c r="F22" s="43"/>
+      <c r="G22" s="43"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="43"/>
+      <c r="M22" s="43"/>
+      <c r="N22" s="43"/>
       <c r="O22" s="7"/>
     </row>
     <row r="23" spans="1:15" ht="18" customHeight="1">
-      <c r="A23" s="43"/>
-      <c r="B23" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="C23" s="43"/>
-      <c r="D23" s="43"/>
-      <c r="E23" s="43"/>
-      <c r="F23" s="43"/>
-      <c r="G23" s="43"/>
-      <c r="H23" s="43"/>
-      <c r="I23" s="43"/>
-      <c r="J23" s="43"/>
-      <c r="K23" s="43"/>
-      <c r="L23" s="43"/>
-      <c r="M23" s="43"/>
-      <c r="N23" s="43"/>
+      <c r="A23" s="8"/>
+      <c r="B23" s="56" t="s">
+        <v>178</v>
+      </c>
+      <c r="C23" s="8"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="8"/>
+      <c r="F23" s="8"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="8"/>
+      <c r="I23" s="8"/>
+      <c r="J23" s="8"/>
+      <c r="K23" s="8"/>
+      <c r="L23" s="8"/>
+      <c r="M23" s="8"/>
+      <c r="N23" s="8"/>
       <c r="O23" s="7"/>
     </row>
-    <row r="24" spans="1:15" ht="18" customHeight="1">
+    <row r="24" spans="1:15">
       <c r="A24" s="8"/>
-      <c r="B24" s="56" t="s">
-        <v>97</v>
-      </c>
-      <c r="C24" s="8"/>
-      <c r="D24" s="8"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
-      <c r="H24" s="8"/>
-      <c r="I24" s="8"/>
-      <c r="J24" s="8"/>
-      <c r="K24" s="8"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
+      <c r="B24" s="56"/>
+      <c r="C24" s="45"/>
+      <c r="D24" s="45"/>
+      <c r="E24" s="45"/>
+      <c r="G24" s="45"/>
+      <c r="H24" s="45"/>
+      <c r="I24" s="45"/>
+      <c r="J24" s="45"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="45"/>
+      <c r="M24" s="45"/>
+      <c r="N24" s="45"/>
       <c r="O24" s="7"/>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
-      <c r="B25" s="56"/>
+      <c r="B25" s="41" t="s">
+        <v>181</v>
+      </c>
       <c r="C25" s="45"/>
       <c r="D25" s="45"/>
       <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
       <c r="G25" s="45"/>
       <c r="H25" s="45"/>
       <c r="I25" s="45"/>
@@ -6420,8 +6281,8 @@
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="8"/>
-      <c r="B26" s="41" t="s">
-        <v>95</v>
+      <c r="B26" s="56" t="s">
+        <v>182</v>
       </c>
       <c r="C26" s="45"/>
       <c r="D26" s="45"/>
@@ -6440,7 +6301,7 @@
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="56" t="s">
-        <v>98</v>
+        <v>183</v>
       </c>
       <c r="C27" s="45"/>
       <c r="D27" s="45"/>
@@ -6458,9 +6319,7 @@
     </row>
     <row r="28" spans="1:15">
       <c r="A28" s="8"/>
-      <c r="B28" s="56" t="s">
-        <v>86</v>
-      </c>
+      <c r="B28" s="56"/>
       <c r="C28" s="45"/>
       <c r="D28" s="45"/>
       <c r="E28" s="45"/>
@@ -6477,169 +6336,75 @@
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="8"/>
-      <c r="B29" s="56" t="s">
-        <v>87</v>
-      </c>
-      <c r="C29" s="45"/>
-      <c r="D29" s="45"/>
-      <c r="E29" s="45"/>
-      <c r="F29" s="45"/>
-      <c r="G29" s="45"/>
-      <c r="H29" s="45"/>
-      <c r="I29" s="45"/>
-      <c r="J29" s="45"/>
-      <c r="K29" s="45"/>
-      <c r="L29" s="45"/>
-      <c r="M29" s="45"/>
-      <c r="N29" s="45"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
+      <c r="N29" s="8"/>
       <c r="O29" s="7"/>
     </row>
     <row r="30" spans="1:15">
       <c r="A30" s="8"/>
-      <c r="B30" s="56" t="s">
-        <v>99</v>
-      </c>
-      <c r="C30" s="45"/>
-      <c r="D30" s="45"/>
-      <c r="E30" s="45"/>
-      <c r="F30" s="45"/>
-      <c r="G30" s="45"/>
-      <c r="H30" s="45"/>
-      <c r="I30" s="45"/>
-      <c r="J30" s="45"/>
-      <c r="K30" s="45"/>
-      <c r="L30" s="45"/>
-      <c r="M30" s="45"/>
-      <c r="N30" s="45"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8"/>
       <c r="O30" s="7"/>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" s="8"/>
-      <c r="B31" s="56"/>
-      <c r="C31" s="45"/>
-      <c r="D31" s="45"/>
-      <c r="E31" s="45"/>
-      <c r="F31" s="45"/>
-      <c r="G31" s="45"/>
-      <c r="H31" s="45"/>
-      <c r="I31" s="45"/>
-      <c r="J31" s="45"/>
-      <c r="K31" s="45"/>
-      <c r="L31" s="45"/>
-      <c r="M31" s="45"/>
-      <c r="N31" s="45"/>
+      <c r="B31" s="8"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="8"/>
+      <c r="E31" s="8"/>
+      <c r="F31" s="8"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="8"/>
+      <c r="I31" s="8"/>
+      <c r="J31" s="8"/>
+      <c r="K31" s="8"/>
+      <c r="L31" s="8"/>
+      <c r="M31" s="8"/>
+      <c r="N31" s="8"/>
       <c r="O31" s="7"/>
     </row>
     <row r="32" spans="1:15">
       <c r="A32" s="8"/>
-      <c r="B32" s="56" t="s">
-        <v>84</v>
-      </c>
-      <c r="C32" s="45"/>
-      <c r="D32" s="45"/>
-      <c r="E32" s="45"/>
-      <c r="F32" s="45"/>
-      <c r="G32" s="45"/>
-      <c r="H32" s="45"/>
-      <c r="I32" s="45"/>
-      <c r="J32" s="45"/>
-      <c r="K32" s="45"/>
-      <c r="L32" s="45"/>
-      <c r="M32" s="45"/>
-      <c r="N32" s="45"/>
+      <c r="B32" s="8"/>
+      <c r="C32" s="8"/>
+      <c r="D32" s="8"/>
+      <c r="E32" s="8"/>
+      <c r="F32" s="8"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+      <c r="J32" s="8"/>
+      <c r="K32" s="8"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="8"/>
+      <c r="N32" s="8"/>
       <c r="O32" s="7"/>
     </row>
-    <row r="33" spans="1:15">
-      <c r="A33" s="8"/>
-      <c r="B33" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="C33" s="8"/>
-      <c r="D33" s="8"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="8"/>
-      <c r="H33" s="8"/>
-      <c r="I33" s="8"/>
-      <c r="J33" s="8"/>
-      <c r="K33" s="8"/>
-      <c r="L33" s="8"/>
-      <c r="M33" s="8"/>
-      <c r="N33" s="8"/>
-      <c r="O33" s="7"/>
-    </row>
-    <row r="34" spans="1:15">
-      <c r="A34" s="8"/>
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="8"/>
-      <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="8"/>
-      <c r="M34" s="8"/>
-      <c r="N34" s="8"/>
-      <c r="O34" s="7"/>
-    </row>
-    <row r="35" spans="1:15">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="8"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="8"/>
-      <c r="J35" s="8"/>
-      <c r="K35" s="8"/>
-      <c r="L35" s="8"/>
-      <c r="M35" s="8"/>
-      <c r="N35" s="8"/>
-      <c r="O35" s="7"/>
-    </row>
-    <row r="36" spans="1:15">
-      <c r="A36" s="8"/>
-      <c r="B36" s="8"/>
-      <c r="C36" s="8"/>
-      <c r="D36" s="8"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="8"/>
-      <c r="H36" s="8"/>
-      <c r="I36" s="8"/>
-      <c r="J36" s="8"/>
-      <c r="K36" s="8"/>
-      <c r="L36" s="8"/>
-      <c r="M36" s="8"/>
-      <c r="N36" s="8"/>
-      <c r="O36" s="7"/>
-    </row>
-    <row r="37" spans="1:15">
-      <c r="A37" s="8"/>
-      <c r="B37" s="8"/>
-      <c r="C37" s="8"/>
-      <c r="D37" s="8"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="8"/>
-      <c r="H37" s="8"/>
-      <c r="I37" s="8"/>
-      <c r="J37" s="8"/>
-      <c r="K37" s="8"/>
-      <c r="L37" s="8"/>
-      <c r="M37" s="8"/>
-      <c r="N37" s="8"/>
-      <c r="O37" s="7"/>
-    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="7">
     <mergeCell ref="E10:J10"/>
-    <mergeCell ref="B11:D11"/>
     <mergeCell ref="A1:B2"/>
     <mergeCell ref="C1:D1"/>
     <mergeCell ref="N1:O1"/>
@@ -6682,7 +6447,7 @@
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -6749,7 +6514,7 @@
     <row r="5" spans="1:15">
       <c r="A5" s="8"/>
       <c r="B5" s="30" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="C5" s="30"/>
       <c r="D5" s="30"/>
@@ -6804,7 +6569,7 @@
     <row r="8" spans="1:15">
       <c r="A8" s="34"/>
       <c r="B8" s="34" t="s">
-        <v>127</v>
+        <v>107</v>
       </c>
       <c r="C8" s="34"/>
       <c r="D8" s="34"/>
@@ -6840,7 +6605,7 @@
     <row r="10" spans="1:15">
       <c r="A10" s="34"/>
       <c r="B10" s="7" t="s">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -6859,7 +6624,7 @@
     <row r="11" spans="1:15">
       <c r="A11" s="34"/>
       <c r="B11" s="41" t="s">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="C11" s="41"/>
       <c r="D11" s="41"/>
@@ -7224,7 +6989,7 @@
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -7272,7 +7037,7 @@
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="34" t="s">
-        <v>116</v>
+        <v>96</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -7318,11 +7083,11 @@
     <row r="6" spans="1:15">
       <c r="A6" s="8"/>
       <c r="B6" s="52" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="C6" s="60"/>
       <c r="D6" s="52" t="s">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="E6" s="55"/>
       <c r="F6" s="52">
@@ -7330,11 +7095,11 @@
       </c>
       <c r="G6" s="55"/>
       <c r="H6" s="52" t="s">
-        <v>109</v>
+        <v>89</v>
       </c>
       <c r="I6" s="55"/>
       <c r="J6" s="52" t="s">
-        <v>108</v>
+        <v>88</v>
       </c>
       <c r="K6" s="53"/>
       <c r="L6" s="61"/>
@@ -7345,11 +7110,11 @@
     <row r="7" spans="1:15">
       <c r="A7" s="34"/>
       <c r="B7" s="52" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C7" s="55"/>
       <c r="D7" s="52" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E7" s="55"/>
       <c r="F7" s="52">
@@ -7361,7 +7126,7 @@
       </c>
       <c r="I7" s="55"/>
       <c r="J7" s="52" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K7" s="53"/>
       <c r="L7" s="61"/>
@@ -7372,7 +7137,7 @@
     <row r="8" spans="1:15">
       <c r="A8" s="34"/>
       <c r="B8" s="52" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C8" s="55"/>
       <c r="D8" s="52" t="s">
@@ -7388,7 +7153,7 @@
       </c>
       <c r="I8" s="55"/>
       <c r="J8" s="52" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K8" s="23"/>
       <c r="L8" s="53"/>
@@ -7399,11 +7164,11 @@
     <row r="9" spans="1:15" ht="36" customHeight="1">
       <c r="A9" s="34"/>
       <c r="B9" s="52" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C9" s="55"/>
       <c r="D9" s="52" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E9" s="55"/>
       <c r="F9" s="52">
@@ -7415,7 +7180,7 @@
       </c>
       <c r="I9" s="55"/>
       <c r="J9" s="154" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="K9" s="155"/>
       <c r="L9" s="155"/>
@@ -7426,11 +7191,11 @@
     <row r="10" spans="1:15">
       <c r="A10" s="34"/>
       <c r="B10" s="52" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="C10" s="55"/>
       <c r="D10" s="52" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E10" s="55"/>
       <c r="F10" s="52">
@@ -7438,11 +7203,11 @@
       </c>
       <c r="G10" s="55"/>
       <c r="H10" s="52" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="I10" s="23"/>
       <c r="J10" s="75" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="K10" s="23"/>
       <c r="L10" s="53"/>
@@ -7453,11 +7218,11 @@
     <row r="11" spans="1:15" ht="54" customHeight="1">
       <c r="A11" s="34"/>
       <c r="B11" s="67" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="C11" s="55"/>
       <c r="D11" s="52" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E11" s="55"/>
       <c r="F11" s="17">
@@ -7469,7 +7234,7 @@
       </c>
       <c r="I11" s="23"/>
       <c r="J11" s="151" t="s">
-        <v>123</v>
+        <v>103</v>
       </c>
       <c r="K11" s="152"/>
       <c r="L11" s="152"/>
@@ -7480,23 +7245,23 @@
     <row r="12" spans="1:15">
       <c r="A12" s="34"/>
       <c r="B12" s="17" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="C12" s="55"/>
       <c r="D12" s="52" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="E12" s="55"/>
       <c r="F12" s="17" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="G12" s="55"/>
       <c r="H12" s="17" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="I12" s="55"/>
       <c r="J12" s="17" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="K12" s="23"/>
       <c r="L12" s="23"/>
@@ -7507,23 +7272,23 @@
     <row r="13" spans="1:15">
       <c r="A13" s="34"/>
       <c r="B13" s="17" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="C13" s="54"/>
       <c r="D13" s="52" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="E13" s="55"/>
       <c r="F13" s="17" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="G13" s="55"/>
       <c r="H13" s="17" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="I13" s="55"/>
       <c r="J13" s="17" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="K13" s="23"/>
       <c r="L13" s="23"/>
@@ -7534,11 +7299,11 @@
     <row r="14" spans="1:15" ht="36" customHeight="1">
       <c r="A14" s="34"/>
       <c r="B14" s="52" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="C14" s="73"/>
       <c r="D14" s="52" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E14" s="55"/>
       <c r="F14" s="17">
@@ -7550,7 +7315,7 @@
       </c>
       <c r="I14" s="55"/>
       <c r="J14" s="146" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="K14" s="147"/>
       <c r="L14" s="147"/>
@@ -7595,7 +7360,7 @@
     <row r="17" spans="1:15">
       <c r="A17" s="34"/>
       <c r="B17" s="41" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="C17" s="41"/>
       <c r="D17" s="41"/>
@@ -7641,11 +7406,11 @@
     <row r="19" spans="1:15">
       <c r="A19" s="34"/>
       <c r="B19" s="52" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="C19" s="55"/>
       <c r="D19" s="52" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E19" s="55"/>
       <c r="F19" s="52">
@@ -7657,7 +7422,7 @@
       </c>
       <c r="I19" s="55"/>
       <c r="J19" s="52" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K19" s="53"/>
       <c r="L19" s="61"/>
@@ -7668,7 +7433,7 @@
     <row r="20" spans="1:15">
       <c r="A20" s="34"/>
       <c r="B20" s="52" t="s">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="C20" s="55"/>
       <c r="D20" s="52" t="s">
@@ -7680,11 +7445,11 @@
       </c>
       <c r="G20" s="55"/>
       <c r="H20" s="52" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="I20" s="55"/>
       <c r="J20" s="52" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="K20" s="23"/>
       <c r="L20" s="53"/>
@@ -7695,11 +7460,11 @@
     <row r="21" spans="1:15" ht="36" customHeight="1">
       <c r="A21" s="34"/>
       <c r="B21" s="52" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="C21" s="55"/>
       <c r="D21" s="52" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E21" s="55"/>
       <c r="F21" s="52">
@@ -7711,7 +7476,7 @@
       </c>
       <c r="I21" s="55"/>
       <c r="J21" s="52" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="K21" s="23"/>
       <c r="L21" s="53"/>
@@ -7722,11 +7487,11 @@
     <row r="22" spans="1:15" ht="18" customHeight="1">
       <c r="A22" s="43"/>
       <c r="B22" s="52" t="s">
-        <v>122</v>
+        <v>102</v>
       </c>
       <c r="C22" s="55"/>
       <c r="D22" s="52" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="E22" s="55"/>
       <c r="F22" s="52">
@@ -7734,7 +7499,7 @@
       </c>
       <c r="G22" s="55"/>
       <c r="H22" s="52" t="s">
-        <v>102</v>
+        <v>82</v>
       </c>
       <c r="I22" s="23"/>
       <c r="J22" s="75"/>
@@ -7747,11 +7512,11 @@
     <row r="23" spans="1:15" ht="36" customHeight="1">
       <c r="A23" s="8"/>
       <c r="B23" s="67" t="s">
-        <v>125</v>
+        <v>105</v>
       </c>
       <c r="C23" s="55"/>
       <c r="D23" s="52" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E23" s="55"/>
       <c r="F23" s="17">
@@ -7763,7 +7528,7 @@
       </c>
       <c r="I23" s="23"/>
       <c r="J23" s="151" t="s">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="K23" s="152"/>
       <c r="L23" s="152"/>
@@ -7774,23 +7539,23 @@
     <row r="24" spans="1:15">
       <c r="A24" s="8"/>
       <c r="B24" s="17" t="s">
-        <v>104</v>
+        <v>84</v>
       </c>
       <c r="C24" s="55"/>
       <c r="D24" s="52" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="E24" s="55"/>
       <c r="F24" s="17" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="G24" s="55"/>
       <c r="H24" s="17" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="I24" s="55"/>
       <c r="J24" s="17" t="s">
-        <v>114</v>
+        <v>94</v>
       </c>
       <c r="K24" s="23"/>
       <c r="L24" s="23"/>
@@ -7801,23 +7566,23 @@
     <row r="25" spans="1:15" ht="18" customHeight="1">
       <c r="A25" s="8"/>
       <c r="B25" s="17" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="C25" s="54"/>
       <c r="D25" s="52" t="s">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="E25" s="55"/>
       <c r="F25" s="17" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="G25" s="55"/>
       <c r="H25" s="17" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="I25" s="55"/>
       <c r="J25" s="17" t="s">
-        <v>115</v>
+        <v>95</v>
       </c>
       <c r="K25" s="23"/>
       <c r="L25" s="23"/>
@@ -7828,11 +7593,11 @@
     <row r="26" spans="1:15" ht="36" customHeight="1">
       <c r="A26" s="8"/>
       <c r="B26" s="52" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="C26" s="73"/>
       <c r="D26" s="52" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E26" s="55"/>
       <c r="F26" s="17">
@@ -7844,7 +7609,7 @@
       </c>
       <c r="I26" s="55"/>
       <c r="J26" s="146" t="s">
-        <v>112</v>
+        <v>92</v>
       </c>
       <c r="K26" s="147"/>
       <c r="L26" s="147"/>
@@ -8034,7 +7799,7 @@
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -8127,21 +7892,21 @@
         <v>1</v>
       </c>
       <c r="C6" s="75" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="D6" s="77"/>
       <c r="E6" s="78"/>
       <c r="F6" s="77"/>
       <c r="G6" s="76"/>
       <c r="H6" s="75" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="I6" s="78"/>
       <c r="J6" s="77"/>
       <c r="K6" s="77"/>
       <c r="L6" s="79"/>
       <c r="M6" s="151" t="s">
-        <v>134</v>
+        <v>114</v>
       </c>
       <c r="N6" s="152"/>
       <c r="O6" s="153"/>
@@ -8153,21 +7918,21 @@
         <v>2</v>
       </c>
       <c r="C7" s="75" t="s">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="D7" s="77"/>
       <c r="E7" s="78"/>
       <c r="F7" s="77"/>
       <c r="G7" s="76"/>
       <c r="H7" s="75" t="s">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="I7" s="78"/>
       <c r="J7" s="77"/>
       <c r="K7" s="77"/>
       <c r="L7" s="79"/>
       <c r="M7" s="157" t="s">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="N7" s="158"/>
       <c r="O7" s="159"/>

--- a/要件定義書（カレンダーアプリ）.xlsx
+++ b/要件定義書（カレンダーアプリ）.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\my_application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F96DD44A-7C7D-4580-820D-F2180240CAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F12FF23-92AA-48C4-8C47-7A16D8A5CA10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="5" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="7" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="186">
   <si>
     <t>要件定義</t>
   </si>
@@ -524,13 +524,6 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>【タスク情報】</t>
-    <rPh sb="4" eb="6">
-      <t>ジョウホウ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
     <t>ラジオボタン
 男：0　女：1　両方：2</t>
     <rPh sb="7" eb="8">
@@ -545,34 +538,6 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>タスク名</t>
-    <rPh sb="3" eb="4">
-      <t>メイ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>タスク詳細</t>
-    <rPh sb="3" eb="5">
-      <t>ショウサイ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>優先度</t>
-    <rPh sb="0" eb="3">
-      <t>ユウセンド</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>期限</t>
-    <rPh sb="0" eb="2">
-      <t>キゲン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
     <t>「営業部」：１「総務部」：２「人事部」：３「経理部」：４「システム部」：５
 「マーケティング部」：６</t>
     <rPh sb="1" eb="3">
@@ -604,34 +569,6 @@
     </rPh>
     <rPh sb="46" eb="47">
       <t>ブ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>★：１、★★：２、★★★：３</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>ステータス</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>「未着手」：１「対応中」：２
-「確認中」：３「完了」：４「保留」：５</t>
-    <rPh sb="1" eb="4">
-      <t>ミチャクシュ</t>
-    </rPh>
-    <rPh sb="8" eb="11">
-      <t>タイオウチュウ</t>
-    </rPh>
-    <rPh sb="16" eb="19">
-      <t>カクニンチュウ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>カンリョウ</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>ホリュウ</t>
     </rPh>
     <phoneticPr fontId="13"/>
   </si>
@@ -1441,25 +1378,6 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>・スケジュール（タイトル・時間・内容詳細・登録者）を登録　</t>
-    <rPh sb="13" eb="15">
-      <t>ジカン</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ナイヨウ</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>ショウサイ</t>
-    </rPh>
-    <rPh sb="21" eb="24">
-      <t>トウロクシャ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>トウロク</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
     <t>※更新日時はDB登録時に自動反映</t>
     <phoneticPr fontId="13"/>
   </si>
@@ -1514,6 +1432,116 @@
     </rPh>
     <rPh sb="18" eb="20">
       <t>カノウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・他者からのスケジュール変更は不可</t>
+    <rPh sb="1" eb="3">
+      <t>タシャ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ヘンコウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>フカ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>【スケジュール情報】</t>
+    <rPh sb="7" eb="9">
+      <t>ジョウホウ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>タイトル</t>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>時間</t>
+    <rPh sb="0" eb="2">
+      <t>ジカン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>内容詳細</t>
+    <rPh sb="0" eb="4">
+      <t>ナイヨウショウサイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>登録者</t>
+    <rPh sb="0" eb="3">
+      <t>トウロクシャ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・スケジュール（タイトル・時間・内容詳細・登録者・登録日時）を登録　</t>
+    <rPh sb="13" eb="15">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ショウサイ</t>
+    </rPh>
+    <rPh sb="21" eb="24">
+      <t>トウロクシャ</t>
+    </rPh>
+    <rPh sb="25" eb="29">
+      <t>トウロクニチジ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>トウロク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>時間</t>
+    <rPh sb="0" eb="2">
+      <t>ジカン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>プルダウン（15分間隔）にて選択</t>
+    <rPh sb="8" eb="9">
+      <t>ブ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>カンカク</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>センタク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>自動入力（入力者（ログインIDにて識別））</t>
+    <rPh sb="0" eb="2">
+      <t>ジドウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ニュウリョクシャ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>シキベツ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>任意</t>
+    <rPh sb="0" eb="2">
+      <t>ニンイ</t>
     </rPh>
     <phoneticPr fontId="13"/>
   </si>
@@ -2894,7 +2922,7 @@
       <c r="B6" s="105"/>
       <c r="C6" s="103"/>
       <c r="D6" s="106" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="E6" s="106"/>
       <c r="F6" s="106"/>
@@ -3246,7 +3274,7 @@
         <v>2</v>
       </c>
       <c r="Q1" s="132" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="R1" s="133"/>
     </row>
@@ -3975,7 +4003,7 @@
         <v>2</v>
       </c>
       <c r="N1" s="22" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="O1" s="25" t="s">
         <v>3</v>
@@ -4068,7 +4096,7 @@
         <v>18</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="C6" s="30"/>
       <c r="D6" s="30"/>
@@ -4076,7 +4104,7 @@
       <c r="F6" s="30"/>
       <c r="G6" s="30"/>
       <c r="I6" s="35" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="J6" s="30" t="s">
         <v>69</v>
@@ -4089,10 +4117,10 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="81" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C7" s="30"/>
       <c r="D7" s="30"/>
@@ -4100,10 +4128,10 @@
       <c r="F7" s="30"/>
       <c r="G7" s="30"/>
       <c r="I7" s="81" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="J7" s="30" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="K7" s="30"/>
       <c r="L7" s="30"/>
@@ -4113,10 +4141,10 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="81" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="C8" s="34"/>
       <c r="D8" s="34"/>
@@ -4124,10 +4152,10 @@
       <c r="F8" s="34"/>
       <c r="G8" s="34"/>
       <c r="I8" s="81" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="J8" s="34" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="K8" s="34"/>
       <c r="L8" s="34"/>
@@ -4137,10 +4165,10 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="81" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="C9" s="30"/>
       <c r="D9" s="30"/>
@@ -4148,10 +4176,10 @@
       <c r="F9" s="30"/>
       <c r="G9" s="30"/>
       <c r="I9" s="81" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="K9" s="30"/>
       <c r="L9" s="30"/>
@@ -4161,10 +4189,10 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="81" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="C10" s="30"/>
       <c r="D10" s="30"/>
@@ -4181,7 +4209,7 @@
         <v>1.5</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="C11" s="30"/>
       <c r="D11" s="30"/>
@@ -4189,7 +4217,7 @@
       <c r="F11" s="30"/>
       <c r="G11" s="30"/>
       <c r="I11" s="35" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="J11" s="30"/>
       <c r="K11" s="30"/>
@@ -4207,10 +4235,10 @@
       <c r="F12" s="30"/>
       <c r="G12" s="30"/>
       <c r="I12" s="82" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="J12" s="30" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="K12" s="30"/>
       <c r="L12" s="30"/>
@@ -4223,7 +4251,7 @@
         <v>22</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="C13" s="30"/>
       <c r="D13" s="30"/>
@@ -4232,7 +4260,7 @@
       <c r="G13" s="30"/>
       <c r="I13" s="35"/>
       <c r="J13" s="30" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="K13" s="30"/>
       <c r="L13" s="30"/>
@@ -4242,10 +4270,10 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="82" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="C14" s="30"/>
       <c r="D14" s="30"/>
@@ -4253,7 +4281,7 @@
       <c r="F14" s="30"/>
       <c r="G14" s="30"/>
       <c r="J14" s="30" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="K14" s="30"/>
       <c r="L14" s="30"/>
@@ -4281,7 +4309,7 @@
         <v>23</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C16" s="30"/>
       <c r="D16" s="30"/>
@@ -4290,7 +4318,7 @@
       <c r="G16" s="30"/>
       <c r="H16" s="7"/>
       <c r="I16" s="16" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="J16" s="30"/>
       <c r="K16" s="30"/>
@@ -4301,10 +4329,10 @@
     </row>
     <row r="17" spans="1:15" ht="26.5">
       <c r="A17" s="82" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="B17" s="30" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="C17" s="30"/>
       <c r="D17" s="30"/>
@@ -4313,10 +4341,10 @@
       <c r="G17" s="30"/>
       <c r="H17" s="7"/>
       <c r="I17" s="82" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="J17" s="30" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="K17" s="36"/>
       <c r="L17" s="36"/>
@@ -4326,10 +4354,10 @@
     </row>
     <row r="18" spans="1:15" ht="26.5">
       <c r="A18" s="82" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="C18" s="34"/>
       <c r="D18" s="34"/>
@@ -4566,7 +4594,7 @@
     <row r="5" spans="1:18" ht="18" customHeight="1">
       <c r="A5" s="8"/>
       <c r="B5" s="96" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="C5" s="96"/>
       <c r="D5" s="96"/>
@@ -4585,7 +4613,7 @@
     <row r="6" spans="1:18">
       <c r="A6" s="34"/>
       <c r="B6" s="34" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="C6" s="34"/>
       <c r="D6" s="34"/>
@@ -4640,7 +4668,7 @@
     <row r="9" spans="1:18" ht="18" customHeight="1">
       <c r="A9" s="34"/>
       <c r="B9" s="85" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C9" s="85"/>
       <c r="D9" s="85"/>
@@ -4659,7 +4687,7 @@
     <row r="10" spans="1:18">
       <c r="A10" s="34"/>
       <c r="B10" s="85" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C10" s="85"/>
       <c r="D10" s="85"/>
@@ -4678,7 +4706,7 @@
     <row r="11" spans="1:18" ht="18" customHeight="1">
       <c r="A11" s="34"/>
       <c r="B11" s="85" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C11" s="85"/>
       <c r="D11" s="85"/>
@@ -4697,7 +4725,7 @@
     <row r="12" spans="1:18" ht="18" customHeight="1">
       <c r="A12" s="34"/>
       <c r="B12" s="85" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="C12" s="85"/>
       <c r="D12" s="85"/>
@@ -4796,7 +4824,7 @@
     <row r="17" spans="1:15" ht="18" customHeight="1">
       <c r="A17" s="34"/>
       <c r="B17" s="86" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="C17" s="86"/>
       <c r="D17" s="86"/>
@@ -4815,7 +4843,7 @@
     <row r="18" spans="1:15" ht="18" customHeight="1">
       <c r="A18" s="34"/>
       <c r="B18" s="86" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="C18" s="86"/>
       <c r="D18" s="86"/>
@@ -4834,7 +4862,7 @@
     <row r="19" spans="1:15" ht="18" customHeight="1">
       <c r="A19" s="34"/>
       <c r="B19" s="86" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C19" s="86"/>
       <c r="D19" s="86"/>
@@ -4978,7 +5006,7 @@
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="44" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C27" s="45"/>
       <c r="D27" s="45"/>
@@ -4997,7 +5025,7 @@
     <row r="28" spans="1:15">
       <c r="A28" s="8"/>
       <c r="B28" s="44" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C28" s="45"/>
       <c r="D28" s="45"/>
@@ -5016,7 +5044,7 @@
     <row r="29" spans="1:15">
       <c r="A29" s="8"/>
       <c r="B29" s="44" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C29" s="45"/>
       <c r="D29" s="45"/>
@@ -5070,7 +5098,7 @@
     <row r="32" spans="1:15">
       <c r="A32" s="8"/>
       <c r="B32" s="46" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -5089,7 +5117,7 @@
     <row r="33" spans="1:15">
       <c r="A33" s="8"/>
       <c r="B33" s="46" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
@@ -5108,7 +5136,7 @@
     <row r="34" spans="1:15">
       <c r="A34" s="8"/>
       <c r="B34" s="46" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
@@ -5127,7 +5155,7 @@
     <row r="35" spans="1:15">
       <c r="A35" s="8"/>
       <c r="B35" s="46" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
@@ -5308,7 +5336,7 @@
       </c>
       <c r="C7" s="143"/>
       <c r="D7" s="17" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="E7" s="53"/>
       <c r="F7" s="53"/>
@@ -5329,7 +5357,7 @@
       </c>
       <c r="C8" s="143"/>
       <c r="D8" s="17" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
@@ -5946,12 +5974,12 @@
     <row r="8" spans="1:15">
       <c r="A8" s="34"/>
       <c r="B8" s="52" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="C8" s="53"/>
       <c r="D8" s="53"/>
       <c r="E8" s="67" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="F8" s="23"/>
       <c r="G8" s="53"/>
@@ -5969,12 +5997,12 @@
     <row r="9" spans="1:15">
       <c r="A9" s="34"/>
       <c r="B9" s="52" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="C9" s="53"/>
       <c r="D9" s="53"/>
       <c r="E9" s="67" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="F9" s="23"/>
       <c r="G9" s="53"/>
@@ -5992,12 +6020,12 @@
     <row r="10" spans="1:15">
       <c r="A10" s="34"/>
       <c r="B10" s="52" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
       <c r="E10" s="146" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="F10" s="147"/>
       <c r="G10" s="147"/>
@@ -6116,7 +6144,7 @@
     <row r="17" spans="1:15">
       <c r="A17" s="34"/>
       <c r="B17" s="7" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="C17" s="56"/>
       <c r="D17" s="56"/>
@@ -6135,7 +6163,7 @@
     <row r="18" spans="1:15">
       <c r="A18" s="34"/>
       <c r="B18" s="56" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C18" s="41"/>
       <c r="D18" s="41"/>
@@ -6154,7 +6182,7 @@
     <row r="19" spans="1:15">
       <c r="A19" s="34"/>
       <c r="B19" s="7" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="C19" s="41"/>
       <c r="D19" s="41"/>
@@ -6190,7 +6218,7 @@
     <row r="21" spans="1:15">
       <c r="A21" s="34"/>
       <c r="B21" s="7" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="C21" s="41"/>
       <c r="D21" s="41"/>
@@ -6209,7 +6237,7 @@
     <row r="22" spans="1:15" ht="18" customHeight="1">
       <c r="A22" s="43"/>
       <c r="B22" s="7" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="C22" s="43"/>
       <c r="D22" s="43"/>
@@ -6228,7 +6256,7 @@
     <row r="23" spans="1:15" ht="18" customHeight="1">
       <c r="A23" s="8"/>
       <c r="B23" s="56" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
@@ -6263,7 +6291,7 @@
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
       <c r="B25" s="41" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="C25" s="45"/>
       <c r="D25" s="45"/>
@@ -6282,7 +6310,7 @@
     <row r="26" spans="1:15">
       <c r="A26" s="8"/>
       <c r="B26" s="56" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C26" s="45"/>
       <c r="D26" s="45"/>
@@ -6301,7 +6329,7 @@
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="56" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="C27" s="45"/>
       <c r="D27" s="45"/>
@@ -6419,7 +6447,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D678CDCE-2C5A-4AFB-B9CB-39BA46C32C81}">
-  <dimension ref="A1:O29"/>
+  <dimension ref="A1:O30"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="15" max="15" width="9.25" bestFit="1" customWidth="1"/>
@@ -6447,12 +6475,14 @@
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="38"/>
+      <c r="O1" s="38">
+        <v>46289</v>
+      </c>
     </row>
     <row r="2" spans="1:15" ht="20">
       <c r="A2" s="89"/>
@@ -6514,7 +6544,7 @@
     <row r="5" spans="1:15">
       <c r="A5" s="8"/>
       <c r="B5" s="30" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C5" s="30"/>
       <c r="D5" s="30"/>
@@ -6569,7 +6599,7 @@
     <row r="8" spans="1:15">
       <c r="A8" s="34"/>
       <c r="B8" s="34" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="C8" s="34"/>
       <c r="D8" s="34"/>
@@ -6587,26 +6617,26 @@
     </row>
     <row r="9" spans="1:15">
       <c r="A9" s="34"/>
-      <c r="B9" s="34"/>
-      <c r="C9" s="8"/>
-      <c r="D9" s="8"/>
-      <c r="E9" s="8"/>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
+      <c r="B9" s="34" t="s">
+        <v>175</v>
+      </c>
+      <c r="C9" s="34"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="34"/>
       <c r="I9" s="8"/>
-      <c r="J9" s="8"/>
-      <c r="K9" s="8"/>
-      <c r="L9" s="8"/>
-      <c r="M9" s="8"/>
-      <c r="N9" s="8"/>
+      <c r="J9" s="34"/>
+      <c r="K9" s="34"/>
+      <c r="L9" s="34"/>
+      <c r="M9" s="34"/>
+      <c r="N9" s="34"/>
       <c r="O9" s="34"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="34"/>
-      <c r="B10" s="7" t="s">
-        <v>108</v>
-      </c>
+      <c r="B10" s="34"/>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
@@ -6623,26 +6653,28 @@
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="34"/>
-      <c r="B11" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="41"/>
-      <c r="I11" s="41"/>
-      <c r="J11" s="41"/>
-      <c r="K11" s="41"/>
-      <c r="L11" s="41"/>
-      <c r="M11" s="41"/>
-      <c r="N11" s="41"/>
-      <c r="O11" s="41"/>
+      <c r="B11" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="8"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="34"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="34"/>
-      <c r="B12" s="41"/>
+      <c r="B12" s="41" t="s">
+        <v>101</v>
+      </c>
       <c r="C12" s="41"/>
       <c r="D12" s="41"/>
       <c r="E12" s="41"/>
@@ -6676,37 +6708,37 @@
     </row>
     <row r="14" spans="1:15">
       <c r="A14" s="34"/>
-      <c r="B14" s="58"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="58"/>
-      <c r="H14" s="58"/>
-      <c r="I14" s="58"/>
-      <c r="J14" s="58"/>
-      <c r="K14" s="58"/>
-      <c r="L14" s="58"/>
-      <c r="M14" s="58"/>
-      <c r="N14" s="58"/>
-      <c r="O14" s="58"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
+      <c r="D14" s="41"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="41"/>
+      <c r="G14" s="41"/>
+      <c r="H14" s="41"/>
+      <c r="I14" s="41"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="41"/>
+      <c r="L14" s="41"/>
+      <c r="M14" s="41"/>
+      <c r="N14" s="41"/>
+      <c r="O14" s="41"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="34"/>
-      <c r="B15" s="41"/>
-      <c r="C15" s="41"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="41"/>
-      <c r="F15" s="41"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="41"/>
-      <c r="I15" s="41"/>
-      <c r="J15" s="41"/>
-      <c r="K15" s="41"/>
-      <c r="L15" s="41"/>
-      <c r="M15" s="41"/>
-      <c r="N15" s="41"/>
-      <c r="O15" s="41"/>
+      <c r="B15" s="58"/>
+      <c r="C15" s="58"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="58"/>
+      <c r="I15" s="58"/>
+      <c r="J15" s="58"/>
+      <c r="K15" s="58"/>
+      <c r="L15" s="58"/>
+      <c r="M15" s="58"/>
+      <c r="N15" s="58"/>
+      <c r="O15" s="58"/>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="34"/>
@@ -6742,56 +6774,56 @@
       <c r="N17" s="41"/>
       <c r="O17" s="41"/>
     </row>
-    <row r="18" spans="1:15" ht="26.5">
-      <c r="A18" s="43"/>
-      <c r="B18" s="43"/>
-      <c r="C18" s="43"/>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="43"/>
-      <c r="I18" s="43"/>
-      <c r="J18" s="43"/>
-      <c r="K18" s="43"/>
-      <c r="L18" s="43"/>
-      <c r="M18" s="43"/>
-      <c r="N18" s="43"/>
-      <c r="O18" s="43"/>
-    </row>
-    <row r="19" spans="1:15">
-      <c r="A19" s="8"/>
-      <c r="B19" s="8"/>
-      <c r="C19" s="8"/>
-      <c r="D19" s="8"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-      <c r="J19" s="8"/>
-      <c r="K19" s="8"/>
-      <c r="L19" s="8"/>
-      <c r="M19" s="8"/>
-      <c r="N19" s="8"/>
-      <c r="O19" s="8"/>
+    <row r="18" spans="1:15">
+      <c r="A18" s="34"/>
+      <c r="B18" s="41"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="41"/>
+      <c r="I18" s="41"/>
+      <c r="J18" s="41"/>
+      <c r="K18" s="41"/>
+      <c r="L18" s="41"/>
+      <c r="M18" s="41"/>
+      <c r="N18" s="41"/>
+      <c r="O18" s="41"/>
+    </row>
+    <row r="19" spans="1:15" ht="26.5">
+      <c r="A19" s="43"/>
+      <c r="B19" s="43"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="43"/>
+      <c r="G19" s="43"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="43"/>
+      <c r="L19" s="43"/>
+      <c r="M19" s="43"/>
+      <c r="N19" s="43"/>
+      <c r="O19" s="43"/>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="8"/>
-      <c r="B20" s="56"/>
-      <c r="C20" s="56"/>
-      <c r="D20" s="56"/>
-      <c r="E20" s="56"/>
-      <c r="F20" s="56"/>
-      <c r="G20" s="56"/>
-      <c r="H20" s="56"/>
-      <c r="I20" s="56"/>
-      <c r="J20" s="56"/>
-      <c r="K20" s="56"/>
-      <c r="L20" s="56"/>
-      <c r="M20" s="56"/>
-      <c r="N20" s="56"/>
-      <c r="O20" s="56"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="8"/>
+      <c r="I20" s="8"/>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8"/>
+      <c r="L20" s="8"/>
+      <c r="M20" s="8"/>
+      <c r="N20" s="8"/>
+      <c r="O20" s="8"/>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="8"/>
@@ -6863,20 +6895,20 @@
     </row>
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
-      <c r="B25" s="8"/>
-      <c r="C25" s="8"/>
-      <c r="D25" s="8"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-      <c r="J25" s="8"/>
-      <c r="K25" s="8"/>
-      <c r="L25" s="8"/>
-      <c r="M25" s="8"/>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
+      <c r="B25" s="56"/>
+      <c r="C25" s="56"/>
+      <c r="D25" s="56"/>
+      <c r="E25" s="56"/>
+      <c r="F25" s="56"/>
+      <c r="G25" s="56"/>
+      <c r="H25" s="56"/>
+      <c r="I25" s="56"/>
+      <c r="J25" s="56"/>
+      <c r="K25" s="56"/>
+      <c r="L25" s="56"/>
+      <c r="M25" s="56"/>
+      <c r="N25" s="56"/>
+      <c r="O25" s="56"/>
     </row>
     <row r="26" spans="1:15">
       <c r="A26" s="8"/>
@@ -6946,6 +6978,23 @@
       <c r="N29" s="8"/>
       <c r="O29" s="8"/>
     </row>
+    <row r="30" spans="1:15">
+      <c r="A30" s="8"/>
+      <c r="B30" s="8"/>
+      <c r="C30" s="8"/>
+      <c r="D30" s="8"/>
+      <c r="E30" s="8"/>
+      <c r="F30" s="8"/>
+      <c r="G30" s="8"/>
+      <c r="H30" s="8"/>
+      <c r="I30" s="8"/>
+      <c r="J30" s="8"/>
+      <c r="K30" s="8"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="8"/>
+      <c r="N30" s="8"/>
+      <c r="O30" s="8"/>
+    </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A1:B2"/>
@@ -6961,7 +7010,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{140C4B60-E55A-4E72-B14E-C7619F01C68D}">
-  <dimension ref="A1:O34"/>
+  <dimension ref="A1:O33"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="15" max="15" width="9.25" bestFit="1" customWidth="1"/>
@@ -6994,7 +7043,9 @@
       <c r="N1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="38"/>
+      <c r="O1" s="38">
+        <v>46289</v>
+      </c>
     </row>
     <row r="2" spans="1:15" ht="20">
       <c r="A2" s="89"/>
@@ -7180,7 +7231,7 @@
       </c>
       <c r="I9" s="55"/>
       <c r="J9" s="154" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="K9" s="155"/>
       <c r="L9" s="155"/>
@@ -7234,7 +7285,7 @@
       </c>
       <c r="I11" s="23"/>
       <c r="J11" s="151" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="K11" s="152"/>
       <c r="L11" s="152"/>
@@ -7360,7 +7411,7 @@
     <row r="17" spans="1:15">
       <c r="A17" s="34"/>
       <c r="B17" s="41" t="s">
-        <v>97</v>
+        <v>176</v>
       </c>
       <c r="C17" s="41"/>
       <c r="D17" s="41"/>
@@ -7406,7 +7457,7 @@
     <row r="19" spans="1:15">
       <c r="A19" s="34"/>
       <c r="B19" s="52" t="s">
-        <v>99</v>
+        <v>177</v>
       </c>
       <c r="C19" s="55"/>
       <c r="D19" s="52" t="s">
@@ -7433,23 +7484,23 @@
     <row r="20" spans="1:15">
       <c r="A20" s="34"/>
       <c r="B20" s="52" t="s">
-        <v>100</v>
+        <v>178</v>
       </c>
       <c r="C20" s="55"/>
       <c r="D20" s="52" t="s">
-        <v>45</v>
+        <v>182</v>
       </c>
       <c r="E20" s="55"/>
-      <c r="F20" s="52">
-        <v>1000</v>
+      <c r="F20" s="52" t="s">
+        <v>93</v>
       </c>
       <c r="G20" s="55"/>
       <c r="H20" s="52" t="s">
-        <v>93</v>
+        <v>185</v>
       </c>
       <c r="I20" s="55"/>
       <c r="J20" s="52" t="s">
-        <v>67</v>
+        <v>183</v>
       </c>
       <c r="K20" s="23"/>
       <c r="L20" s="53"/>
@@ -7460,24 +7511,22 @@
     <row r="21" spans="1:15" ht="36" customHeight="1">
       <c r="A21" s="34"/>
       <c r="B21" s="52" t="s">
-        <v>101</v>
+        <v>179</v>
       </c>
       <c r="C21" s="55"/>
       <c r="D21" s="52" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E21" s="55"/>
       <c r="F21" s="52">
-        <v>1</v>
+        <v>1000</v>
       </c>
       <c r="G21" s="55"/>
       <c r="H21" s="52" t="s">
-        <v>46</v>
+        <v>185</v>
       </c>
       <c r="I21" s="55"/>
-      <c r="J21" s="52" t="s">
-        <v>104</v>
-      </c>
+      <c r="J21" s="52"/>
       <c r="K21" s="23"/>
       <c r="L21" s="53"/>
       <c r="M21" s="54"/>
@@ -7487,61 +7536,63 @@
     <row r="22" spans="1:15" ht="18" customHeight="1">
       <c r="A22" s="43"/>
       <c r="B22" s="52" t="s">
-        <v>102</v>
+        <v>180</v>
       </c>
       <c r="C22" s="55"/>
       <c r="D22" s="52" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="E22" s="55"/>
       <c r="F22" s="52">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G22" s="55"/>
       <c r="H22" s="52" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I22" s="23"/>
-      <c r="J22" s="75"/>
+      <c r="J22" s="17" t="s">
+        <v>184</v>
+      </c>
       <c r="K22" s="23"/>
       <c r="L22" s="53"/>
       <c r="M22" s="54"/>
       <c r="N22" s="43"/>
       <c r="O22" s="43"/>
     </row>
-    <row r="23" spans="1:15" ht="36" customHeight="1">
+    <row r="23" spans="1:15">
       <c r="A23" s="8"/>
-      <c r="B23" s="67" t="s">
-        <v>105</v>
+      <c r="B23" s="52" t="s">
+        <v>84</v>
       </c>
       <c r="C23" s="55"/>
       <c r="D23" s="52" t="s">
-        <v>65</v>
+        <v>91</v>
       </c>
       <c r="E23" s="55"/>
-      <c r="F23" s="17">
-        <v>1</v>
+      <c r="F23" s="17" t="s">
+        <v>93</v>
       </c>
       <c r="G23" s="55"/>
       <c r="H23" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="I23" s="23"/>
-      <c r="J23" s="151" t="s">
-        <v>106</v>
-      </c>
-      <c r="K23" s="152"/>
-      <c r="L23" s="152"/>
-      <c r="M23" s="153"/>
-      <c r="N23" s="8"/>
-      <c r="O23" s="8"/>
-    </row>
-    <row r="24" spans="1:15">
+        <v>93</v>
+      </c>
+      <c r="I23" s="55"/>
+      <c r="J23" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="K23" s="23"/>
+      <c r="L23" s="23"/>
+      <c r="M23" s="55"/>
+      <c r="N23" s="56"/>
+      <c r="O23" s="56"/>
+    </row>
+    <row r="24" spans="1:15" ht="18" customHeight="1">
       <c r="A24" s="8"/>
-      <c r="B24" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="C24" s="55"/>
+      <c r="B24" s="52" t="s">
+        <v>85</v>
+      </c>
+      <c r="C24" s="54"/>
       <c r="D24" s="52" t="s">
         <v>91</v>
       </c>
@@ -7555,7 +7606,7 @@
       </c>
       <c r="I24" s="55"/>
       <c r="J24" s="17" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="K24" s="23"/>
       <c r="L24" s="23"/>
@@ -7563,57 +7614,47 @@
       <c r="N24" s="56"/>
       <c r="O24" s="56"/>
     </row>
-    <row r="25" spans="1:15" ht="18" customHeight="1">
+    <row r="25" spans="1:15" ht="36" customHeight="1">
       <c r="A25" s="8"/>
-      <c r="B25" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="C25" s="54"/>
+      <c r="B25" s="52" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" s="73"/>
       <c r="D25" s="52" t="s">
-        <v>91</v>
+        <v>66</v>
       </c>
       <c r="E25" s="55"/>
-      <c r="F25" s="17" t="s">
-        <v>93</v>
+      <c r="F25" s="17">
+        <v>1</v>
       </c>
       <c r="G25" s="55"/>
       <c r="H25" s="17" t="s">
         <v>93</v>
       </c>
       <c r="I25" s="55"/>
-      <c r="J25" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="K25" s="23"/>
-      <c r="L25" s="23"/>
-      <c r="M25" s="55"/>
+      <c r="J25" s="146" t="s">
+        <v>92</v>
+      </c>
+      <c r="K25" s="147"/>
+      <c r="L25" s="147"/>
+      <c r="M25" s="148"/>
       <c r="N25" s="56"/>
       <c r="O25" s="56"/>
     </row>
-    <row r="26" spans="1:15" ht="36" customHeight="1">
+    <row r="26" spans="1:15">
       <c r="A26" s="8"/>
-      <c r="B26" s="52" t="s">
-        <v>86</v>
-      </c>
-      <c r="C26" s="73"/>
-      <c r="D26" s="52" t="s">
-        <v>66</v>
-      </c>
-      <c r="E26" s="55"/>
-      <c r="F26" s="17">
-        <v>1</v>
-      </c>
-      <c r="G26" s="55"/>
-      <c r="H26" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="I26" s="55"/>
-      <c r="J26" s="146" t="s">
-        <v>92</v>
-      </c>
-      <c r="K26" s="147"/>
-      <c r="L26" s="147"/>
-      <c r="M26" s="148"/>
+      <c r="B26" s="56"/>
+      <c r="C26" s="56"/>
+      <c r="D26" s="56"/>
+      <c r="E26" s="56"/>
+      <c r="F26" s="56"/>
+      <c r="G26" s="56"/>
+      <c r="H26" s="56"/>
+      <c r="I26" s="56"/>
+      <c r="J26" s="56"/>
+      <c r="K26" s="56"/>
+      <c r="L26" s="56"/>
+      <c r="M26" s="56"/>
       <c r="N26" s="56"/>
       <c r="O26" s="56"/>
     </row>
@@ -7648,23 +7689,23 @@
       <c r="K28" s="56"/>
       <c r="L28" s="56"/>
       <c r="M28" s="56"/>
-      <c r="N28" s="56"/>
-      <c r="O28" s="56"/>
+      <c r="N28" s="8"/>
+      <c r="O28" s="8"/>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" s="8"/>
-      <c r="B29" s="56"/>
-      <c r="C29" s="56"/>
-      <c r="D29" s="56"/>
-      <c r="E29" s="56"/>
-      <c r="F29" s="56"/>
-      <c r="G29" s="56"/>
-      <c r="H29" s="56"/>
-      <c r="I29" s="56"/>
-      <c r="J29" s="56"/>
-      <c r="K29" s="56"/>
-      <c r="L29" s="56"/>
-      <c r="M29" s="56"/>
+      <c r="B29" s="8"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="8"/>
+      <c r="E29" s="8"/>
+      <c r="F29" s="8"/>
+      <c r="G29" s="8"/>
+      <c r="H29" s="8"/>
+      <c r="I29" s="8"/>
+      <c r="J29" s="8"/>
+      <c r="K29" s="8"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="8"/>
       <c r="N29" s="8"/>
       <c r="O29" s="8"/>
     </row>
@@ -7719,8 +7760,7 @@
       <c r="N32" s="8"/>
       <c r="O32" s="8"/>
     </row>
-    <row r="33" spans="1:15">
-      <c r="A33" s="8"/>
+    <row r="33" spans="2:13">
       <c r="B33" s="8"/>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
@@ -7733,27 +7773,10 @@
       <c r="K33" s="8"/>
       <c r="L33" s="8"/>
       <c r="M33" s="8"/>
-      <c r="N33" s="8"/>
-      <c r="O33" s="8"/>
-    </row>
-    <row r="34" spans="1:15">
-      <c r="B34" s="8"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="8"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="8"/>
-      <c r="H34" s="8"/>
-      <c r="I34" s="8"/>
-      <c r="J34" s="8"/>
-      <c r="K34" s="8"/>
-      <c r="L34" s="8"/>
-      <c r="M34" s="8"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="J23:M23"/>
-    <mergeCell ref="J26:M26"/>
+  <mergeCells count="9">
+    <mergeCell ref="J25:M25"/>
     <mergeCell ref="J9:M9"/>
     <mergeCell ref="J14:M14"/>
     <mergeCell ref="A1:B2"/>
@@ -7892,21 +7915,21 @@
         <v>1</v>
       </c>
       <c r="C6" s="75" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="D6" s="77"/>
       <c r="E6" s="78"/>
       <c r="F6" s="77"/>
       <c r="G6" s="76"/>
       <c r="H6" s="75" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="I6" s="78"/>
       <c r="J6" s="77"/>
       <c r="K6" s="77"/>
       <c r="L6" s="79"/>
       <c r="M6" s="151" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="N6" s="152"/>
       <c r="O6" s="153"/>
@@ -7918,21 +7941,21 @@
         <v>2</v>
       </c>
       <c r="C7" s="75" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="D7" s="77"/>
       <c r="E7" s="78"/>
       <c r="F7" s="77"/>
       <c r="G7" s="76"/>
       <c r="H7" s="75" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="I7" s="78"/>
       <c r="J7" s="77"/>
       <c r="K7" s="77"/>
       <c r="L7" s="79"/>
       <c r="M7" s="157" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="N7" s="158"/>
       <c r="O7" s="159"/>

--- a/要件定義書（カレンダーアプリ）.xlsx
+++ b/要件定義書（カレンダーアプリ）.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\my_application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F12FF23-92AA-48C4-8C47-7A16D8A5CA10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72F46712-B132-408E-8C0F-C57958640ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="7" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="275" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="186">
   <si>
     <t>要件定義</t>
   </si>
@@ -617,86 +617,12 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>タスク登録の増加によるデータの圧迫</t>
-    <rPh sb="3" eb="5">
-      <t>トウロク</t>
-    </rPh>
-    <rPh sb="6" eb="8">
-      <t>ゾウカ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>アッパク</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
     <t>表示に時間がかかるのではないか。</t>
     <rPh sb="0" eb="2">
       <t>ヒョウジ</t>
     </rPh>
     <rPh sb="3" eb="5">
       <t>ジカン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>タスクステータス・削除フラグの設定による表示件数の限定化</t>
-    <rPh sb="9" eb="11">
-      <t>サクジョ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>セッテイ</t>
-    </rPh>
-    <rPh sb="20" eb="24">
-      <t>ヒョウジケンスウ</t>
-    </rPh>
-    <rPh sb="25" eb="27">
-      <t>ゲンテイ</t>
-    </rPh>
-    <rPh sb="27" eb="28">
-      <t>カ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>入力漏れ</t>
-    <rPh sb="0" eb="2">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>モ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>入力漏れによる業務漏れ・遅延</t>
-    <rPh sb="0" eb="3">
-      <t>ニュウリョクモ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ギョウム</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>モ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>チエン</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>朝礼・ミーティング等で相互確認の徹底</t>
-    <rPh sb="0" eb="2">
-      <t>チョウレイ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>トウ</t>
-    </rPh>
-    <rPh sb="11" eb="15">
-      <t>ソウゴカクニン</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>テッテイ</t>
     </rPh>
     <phoneticPr fontId="13"/>
   </si>
@@ -1545,6 +1471,188 @@
     </rPh>
     <phoneticPr fontId="13"/>
   </si>
+  <si>
+    <t>スケジュールの増加によるデータの圧迫</t>
+    <rPh sb="7" eb="9">
+      <t>ゾウカ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>アッパク</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>削除フラグの設定による表示件数の限定化</t>
+    <rPh sb="0" eb="2">
+      <t>サクジョ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>セッテイ</t>
+    </rPh>
+    <rPh sb="11" eb="15">
+      <t>ヒョウジケンスウ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>ゲンテイ</t>
+    </rPh>
+    <rPh sb="18" eb="19">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>渡辺のぞみ</t>
+    <rPh sb="0" eb="2">
+      <t>ワタナベ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>w</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>業務要件1-1・1-2</t>
+    </r>
+    <rPh sb="1" eb="5">
+      <t>ギョウムヨウケン</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>w</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>業務要件1-3・1-4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>w</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">利用者権限
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>w</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">機能要件
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>w</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">非機能要件
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Wingdings"/>
+        <charset val="2"/>
+      </rPr>
+      <t>w</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="游ゴシック"/>
+        <family val="3"/>
+        <charset val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>データ項目定義</t>
+    </r>
+    <rPh sb="1" eb="5">
+      <t>ギョウムヨウケン</t>
+    </rPh>
+    <rPh sb="14" eb="19">
+      <t>リヨウシャケンゲン</t>
+    </rPh>
+    <rPh sb="21" eb="25">
+      <t>キノウヨウケン</t>
+    </rPh>
+    <rPh sb="27" eb="32">
+      <t>ヒキノウヨウケン</t>
+    </rPh>
+    <rPh sb="37" eb="41">
+      <t>コウモクテイギ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
 </sst>
 </file>
 
@@ -1553,7 +1661,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1672,6 +1780,25 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="Wingdings"/>
+      <charset val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="游ゴシック"/>
+      <family val="3"/>
+      <charset val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -1693,7 +1820,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -2023,13 +2150,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="hair">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="hair">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="160">
+  <cellXfs count="165">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2399,9 +2548,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2509,6 +2655,24 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2922,7 +3086,7 @@
       <c r="B6" s="105"/>
       <c r="C6" s="103"/>
       <c r="D6" s="106" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="E6" s="106"/>
       <c r="F6" s="106"/>
@@ -3043,7 +3207,9 @@
         <v>3</v>
       </c>
       <c r="G12" s="98"/>
-      <c r="H12" s="99"/>
+      <c r="H12" s="99">
+        <v>46282</v>
+      </c>
       <c r="I12" s="100"/>
       <c r="J12" s="100"/>
       <c r="K12" s="100"/>
@@ -3063,7 +3229,9 @@
         <v>10</v>
       </c>
       <c r="G13" s="98"/>
-      <c r="H13" s="99"/>
+      <c r="H13" s="99">
+        <v>46289</v>
+      </c>
       <c r="I13" s="100"/>
       <c r="J13" s="100"/>
       <c r="K13" s="100"/>
@@ -3254,51 +3422,53 @@
       <c r="A1" s="87" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="124"/>
+      <c r="B1" s="123"/>
       <c r="C1" s="88"/>
-      <c r="D1" s="126" t="s">
+      <c r="D1" s="125" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="127"/>
-      <c r="F1" s="127"/>
-      <c r="G1" s="127"/>
-      <c r="H1" s="127"/>
-      <c r="I1" s="127"/>
-      <c r="J1" s="127"/>
-      <c r="K1" s="127"/>
-      <c r="L1" s="127"/>
-      <c r="M1" s="127"/>
-      <c r="N1" s="127"/>
-      <c r="O1" s="128"/>
+      <c r="E1" s="126"/>
+      <c r="F1" s="126"/>
+      <c r="G1" s="126"/>
+      <c r="H1" s="126"/>
+      <c r="I1" s="126"/>
+      <c r="J1" s="126"/>
+      <c r="K1" s="126"/>
+      <c r="L1" s="126"/>
+      <c r="M1" s="126"/>
+      <c r="N1" s="126"/>
+      <c r="O1" s="127"/>
       <c r="P1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="132" t="s">
+      <c r="Q1" s="131" t="s">
         <v>103</v>
       </c>
-      <c r="R1" s="133"/>
+      <c r="R1" s="132"/>
     </row>
     <row r="2" spans="1:18">
       <c r="A2" s="89"/>
-      <c r="B2" s="125"/>
+      <c r="B2" s="124"/>
       <c r="C2" s="90"/>
-      <c r="D2" s="129"/>
-      <c r="E2" s="130"/>
-      <c r="F2" s="130"/>
-      <c r="G2" s="130"/>
-      <c r="H2" s="130"/>
-      <c r="I2" s="130"/>
-      <c r="J2" s="130"/>
-      <c r="K2" s="130"/>
-      <c r="L2" s="130"/>
-      <c r="M2" s="130"/>
-      <c r="N2" s="130"/>
-      <c r="O2" s="131"/>
+      <c r="D2" s="128"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="I2" s="129"/>
+      <c r="J2" s="129"/>
+      <c r="K2" s="129"/>
+      <c r="L2" s="129"/>
+      <c r="M2" s="129"/>
+      <c r="N2" s="129"/>
+      <c r="O2" s="130"/>
       <c r="P2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="Q2" s="134"/>
-      <c r="R2" s="135"/>
+      <c r="Q2" s="133">
+        <v>46289</v>
+      </c>
+      <c r="R2" s="134"/>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="2"/>
@@ -3324,45 +3494,51 @@
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="136" t="s">
+      <c r="B4" s="135" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="137"/>
-      <c r="D4" s="136" t="s">
+      <c r="C4" s="136"/>
+      <c r="D4" s="135" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="137"/>
-      <c r="F4" s="136" t="s">
+      <c r="E4" s="136"/>
+      <c r="F4" s="135" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="138"/>
-      <c r="H4" s="138"/>
-      <c r="I4" s="138"/>
-      <c r="J4" s="137"/>
-      <c r="K4" s="136" t="s">
+      <c r="G4" s="137"/>
+      <c r="H4" s="137"/>
+      <c r="I4" s="137"/>
+      <c r="J4" s="136"/>
+      <c r="K4" s="135" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="138"/>
-      <c r="M4" s="138"/>
-      <c r="N4" s="138"/>
-      <c r="O4" s="138"/>
-      <c r="P4" s="138"/>
-      <c r="Q4" s="138"/>
-      <c r="R4" s="137"/>
+      <c r="L4" s="137"/>
+      <c r="M4" s="137"/>
+      <c r="N4" s="137"/>
+      <c r="O4" s="137"/>
+      <c r="P4" s="137"/>
+      <c r="Q4" s="137"/>
+      <c r="R4" s="136"/>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="4">
         <v>1</v>
       </c>
-      <c r="B5" s="117"/>
+      <c r="B5" s="117">
+        <v>46282</v>
+      </c>
       <c r="C5" s="118"/>
-      <c r="D5" s="119"/>
+      <c r="D5" s="119" t="s">
+        <v>183</v>
+      </c>
       <c r="E5" s="118"/>
-      <c r="F5" s="120"/>
-      <c r="G5" s="121"/>
-      <c r="H5" s="121"/>
-      <c r="I5" s="121"/>
-      <c r="J5" s="122"/>
+      <c r="F5" s="159" t="s">
+        <v>184</v>
+      </c>
+      <c r="G5" s="160"/>
+      <c r="H5" s="160"/>
+      <c r="I5" s="160"/>
+      <c r="J5" s="161"/>
       <c r="K5" s="120"/>
       <c r="L5" s="121"/>
       <c r="M5" s="121"/>
@@ -3372,19 +3548,25 @@
       <c r="Q5" s="121"/>
       <c r="R5" s="122"/>
     </row>
-    <row r="6" spans="1:18" ht="54" customHeight="1">
+    <row r="6" spans="1:18" ht="90" customHeight="1">
       <c r="A6" s="6">
         <v>2</v>
       </c>
-      <c r="B6" s="113"/>
+      <c r="B6" s="113">
+        <v>46289</v>
+      </c>
       <c r="C6" s="108"/>
-      <c r="D6" s="107"/>
+      <c r="D6" s="107" t="s">
+        <v>183</v>
+      </c>
       <c r="E6" s="108"/>
-      <c r="F6" s="123"/>
-      <c r="G6" s="111"/>
-      <c r="H6" s="111"/>
-      <c r="I6" s="111"/>
-      <c r="J6" s="112"/>
+      <c r="F6" s="162" t="s">
+        <v>185</v>
+      </c>
+      <c r="G6" s="163"/>
+      <c r="H6" s="163"/>
+      <c r="I6" s="163"/>
+      <c r="J6" s="164"/>
       <c r="K6" s="110"/>
       <c r="L6" s="111"/>
       <c r="M6" s="111"/>
@@ -3990,15 +4172,15 @@
       <c r="C1" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="124"/>
-      <c r="E1" s="124"/>
-      <c r="F1" s="124"/>
-      <c r="G1" s="124"/>
-      <c r="H1" s="124"/>
-      <c r="I1" s="124"/>
-      <c r="J1" s="124"/>
-      <c r="K1" s="124"/>
-      <c r="L1" s="124"/>
+      <c r="D1" s="123"/>
+      <c r="E1" s="123"/>
+      <c r="F1" s="123"/>
+      <c r="G1" s="123"/>
+      <c r="H1" s="123"/>
+      <c r="I1" s="123"/>
+      <c r="J1" s="123"/>
+      <c r="K1" s="123"/>
+      <c r="L1" s="123"/>
       <c r="M1" s="24" t="s">
         <v>2</v>
       </c>
@@ -4014,15 +4196,15 @@
       <c r="A2" s="89"/>
       <c r="B2" s="90"/>
       <c r="C2" s="89"/>
-      <c r="D2" s="125"/>
-      <c r="E2" s="125"/>
-      <c r="F2" s="125"/>
-      <c r="G2" s="125"/>
-      <c r="H2" s="125"/>
-      <c r="I2" s="125"/>
-      <c r="J2" s="125"/>
-      <c r="K2" s="125"/>
-      <c r="L2" s="125"/>
+      <c r="D2" s="124"/>
+      <c r="E2" s="124"/>
+      <c r="F2" s="124"/>
+      <c r="G2" s="124"/>
+      <c r="H2" s="124"/>
+      <c r="I2" s="124"/>
+      <c r="J2" s="124"/>
+      <c r="K2" s="124"/>
+      <c r="L2" s="124"/>
       <c r="M2" s="27" t="s">
         <v>14</v>
       </c>
@@ -4053,26 +4235,26 @@
       <c r="A4" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="139" t="s">
+      <c r="B4" s="138" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="140"/>
-      <c r="D4" s="140"/>
-      <c r="E4" s="140"/>
-      <c r="F4" s="140"/>
-      <c r="G4" s="141"/>
+      <c r="C4" s="139"/>
+      <c r="D4" s="139"/>
+      <c r="E4" s="139"/>
+      <c r="F4" s="139"/>
+      <c r="G4" s="140"/>
       <c r="H4" s="30"/>
       <c r="I4" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="139" t="s">
+      <c r="J4" s="138" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="140"/>
-      <c r="L4" s="140"/>
-      <c r="M4" s="140"/>
-      <c r="N4" s="140"/>
-      <c r="O4" s="141"/>
+      <c r="K4" s="139"/>
+      <c r="L4" s="139"/>
+      <c r="M4" s="139"/>
+      <c r="N4" s="139"/>
+      <c r="O4" s="140"/>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="16"/>
@@ -4096,7 +4278,7 @@
         <v>18</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C6" s="30"/>
       <c r="D6" s="30"/>
@@ -4104,7 +4286,7 @@
       <c r="F6" s="30"/>
       <c r="G6" s="30"/>
       <c r="I6" s="35" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="J6" s="30" t="s">
         <v>69</v>
@@ -4117,10 +4299,10 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="81" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C7" s="30"/>
       <c r="D7" s="30"/>
@@ -4128,10 +4310,10 @@
       <c r="F7" s="30"/>
       <c r="G7" s="30"/>
       <c r="I7" s="81" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="J7" s="30" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="K7" s="30"/>
       <c r="L7" s="30"/>
@@ -4141,10 +4323,10 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="81" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C8" s="34"/>
       <c r="D8" s="34"/>
@@ -4152,10 +4334,10 @@
       <c r="F8" s="34"/>
       <c r="G8" s="34"/>
       <c r="I8" s="81" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="J8" s="34" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="K8" s="34"/>
       <c r="L8" s="34"/>
@@ -4165,10 +4347,10 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="81" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="C9" s="30"/>
       <c r="D9" s="30"/>
@@ -4176,10 +4358,10 @@
       <c r="F9" s="30"/>
       <c r="G9" s="30"/>
       <c r="I9" s="81" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="K9" s="30"/>
       <c r="L9" s="30"/>
@@ -4189,10 +4371,10 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="81" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C10" s="30"/>
       <c r="D10" s="30"/>
@@ -4209,7 +4391,7 @@
         <v>1.5</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C11" s="30"/>
       <c r="D11" s="30"/>
@@ -4217,7 +4399,7 @@
       <c r="F11" s="30"/>
       <c r="G11" s="30"/>
       <c r="I11" s="35" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="J11" s="30"/>
       <c r="K11" s="30"/>
@@ -4235,10 +4417,10 @@
       <c r="F12" s="30"/>
       <c r="G12" s="30"/>
       <c r="I12" s="82" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="J12" s="30" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="K12" s="30"/>
       <c r="L12" s="30"/>
@@ -4251,7 +4433,7 @@
         <v>22</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C13" s="30"/>
       <c r="D13" s="30"/>
@@ -4260,7 +4442,7 @@
       <c r="G13" s="30"/>
       <c r="I13" s="35"/>
       <c r="J13" s="30" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="K13" s="30"/>
       <c r="L13" s="30"/>
@@ -4270,10 +4452,10 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="82" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C14" s="30"/>
       <c r="D14" s="30"/>
@@ -4281,7 +4463,7 @@
       <c r="F14" s="30"/>
       <c r="G14" s="30"/>
       <c r="J14" s="30" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="K14" s="30"/>
       <c r="L14" s="30"/>
@@ -4309,7 +4491,7 @@
         <v>23</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C16" s="30"/>
       <c r="D16" s="30"/>
@@ -4318,7 +4500,7 @@
       <c r="G16" s="30"/>
       <c r="H16" s="7"/>
       <c r="I16" s="16" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="J16" s="30"/>
       <c r="K16" s="30"/>
@@ -4329,10 +4511,10 @@
     </row>
     <row r="17" spans="1:15" ht="26.5">
       <c r="A17" s="82" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B17" s="30" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C17" s="30"/>
       <c r="D17" s="30"/>
@@ -4341,10 +4523,10 @@
       <c r="G17" s="30"/>
       <c r="H17" s="7"/>
       <c r="I17" s="82" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="J17" s="30" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="K17" s="36"/>
       <c r="L17" s="36"/>
@@ -4354,10 +4536,10 @@
     </row>
     <row r="18" spans="1:15" ht="26.5">
       <c r="A18" s="82" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="C18" s="34"/>
       <c r="D18" s="34"/>
@@ -4594,7 +4776,7 @@
     <row r="5" spans="1:18" ht="18" customHeight="1">
       <c r="A5" s="8"/>
       <c r="B5" s="96" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="C5" s="96"/>
       <c r="D5" s="96"/>
@@ -4613,7 +4795,7 @@
     <row r="6" spans="1:18">
       <c r="A6" s="34"/>
       <c r="B6" s="34" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="C6" s="34"/>
       <c r="D6" s="34"/>
@@ -4668,7 +4850,7 @@
     <row r="9" spans="1:18" ht="18" customHeight="1">
       <c r="A9" s="34"/>
       <c r="B9" s="85" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="C9" s="85"/>
       <c r="D9" s="85"/>
@@ -4687,7 +4869,7 @@
     <row r="10" spans="1:18">
       <c r="A10" s="34"/>
       <c r="B10" s="85" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="C10" s="85"/>
       <c r="D10" s="85"/>
@@ -4706,7 +4888,7 @@
     <row r="11" spans="1:18" ht="18" customHeight="1">
       <c r="A11" s="34"/>
       <c r="B11" s="85" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C11" s="85"/>
       <c r="D11" s="85"/>
@@ -4725,7 +4907,7 @@
     <row r="12" spans="1:18" ht="18" customHeight="1">
       <c r="A12" s="34"/>
       <c r="B12" s="85" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="C12" s="85"/>
       <c r="D12" s="85"/>
@@ -4824,7 +5006,7 @@
     <row r="17" spans="1:15" ht="18" customHeight="1">
       <c r="A17" s="34"/>
       <c r="B17" s="86" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C17" s="86"/>
       <c r="D17" s="86"/>
@@ -4843,7 +5025,7 @@
     <row r="18" spans="1:15" ht="18" customHeight="1">
       <c r="A18" s="34"/>
       <c r="B18" s="86" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C18" s="86"/>
       <c r="D18" s="86"/>
@@ -4862,7 +5044,7 @@
     <row r="19" spans="1:15" ht="18" customHeight="1">
       <c r="A19" s="34"/>
       <c r="B19" s="86" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C19" s="86"/>
       <c r="D19" s="86"/>
@@ -5006,7 +5188,7 @@
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="44" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C27" s="45"/>
       <c r="D27" s="45"/>
@@ -5025,7 +5207,7 @@
     <row r="28" spans="1:15">
       <c r="A28" s="8"/>
       <c r="B28" s="44" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C28" s="45"/>
       <c r="D28" s="45"/>
@@ -5044,7 +5226,7 @@
     <row r="29" spans="1:15">
       <c r="A29" s="8"/>
       <c r="B29" s="44" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="C29" s="45"/>
       <c r="D29" s="45"/>
@@ -5098,7 +5280,7 @@
     <row r="32" spans="1:15">
       <c r="A32" s="8"/>
       <c r="B32" s="46" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -5117,7 +5299,7 @@
     <row r="33" spans="1:15">
       <c r="A33" s="8"/>
       <c r="B33" s="46" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
@@ -5136,7 +5318,7 @@
     <row r="34" spans="1:15">
       <c r="A34" s="8"/>
       <c r="B34" s="46" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
@@ -5155,7 +5337,7 @@
     <row r="35" spans="1:15">
       <c r="A35" s="8"/>
       <c r="B35" s="46" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
@@ -5310,10 +5492,10 @@
     </row>
     <row r="6" spans="1:15" ht="18" customHeight="1">
       <c r="A6" s="34"/>
-      <c r="B6" s="144" t="s">
+      <c r="B6" s="143" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="145"/>
+      <c r="C6" s="144"/>
       <c r="D6" s="74" t="s">
         <v>72</v>
       </c>
@@ -5331,12 +5513,12 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="34"/>
-      <c r="B7" s="142" t="s">
+      <c r="B7" s="141" t="s">
         <v>71</v>
       </c>
-      <c r="C7" s="143"/>
+      <c r="C7" s="142"/>
       <c r="D7" s="17" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="E7" s="53"/>
       <c r="F7" s="53"/>
@@ -5352,12 +5534,12 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="34"/>
-      <c r="B8" s="142" t="s">
+      <c r="B8" s="141" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="143"/>
+      <c r="C8" s="142"/>
       <c r="D8" s="17" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
@@ -5846,10 +6028,10 @@
       <c r="M1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="149">
+      <c r="N1" s="148">
         <v>46289</v>
       </c>
-      <c r="O1" s="149"/>
+      <c r="O1" s="148"/>
     </row>
     <row r="2" spans="1:15" ht="20">
       <c r="A2" s="89"/>
@@ -5869,8 +6051,8 @@
       <c r="M2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="150"/>
-      <c r="O2" s="150"/>
+      <c r="N2" s="149"/>
+      <c r="O2" s="149"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="39"/>
@@ -5974,12 +6156,12 @@
     <row r="8" spans="1:15">
       <c r="A8" s="34"/>
       <c r="B8" s="52" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C8" s="53"/>
       <c r="D8" s="53"/>
       <c r="E8" s="67" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F8" s="23"/>
       <c r="G8" s="53"/>
@@ -5997,12 +6179,12 @@
     <row r="9" spans="1:15">
       <c r="A9" s="34"/>
       <c r="B9" s="52" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="C9" s="53"/>
       <c r="D9" s="53"/>
       <c r="E9" s="67" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F9" s="23"/>
       <c r="G9" s="53"/>
@@ -6020,18 +6202,18 @@
     <row r="10" spans="1:15">
       <c r="A10" s="34"/>
       <c r="B10" s="52" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
-      <c r="E10" s="146" t="s">
-        <v>166</v>
-      </c>
-      <c r="F10" s="147"/>
-      <c r="G10" s="147"/>
-      <c r="H10" s="147"/>
-      <c r="I10" s="147"/>
-      <c r="J10" s="148"/>
+      <c r="E10" s="145" t="s">
+        <v>161</v>
+      </c>
+      <c r="F10" s="146"/>
+      <c r="G10" s="146"/>
+      <c r="H10" s="146"/>
+      <c r="I10" s="146"/>
+      <c r="J10" s="147"/>
       <c r="K10" s="68" t="s">
         <v>75</v>
       </c>
@@ -6144,7 +6326,7 @@
     <row r="17" spans="1:15">
       <c r="A17" s="34"/>
       <c r="B17" s="7" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="C17" s="56"/>
       <c r="D17" s="56"/>
@@ -6163,7 +6345,7 @@
     <row r="18" spans="1:15">
       <c r="A18" s="34"/>
       <c r="B18" s="56" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C18" s="41"/>
       <c r="D18" s="41"/>
@@ -6182,7 +6364,7 @@
     <row r="19" spans="1:15">
       <c r="A19" s="34"/>
       <c r="B19" s="7" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C19" s="41"/>
       <c r="D19" s="41"/>
@@ -6218,7 +6400,7 @@
     <row r="21" spans="1:15">
       <c r="A21" s="34"/>
       <c r="B21" s="7" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="C21" s="41"/>
       <c r="D21" s="41"/>
@@ -6237,7 +6419,7 @@
     <row r="22" spans="1:15" ht="18" customHeight="1">
       <c r="A22" s="43"/>
       <c r="B22" s="7" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C22" s="43"/>
       <c r="D22" s="43"/>
@@ -6256,7 +6438,7 @@
     <row r="23" spans="1:15" ht="18" customHeight="1">
       <c r="A23" s="8"/>
       <c r="B23" s="56" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
@@ -6291,7 +6473,7 @@
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
       <c r="B25" s="41" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C25" s="45"/>
       <c r="D25" s="45"/>
@@ -6310,7 +6492,7 @@
     <row r="26" spans="1:15">
       <c r="A26" s="8"/>
       <c r="B26" s="56" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="C26" s="45"/>
       <c r="D26" s="45"/>
@@ -6329,7 +6511,7 @@
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="56" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="C27" s="45"/>
       <c r="D27" s="45"/>
@@ -6618,7 +6800,7 @@
     <row r="9" spans="1:15">
       <c r="A9" s="34"/>
       <c r="B9" s="34" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="C9" s="34"/>
       <c r="D9" s="34"/>
@@ -7230,12 +7412,12 @@
         <v>46</v>
       </c>
       <c r="I9" s="55"/>
-      <c r="J9" s="154" t="s">
+      <c r="J9" s="153" t="s">
         <v>97</v>
       </c>
-      <c r="K9" s="155"/>
-      <c r="L9" s="155"/>
-      <c r="M9" s="156"/>
+      <c r="K9" s="154"/>
+      <c r="L9" s="154"/>
+      <c r="M9" s="155"/>
       <c r="N9" s="34"/>
       <c r="O9" s="34"/>
     </row>
@@ -7284,12 +7466,12 @@
         <v>46</v>
       </c>
       <c r="I11" s="23"/>
-      <c r="J11" s="151" t="s">
+      <c r="J11" s="150" t="s">
         <v>98</v>
       </c>
-      <c r="K11" s="152"/>
-      <c r="L11" s="152"/>
-      <c r="M11" s="153"/>
+      <c r="K11" s="151"/>
+      <c r="L11" s="151"/>
+      <c r="M11" s="152"/>
       <c r="N11" s="8"/>
       <c r="O11" s="34"/>
     </row>
@@ -7365,12 +7547,12 @@
         <v>46</v>
       </c>
       <c r="I14" s="55"/>
-      <c r="J14" s="146" t="s">
+      <c r="J14" s="145" t="s">
         <v>92</v>
       </c>
-      <c r="K14" s="147"/>
-      <c r="L14" s="147"/>
-      <c r="M14" s="148"/>
+      <c r="K14" s="146"/>
+      <c r="L14" s="146"/>
+      <c r="M14" s="147"/>
       <c r="N14" s="41"/>
       <c r="O14" s="41"/>
     </row>
@@ -7411,7 +7593,7 @@
     <row r="17" spans="1:15">
       <c r="A17" s="34"/>
       <c r="B17" s="41" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="C17" s="41"/>
       <c r="D17" s="41"/>
@@ -7457,7 +7639,7 @@
     <row r="19" spans="1:15">
       <c r="A19" s="34"/>
       <c r="B19" s="52" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="C19" s="55"/>
       <c r="D19" s="52" t="s">
@@ -7484,11 +7666,11 @@
     <row r="20" spans="1:15">
       <c r="A20" s="34"/>
       <c r="B20" s="52" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="C20" s="55"/>
       <c r="D20" s="52" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E20" s="55"/>
       <c r="F20" s="52" t="s">
@@ -7496,11 +7678,11 @@
       </c>
       <c r="G20" s="55"/>
       <c r="H20" s="52" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I20" s="55"/>
       <c r="J20" s="52" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="K20" s="23"/>
       <c r="L20" s="53"/>
@@ -7511,7 +7693,7 @@
     <row r="21" spans="1:15" ht="36" customHeight="1">
       <c r="A21" s="34"/>
       <c r="B21" s="52" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="C21" s="55"/>
       <c r="D21" s="52" t="s">
@@ -7523,7 +7705,7 @@
       </c>
       <c r="G21" s="55"/>
       <c r="H21" s="52" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="I21" s="55"/>
       <c r="J21" s="52"/>
@@ -7536,7 +7718,7 @@
     <row r="22" spans="1:15" ht="18" customHeight="1">
       <c r="A22" s="43"/>
       <c r="B22" s="52" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C22" s="55"/>
       <c r="D22" s="52" t="s">
@@ -7552,7 +7734,7 @@
       </c>
       <c r="I22" s="23"/>
       <c r="J22" s="17" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="K22" s="23"/>
       <c r="L22" s="53"/>
@@ -7632,12 +7814,12 @@
         <v>93</v>
       </c>
       <c r="I25" s="55"/>
-      <c r="J25" s="146" t="s">
+      <c r="J25" s="145" t="s">
         <v>92</v>
       </c>
-      <c r="K25" s="147"/>
-      <c r="L25" s="147"/>
-      <c r="M25" s="148"/>
+      <c r="K25" s="146"/>
+      <c r="L25" s="146"/>
+      <c r="M25" s="147"/>
       <c r="N25" s="56"/>
       <c r="O25" s="56"/>
     </row>
@@ -7827,7 +8009,9 @@
       <c r="N1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="38"/>
+      <c r="O1" s="38">
+        <v>46289</v>
+      </c>
     </row>
     <row r="2" spans="1:16" ht="20">
       <c r="A2" s="89"/>
@@ -7915,50 +8099,42 @@
         <v>1</v>
       </c>
       <c r="C6" s="75" t="s">
-        <v>104</v>
+        <v>181</v>
       </c>
       <c r="D6" s="77"/>
       <c r="E6" s="78"/>
       <c r="F6" s="77"/>
       <c r="G6" s="76"/>
       <c r="H6" s="75" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="I6" s="78"/>
       <c r="J6" s="77"/>
       <c r="K6" s="77"/>
       <c r="L6" s="79"/>
-      <c r="M6" s="151" t="s">
-        <v>106</v>
-      </c>
-      <c r="N6" s="152"/>
-      <c r="O6" s="153"/>
+      <c r="M6" s="150" t="s">
+        <v>182</v>
+      </c>
+      <c r="N6" s="151"/>
+      <c r="O6" s="152"/>
       <c r="P6" s="80"/>
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="34"/>
-      <c r="B7" s="66">
-        <v>2</v>
-      </c>
-      <c r="C7" s="75" t="s">
-        <v>107</v>
-      </c>
+      <c r="B7" s="66"/>
+      <c r="C7" s="75"/>
       <c r="D7" s="77"/>
       <c r="E7" s="78"/>
       <c r="F7" s="77"/>
       <c r="G7" s="76"/>
-      <c r="H7" s="75" t="s">
-        <v>108</v>
-      </c>
+      <c r="H7" s="75"/>
       <c r="I7" s="78"/>
       <c r="J7" s="77"/>
       <c r="K7" s="77"/>
       <c r="L7" s="79"/>
-      <c r="M7" s="157" t="s">
-        <v>109</v>
-      </c>
-      <c r="N7" s="158"/>
-      <c r="O7" s="159"/>
+      <c r="M7" s="156"/>
+      <c r="N7" s="157"/>
+      <c r="O7" s="158"/>
       <c r="P7" s="80"/>
     </row>
     <row r="8" spans="1:16">

--- a/要件定義書（カレンダーアプリ）.xlsx
+++ b/要件定義書（カレンダーアプリ）.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\my_application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72F46712-B132-408E-8C0F-C57958640ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00142C73-0040-4E49-AEDA-29A5D8C77B84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="1" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="1" activeTab="2" xr2:uid="{85519E7B-6A1D-49E1-91A6-FB7B8A7DAF14}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="2" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="184">
   <si>
     <t>要件定義</t>
   </si>
@@ -93,12 +93,6 @@
   </si>
   <si>
     <t>第4章</t>
-  </si>
-  <si>
-    <t>用語の定義</t>
-  </si>
-  <si>
-    <t>業務の概要</t>
   </si>
   <si>
     <t>第2章</t>
@@ -825,13 +819,6 @@
     <t>・【社員情報】</t>
     <rPh sb="2" eb="6">
       <t>シャインジョウホウ</t>
-    </rPh>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
-    <t>・【タスク情報】</t>
-    <rPh sb="5" eb="7">
-      <t>ジョウホウ</t>
     </rPh>
     <phoneticPr fontId="13"/>
   </si>
@@ -1650,6 +1637,13 @@
     </rPh>
     <rPh sb="37" eb="41">
       <t>コウモクテイギ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
+  </si>
+  <si>
+    <t>・【スケジュール情報】</t>
+    <rPh sb="8" eb="10">
+      <t>ジョウホウ</t>
     </rPh>
     <phoneticPr fontId="13"/>
   </si>
@@ -2434,24 +2428,174 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="56" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2470,138 +2614,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="56" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="56" fontId="4" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2629,6 +2641,15 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -2638,15 +2659,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
@@ -2655,24 +2667,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3082,44 +3076,44 @@
       <c r="P5" s="8"/>
     </row>
     <row r="6" spans="1:16" ht="39" customHeight="1">
-      <c r="A6" s="104"/>
-      <c r="B6" s="105"/>
-      <c r="C6" s="103"/>
-      <c r="D6" s="106" t="s">
-        <v>137</v>
-      </c>
-      <c r="E6" s="106"/>
-      <c r="F6" s="106"/>
-      <c r="G6" s="106"/>
-      <c r="H6" s="106"/>
-      <c r="I6" s="106"/>
-      <c r="J6" s="106"/>
-      <c r="K6" s="106"/>
-      <c r="L6" s="106"/>
-      <c r="M6" s="106"/>
-      <c r="N6" s="105"/>
-      <c r="O6" s="103"/>
-      <c r="P6" s="104"/>
+      <c r="A6" s="126"/>
+      <c r="B6" s="127"/>
+      <c r="C6" s="128"/>
+      <c r="D6" s="129" t="s">
+        <v>134</v>
+      </c>
+      <c r="E6" s="129"/>
+      <c r="F6" s="129"/>
+      <c r="G6" s="129"/>
+      <c r="H6" s="129"/>
+      <c r="I6" s="129"/>
+      <c r="J6" s="129"/>
+      <c r="K6" s="129"/>
+      <c r="L6" s="129"/>
+      <c r="M6" s="129"/>
+      <c r="N6" s="127"/>
+      <c r="O6" s="128"/>
+      <c r="P6" s="126"/>
     </row>
     <row r="7" spans="1:16" ht="39" customHeight="1">
-      <c r="A7" s="104"/>
-      <c r="B7" s="105"/>
-      <c r="C7" s="103"/>
-      <c r="D7" s="106" t="s">
+      <c r="A7" s="126"/>
+      <c r="B7" s="127"/>
+      <c r="C7" s="128"/>
+      <c r="D7" s="129" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="106"/>
-      <c r="F7" s="106"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="106"/>
-      <c r="I7" s="106"/>
-      <c r="J7" s="106"/>
-      <c r="K7" s="106"/>
-      <c r="L7" s="106"/>
-      <c r="M7" s="106"/>
-      <c r="N7" s="105"/>
-      <c r="O7" s="103"/>
-      <c r="P7" s="104"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="129"/>
+      <c r="G7" s="129"/>
+      <c r="H7" s="129"/>
+      <c r="I7" s="129"/>
+      <c r="J7" s="129"/>
+      <c r="K7" s="129"/>
+      <c r="L7" s="129"/>
+      <c r="M7" s="129"/>
+      <c r="N7" s="127"/>
+      <c r="O7" s="128"/>
+      <c r="P7" s="126"/>
     </row>
     <row r="8" spans="1:16" ht="18.5" thickBot="1">
       <c r="A8" s="8"/>
@@ -3181,16 +3175,16 @@
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
-      <c r="F11" s="97" t="s">
+      <c r="F11" s="130" t="s">
         <v>2</v>
       </c>
-      <c r="G11" s="98"/>
-      <c r="H11" s="101" t="s">
-        <v>58</v>
-      </c>
-      <c r="I11" s="102"/>
-      <c r="J11" s="102"/>
-      <c r="K11" s="102"/>
+      <c r="G11" s="131"/>
+      <c r="H11" s="132" t="s">
+        <v>56</v>
+      </c>
+      <c r="I11" s="133"/>
+      <c r="J11" s="133"/>
+      <c r="K11" s="133"/>
       <c r="L11" s="7"/>
       <c r="M11" s="7"/>
       <c r="N11" s="7"/>
@@ -3203,16 +3197,16 @@
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
       <c r="E12" s="8"/>
-      <c r="F12" s="97" t="s">
+      <c r="F12" s="130" t="s">
         <v>3</v>
       </c>
-      <c r="G12" s="98"/>
-      <c r="H12" s="99">
+      <c r="G12" s="131"/>
+      <c r="H12" s="134">
         <v>46282</v>
       </c>
-      <c r="I12" s="100"/>
-      <c r="J12" s="100"/>
-      <c r="K12" s="100"/>
+      <c r="I12" s="135"/>
+      <c r="J12" s="135"/>
+      <c r="K12" s="135"/>
       <c r="L12" s="8"/>
       <c r="M12" s="8"/>
       <c r="N12" s="8"/>
@@ -3225,16 +3219,16 @@
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
-      <c r="F13" s="97" t="s">
+      <c r="F13" s="130" t="s">
         <v>10</v>
       </c>
-      <c r="G13" s="98"/>
-      <c r="H13" s="99">
+      <c r="G13" s="131"/>
+      <c r="H13" s="134">
         <v>46289</v>
       </c>
-      <c r="I13" s="100"/>
-      <c r="J13" s="100"/>
-      <c r="K13" s="100"/>
+      <c r="I13" s="135"/>
+      <c r="J13" s="135"/>
+      <c r="K13" s="135"/>
       <c r="L13" s="8"/>
       <c r="M13" s="8"/>
       <c r="N13" s="8"/>
@@ -3247,14 +3241,14 @@
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
       <c r="E14" s="8"/>
-      <c r="F14" s="97" t="s">
+      <c r="F14" s="130" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="98"/>
-      <c r="H14" s="101"/>
-      <c r="I14" s="102"/>
-      <c r="J14" s="102"/>
-      <c r="K14" s="102"/>
+      <c r="G14" s="131"/>
+      <c r="H14" s="132"/>
+      <c r="I14" s="133"/>
+      <c r="J14" s="133"/>
+      <c r="K14" s="133"/>
       <c r="L14" s="8"/>
       <c r="M14" s="8"/>
       <c r="N14" s="8"/>
@@ -3391,22 +3385,22 @@
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="D6:M6"/>
-    <mergeCell ref="D7:M7"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="H13:K13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="H14:K14"/>
+    <mergeCell ref="O6:O7"/>
     <mergeCell ref="P6:P7"/>
     <mergeCell ref="F11:G11"/>
     <mergeCell ref="H11:K11"/>
     <mergeCell ref="F12:G12"/>
     <mergeCell ref="H12:K12"/>
     <mergeCell ref="N6:N7"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="H13:K13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="H14:K14"/>
-    <mergeCell ref="O6:O7"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="D6:M6"/>
+    <mergeCell ref="D7:M7"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3419,56 +3413,56 @@
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData>
     <row r="1" spans="1:18">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="85" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="123"/>
-      <c r="C1" s="88"/>
-      <c r="D1" s="125" t="s">
+      <c r="B1" s="86"/>
+      <c r="C1" s="87"/>
+      <c r="D1" s="91" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="126"/>
-      <c r="F1" s="126"/>
-      <c r="G1" s="126"/>
-      <c r="H1" s="126"/>
-      <c r="I1" s="126"/>
-      <c r="J1" s="126"/>
-      <c r="K1" s="126"/>
-      <c r="L1" s="126"/>
-      <c r="M1" s="126"/>
-      <c r="N1" s="126"/>
-      <c r="O1" s="127"/>
+      <c r="E1" s="92"/>
+      <c r="F1" s="92"/>
+      <c r="G1" s="92"/>
+      <c r="H1" s="92"/>
+      <c r="I1" s="92"/>
+      <c r="J1" s="92"/>
+      <c r="K1" s="92"/>
+      <c r="L1" s="92"/>
+      <c r="M1" s="92"/>
+      <c r="N1" s="92"/>
+      <c r="O1" s="93"/>
       <c r="P1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="Q1" s="131" t="s">
-        <v>103</v>
-      </c>
-      <c r="R1" s="132"/>
+      <c r="Q1" s="97" t="s">
+        <v>101</v>
+      </c>
+      <c r="R1" s="98"/>
     </row>
     <row r="2" spans="1:18">
-      <c r="A2" s="89"/>
-      <c r="B2" s="124"/>
+      <c r="A2" s="88"/>
+      <c r="B2" s="89"/>
       <c r="C2" s="90"/>
-      <c r="D2" s="128"/>
-      <c r="E2" s="129"/>
-      <c r="F2" s="129"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="129"/>
-      <c r="I2" s="129"/>
-      <c r="J2" s="129"/>
-      <c r="K2" s="129"/>
-      <c r="L2" s="129"/>
-      <c r="M2" s="129"/>
-      <c r="N2" s="129"/>
-      <c r="O2" s="130"/>
+      <c r="D2" s="94"/>
+      <c r="E2" s="95"/>
+      <c r="F2" s="95"/>
+      <c r="G2" s="95"/>
+      <c r="H2" s="95"/>
+      <c r="I2" s="95"/>
+      <c r="J2" s="95"/>
+      <c r="K2" s="95"/>
+      <c r="L2" s="95"/>
+      <c r="M2" s="95"/>
+      <c r="N2" s="95"/>
+      <c r="O2" s="96"/>
       <c r="P2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="Q2" s="133">
+      <c r="Q2" s="99">
         <v>46289</v>
       </c>
-      <c r="R2" s="134"/>
+      <c r="R2" s="100"/>
     </row>
     <row r="3" spans="1:18">
       <c r="A3" s="2"/>
@@ -3494,59 +3488,59 @@
       <c r="A4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="135" t="s">
+      <c r="B4" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="136"/>
-      <c r="D4" s="135" t="s">
+      <c r="C4" s="102"/>
+      <c r="D4" s="101" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="136"/>
-      <c r="F4" s="135" t="s">
+      <c r="E4" s="102"/>
+      <c r="F4" s="101" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="137"/>
-      <c r="H4" s="137"/>
-      <c r="I4" s="137"/>
-      <c r="J4" s="136"/>
-      <c r="K4" s="135" t="s">
+      <c r="G4" s="103"/>
+      <c r="H4" s="103"/>
+      <c r="I4" s="103"/>
+      <c r="J4" s="102"/>
+      <c r="K4" s="101" t="s">
         <v>8</v>
       </c>
-      <c r="L4" s="137"/>
-      <c r="M4" s="137"/>
-      <c r="N4" s="137"/>
-      <c r="O4" s="137"/>
-      <c r="P4" s="137"/>
-      <c r="Q4" s="137"/>
-      <c r="R4" s="136"/>
+      <c r="L4" s="103"/>
+      <c r="M4" s="103"/>
+      <c r="N4" s="103"/>
+      <c r="O4" s="103"/>
+      <c r="P4" s="103"/>
+      <c r="Q4" s="103"/>
+      <c r="R4" s="102"/>
     </row>
     <row r="5" spans="1:18">
       <c r="A5" s="4">
         <v>1</v>
       </c>
-      <c r="B5" s="117">
+      <c r="B5" s="104">
         <v>46282</v>
       </c>
-      <c r="C5" s="118"/>
-      <c r="D5" s="119" t="s">
-        <v>183</v>
-      </c>
-      <c r="E5" s="118"/>
-      <c r="F5" s="159" t="s">
-        <v>184</v>
-      </c>
-      <c r="G5" s="160"/>
-      <c r="H5" s="160"/>
-      <c r="I5" s="160"/>
-      <c r="J5" s="161"/>
-      <c r="K5" s="120"/>
-      <c r="L5" s="121"/>
-      <c r="M5" s="121"/>
-      <c r="N5" s="121"/>
-      <c r="O5" s="121"/>
-      <c r="P5" s="121"/>
-      <c r="Q5" s="121"/>
-      <c r="R5" s="122"/>
+      <c r="C5" s="105"/>
+      <c r="D5" s="106" t="s">
+        <v>180</v>
+      </c>
+      <c r="E5" s="105"/>
+      <c r="F5" s="107" t="s">
+        <v>181</v>
+      </c>
+      <c r="G5" s="108"/>
+      <c r="H5" s="108"/>
+      <c r="I5" s="108"/>
+      <c r="J5" s="109"/>
+      <c r="K5" s="110"/>
+      <c r="L5" s="111"/>
+      <c r="M5" s="111"/>
+      <c r="N5" s="111"/>
+      <c r="O5" s="111"/>
+      <c r="P5" s="111"/>
+      <c r="Q5" s="111"/>
+      <c r="R5" s="112"/>
     </row>
     <row r="6" spans="1:18" ht="90" customHeight="1">
       <c r="A6" s="6">
@@ -3555,378 +3549,378 @@
       <c r="B6" s="113">
         <v>46289</v>
       </c>
-      <c r="C6" s="108"/>
-      <c r="D6" s="107" t="s">
-        <v>183</v>
-      </c>
-      <c r="E6" s="108"/>
-      <c r="F6" s="162" t="s">
-        <v>185</v>
-      </c>
-      <c r="G6" s="163"/>
-      <c r="H6" s="163"/>
-      <c r="I6" s="163"/>
-      <c r="J6" s="164"/>
-      <c r="K6" s="110"/>
-      <c r="L6" s="111"/>
-      <c r="M6" s="111"/>
-      <c r="N6" s="111"/>
-      <c r="O6" s="111"/>
-      <c r="P6" s="111"/>
-      <c r="Q6" s="111"/>
-      <c r="R6" s="112"/>
+      <c r="C6" s="114"/>
+      <c r="D6" s="115" t="s">
+        <v>180</v>
+      </c>
+      <c r="E6" s="114"/>
+      <c r="F6" s="116" t="s">
+        <v>182</v>
+      </c>
+      <c r="G6" s="117"/>
+      <c r="H6" s="117"/>
+      <c r="I6" s="117"/>
+      <c r="J6" s="118"/>
+      <c r="K6" s="119"/>
+      <c r="L6" s="120"/>
+      <c r="M6" s="120"/>
+      <c r="N6" s="120"/>
+      <c r="O6" s="120"/>
+      <c r="P6" s="120"/>
+      <c r="Q6" s="120"/>
+      <c r="R6" s="121"/>
     </row>
     <row r="7" spans="1:18">
       <c r="A7" s="6">
         <v>3</v>
       </c>
       <c r="B7" s="113"/>
-      <c r="C7" s="108"/>
-      <c r="D7" s="107"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="110"/>
-      <c r="G7" s="111"/>
-      <c r="H7" s="111"/>
-      <c r="I7" s="111"/>
-      <c r="J7" s="112"/>
-      <c r="K7" s="110"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
-      <c r="N7" s="111"/>
-      <c r="O7" s="111"/>
-      <c r="P7" s="111"/>
-      <c r="Q7" s="111"/>
-      <c r="R7" s="112"/>
+      <c r="C7" s="114"/>
+      <c r="D7" s="115"/>
+      <c r="E7" s="114"/>
+      <c r="F7" s="119"/>
+      <c r="G7" s="120"/>
+      <c r="H7" s="120"/>
+      <c r="I7" s="120"/>
+      <c r="J7" s="121"/>
+      <c r="K7" s="119"/>
+      <c r="L7" s="120"/>
+      <c r="M7" s="120"/>
+      <c r="N7" s="120"/>
+      <c r="O7" s="120"/>
+      <c r="P7" s="120"/>
+      <c r="Q7" s="120"/>
+      <c r="R7" s="121"/>
     </row>
     <row r="8" spans="1:18">
       <c r="A8" s="6">
         <v>4</v>
       </c>
       <c r="B8" s="113"/>
-      <c r="C8" s="108"/>
-      <c r="D8" s="107"/>
-      <c r="E8" s="108"/>
-      <c r="F8" s="110"/>
-      <c r="G8" s="111"/>
-      <c r="H8" s="111"/>
-      <c r="I8" s="111"/>
-      <c r="J8" s="112"/>
-      <c r="K8" s="110"/>
-      <c r="L8" s="111"/>
-      <c r="M8" s="111"/>
-      <c r="N8" s="111"/>
-      <c r="O8" s="111"/>
-      <c r="P8" s="111"/>
-      <c r="Q8" s="111"/>
-      <c r="R8" s="112"/>
+      <c r="C8" s="114"/>
+      <c r="D8" s="115"/>
+      <c r="E8" s="114"/>
+      <c r="F8" s="119"/>
+      <c r="G8" s="120"/>
+      <c r="H8" s="120"/>
+      <c r="I8" s="120"/>
+      <c r="J8" s="121"/>
+      <c r="K8" s="119"/>
+      <c r="L8" s="120"/>
+      <c r="M8" s="120"/>
+      <c r="N8" s="120"/>
+      <c r="O8" s="120"/>
+      <c r="P8" s="120"/>
+      <c r="Q8" s="120"/>
+      <c r="R8" s="121"/>
     </row>
     <row r="9" spans="1:18">
       <c r="A9" s="6">
         <v>5</v>
       </c>
       <c r="B9" s="113"/>
-      <c r="C9" s="108"/>
-      <c r="D9" s="107"/>
-      <c r="E9" s="108"/>
-      <c r="F9" s="114"/>
-      <c r="G9" s="115"/>
-      <c r="H9" s="115"/>
-      <c r="I9" s="115"/>
-      <c r="J9" s="116"/>
-      <c r="K9" s="110"/>
-      <c r="L9" s="111"/>
-      <c r="M9" s="111"/>
-      <c r="N9" s="111"/>
-      <c r="O9" s="111"/>
-      <c r="P9" s="111"/>
-      <c r="Q9" s="111"/>
-      <c r="R9" s="112"/>
+      <c r="C9" s="114"/>
+      <c r="D9" s="115"/>
+      <c r="E9" s="114"/>
+      <c r="F9" s="122"/>
+      <c r="G9" s="123"/>
+      <c r="H9" s="123"/>
+      <c r="I9" s="123"/>
+      <c r="J9" s="124"/>
+      <c r="K9" s="119"/>
+      <c r="L9" s="120"/>
+      <c r="M9" s="120"/>
+      <c r="N9" s="120"/>
+      <c r="O9" s="120"/>
+      <c r="P9" s="120"/>
+      <c r="Q9" s="120"/>
+      <c r="R9" s="121"/>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="6">
         <v>6</v>
       </c>
-      <c r="B10" s="107"/>
-      <c r="C10" s="108"/>
-      <c r="D10" s="107"/>
-      <c r="E10" s="108"/>
-      <c r="F10" s="107"/>
-      <c r="G10" s="109"/>
-      <c r="H10" s="109"/>
-      <c r="I10" s="109"/>
-      <c r="J10" s="108"/>
-      <c r="K10" s="110"/>
-      <c r="L10" s="111"/>
-      <c r="M10" s="111"/>
-      <c r="N10" s="111"/>
-      <c r="O10" s="111"/>
-      <c r="P10" s="111"/>
-      <c r="Q10" s="111"/>
-      <c r="R10" s="112"/>
+      <c r="B10" s="115"/>
+      <c r="C10" s="114"/>
+      <c r="D10" s="115"/>
+      <c r="E10" s="114"/>
+      <c r="F10" s="115"/>
+      <c r="G10" s="125"/>
+      <c r="H10" s="125"/>
+      <c r="I10" s="125"/>
+      <c r="J10" s="114"/>
+      <c r="K10" s="119"/>
+      <c r="L10" s="120"/>
+      <c r="M10" s="120"/>
+      <c r="N10" s="120"/>
+      <c r="O10" s="120"/>
+      <c r="P10" s="120"/>
+      <c r="Q10" s="120"/>
+      <c r="R10" s="121"/>
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="6">
         <v>7</v>
       </c>
-      <c r="B11" s="107"/>
-      <c r="C11" s="108"/>
-      <c r="D11" s="107"/>
-      <c r="E11" s="108"/>
-      <c r="F11" s="107"/>
-      <c r="G11" s="109"/>
-      <c r="H11" s="109"/>
-      <c r="I11" s="109"/>
-      <c r="J11" s="108"/>
-      <c r="K11" s="110"/>
-      <c r="L11" s="111"/>
-      <c r="M11" s="111"/>
-      <c r="N11" s="111"/>
-      <c r="O11" s="111"/>
-      <c r="P11" s="111"/>
-      <c r="Q11" s="111"/>
-      <c r="R11" s="112"/>
+      <c r="B11" s="115"/>
+      <c r="C11" s="114"/>
+      <c r="D11" s="115"/>
+      <c r="E11" s="114"/>
+      <c r="F11" s="115"/>
+      <c r="G11" s="125"/>
+      <c r="H11" s="125"/>
+      <c r="I11" s="125"/>
+      <c r="J11" s="114"/>
+      <c r="K11" s="119"/>
+      <c r="L11" s="120"/>
+      <c r="M11" s="120"/>
+      <c r="N11" s="120"/>
+      <c r="O11" s="120"/>
+      <c r="P11" s="120"/>
+      <c r="Q11" s="120"/>
+      <c r="R11" s="121"/>
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="6">
         <v>8</v>
       </c>
-      <c r="B12" s="107"/>
-      <c r="C12" s="108"/>
-      <c r="D12" s="107"/>
-      <c r="E12" s="108"/>
-      <c r="F12" s="107"/>
-      <c r="G12" s="109"/>
-      <c r="H12" s="109"/>
-      <c r="I12" s="109"/>
-      <c r="J12" s="108"/>
-      <c r="K12" s="110"/>
-      <c r="L12" s="111"/>
-      <c r="M12" s="111"/>
-      <c r="N12" s="111"/>
-      <c r="O12" s="111"/>
-      <c r="P12" s="111"/>
-      <c r="Q12" s="111"/>
-      <c r="R12" s="112"/>
+      <c r="B12" s="115"/>
+      <c r="C12" s="114"/>
+      <c r="D12" s="115"/>
+      <c r="E12" s="114"/>
+      <c r="F12" s="115"/>
+      <c r="G12" s="125"/>
+      <c r="H12" s="125"/>
+      <c r="I12" s="125"/>
+      <c r="J12" s="114"/>
+      <c r="K12" s="119"/>
+      <c r="L12" s="120"/>
+      <c r="M12" s="120"/>
+      <c r="N12" s="120"/>
+      <c r="O12" s="120"/>
+      <c r="P12" s="120"/>
+      <c r="Q12" s="120"/>
+      <c r="R12" s="121"/>
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="6">
         <v>9</v>
       </c>
-      <c r="B13" s="107"/>
-      <c r="C13" s="108"/>
-      <c r="D13" s="107"/>
-      <c r="E13" s="108"/>
-      <c r="F13" s="107"/>
-      <c r="G13" s="109"/>
-      <c r="H13" s="109"/>
-      <c r="I13" s="109"/>
-      <c r="J13" s="108"/>
-      <c r="K13" s="110"/>
-      <c r="L13" s="111"/>
-      <c r="M13" s="111"/>
-      <c r="N13" s="111"/>
-      <c r="O13" s="111"/>
-      <c r="P13" s="111"/>
-      <c r="Q13" s="111"/>
-      <c r="R13" s="112"/>
+      <c r="B13" s="115"/>
+      <c r="C13" s="114"/>
+      <c r="D13" s="115"/>
+      <c r="E13" s="114"/>
+      <c r="F13" s="115"/>
+      <c r="G13" s="125"/>
+      <c r="H13" s="125"/>
+      <c r="I13" s="125"/>
+      <c r="J13" s="114"/>
+      <c r="K13" s="119"/>
+      <c r="L13" s="120"/>
+      <c r="M13" s="120"/>
+      <c r="N13" s="120"/>
+      <c r="O13" s="120"/>
+      <c r="P13" s="120"/>
+      <c r="Q13" s="120"/>
+      <c r="R13" s="121"/>
     </row>
     <row r="14" spans="1:18">
       <c r="A14" s="6">
         <v>10</v>
       </c>
-      <c r="B14" s="107"/>
-      <c r="C14" s="108"/>
-      <c r="D14" s="107"/>
-      <c r="E14" s="108"/>
-      <c r="F14" s="107"/>
-      <c r="G14" s="109"/>
-      <c r="H14" s="109"/>
-      <c r="I14" s="109"/>
-      <c r="J14" s="108"/>
-      <c r="K14" s="110"/>
-      <c r="L14" s="111"/>
-      <c r="M14" s="111"/>
-      <c r="N14" s="111"/>
-      <c r="O14" s="111"/>
-      <c r="P14" s="111"/>
-      <c r="Q14" s="111"/>
-      <c r="R14" s="112"/>
+      <c r="B14" s="115"/>
+      <c r="C14" s="114"/>
+      <c r="D14" s="115"/>
+      <c r="E14" s="114"/>
+      <c r="F14" s="115"/>
+      <c r="G14" s="125"/>
+      <c r="H14" s="125"/>
+      <c r="I14" s="125"/>
+      <c r="J14" s="114"/>
+      <c r="K14" s="119"/>
+      <c r="L14" s="120"/>
+      <c r="M14" s="120"/>
+      <c r="N14" s="120"/>
+      <c r="O14" s="120"/>
+      <c r="P14" s="120"/>
+      <c r="Q14" s="120"/>
+      <c r="R14" s="121"/>
     </row>
     <row r="15" spans="1:18">
       <c r="A15" s="6">
         <v>11</v>
       </c>
-      <c r="B15" s="107"/>
-      <c r="C15" s="108"/>
-      <c r="D15" s="107"/>
-      <c r="E15" s="108"/>
-      <c r="F15" s="107"/>
-      <c r="G15" s="109"/>
-      <c r="H15" s="109"/>
-      <c r="I15" s="109"/>
-      <c r="J15" s="108"/>
-      <c r="K15" s="110"/>
-      <c r="L15" s="111"/>
-      <c r="M15" s="111"/>
-      <c r="N15" s="111"/>
-      <c r="O15" s="111"/>
-      <c r="P15" s="111"/>
-      <c r="Q15" s="111"/>
-      <c r="R15" s="112"/>
+      <c r="B15" s="115"/>
+      <c r="C15" s="114"/>
+      <c r="D15" s="115"/>
+      <c r="E15" s="114"/>
+      <c r="F15" s="115"/>
+      <c r="G15" s="125"/>
+      <c r="H15" s="125"/>
+      <c r="I15" s="125"/>
+      <c r="J15" s="114"/>
+      <c r="K15" s="119"/>
+      <c r="L15" s="120"/>
+      <c r="M15" s="120"/>
+      <c r="N15" s="120"/>
+      <c r="O15" s="120"/>
+      <c r="P15" s="120"/>
+      <c r="Q15" s="120"/>
+      <c r="R15" s="121"/>
     </row>
     <row r="16" spans="1:18">
       <c r="A16" s="6">
         <v>12</v>
       </c>
-      <c r="B16" s="107"/>
-      <c r="C16" s="108"/>
-      <c r="D16" s="107"/>
-      <c r="E16" s="108"/>
-      <c r="F16" s="107"/>
-      <c r="G16" s="109"/>
-      <c r="H16" s="109"/>
-      <c r="I16" s="109"/>
-      <c r="J16" s="108"/>
-      <c r="K16" s="110"/>
-      <c r="L16" s="111"/>
-      <c r="M16" s="111"/>
-      <c r="N16" s="111"/>
-      <c r="O16" s="111"/>
-      <c r="P16" s="111"/>
-      <c r="Q16" s="111"/>
-      <c r="R16" s="112"/>
+      <c r="B16" s="115"/>
+      <c r="C16" s="114"/>
+      <c r="D16" s="115"/>
+      <c r="E16" s="114"/>
+      <c r="F16" s="115"/>
+      <c r="G16" s="125"/>
+      <c r="H16" s="125"/>
+      <c r="I16" s="125"/>
+      <c r="J16" s="114"/>
+      <c r="K16" s="119"/>
+      <c r="L16" s="120"/>
+      <c r="M16" s="120"/>
+      <c r="N16" s="120"/>
+      <c r="O16" s="120"/>
+      <c r="P16" s="120"/>
+      <c r="Q16" s="120"/>
+      <c r="R16" s="121"/>
     </row>
     <row r="17" spans="1:18">
       <c r="A17" s="6">
         <v>13</v>
       </c>
-      <c r="B17" s="107"/>
-      <c r="C17" s="108"/>
-      <c r="D17" s="107"/>
-      <c r="E17" s="108"/>
-      <c r="F17" s="107"/>
-      <c r="G17" s="109"/>
-      <c r="H17" s="109"/>
-      <c r="I17" s="109"/>
-      <c r="J17" s="108"/>
-      <c r="K17" s="110"/>
-      <c r="L17" s="111"/>
-      <c r="M17" s="111"/>
-      <c r="N17" s="111"/>
-      <c r="O17" s="111"/>
-      <c r="P17" s="111"/>
-      <c r="Q17" s="111"/>
-      <c r="R17" s="112"/>
+      <c r="B17" s="115"/>
+      <c r="C17" s="114"/>
+      <c r="D17" s="115"/>
+      <c r="E17" s="114"/>
+      <c r="F17" s="115"/>
+      <c r="G17" s="125"/>
+      <c r="H17" s="125"/>
+      <c r="I17" s="125"/>
+      <c r="J17" s="114"/>
+      <c r="K17" s="119"/>
+      <c r="L17" s="120"/>
+      <c r="M17" s="120"/>
+      <c r="N17" s="120"/>
+      <c r="O17" s="120"/>
+      <c r="P17" s="120"/>
+      <c r="Q17" s="120"/>
+      <c r="R17" s="121"/>
     </row>
     <row r="18" spans="1:18">
       <c r="A18" s="6">
         <v>14</v>
       </c>
-      <c r="B18" s="107"/>
-      <c r="C18" s="108"/>
-      <c r="D18" s="107"/>
-      <c r="E18" s="108"/>
-      <c r="F18" s="107"/>
-      <c r="G18" s="109"/>
-      <c r="H18" s="109"/>
-      <c r="I18" s="109"/>
-      <c r="J18" s="108"/>
-      <c r="K18" s="110"/>
-      <c r="L18" s="111"/>
-      <c r="M18" s="111"/>
-      <c r="N18" s="111"/>
-      <c r="O18" s="111"/>
-      <c r="P18" s="111"/>
-      <c r="Q18" s="111"/>
-      <c r="R18" s="112"/>
+      <c r="B18" s="115"/>
+      <c r="C18" s="114"/>
+      <c r="D18" s="115"/>
+      <c r="E18" s="114"/>
+      <c r="F18" s="115"/>
+      <c r="G18" s="125"/>
+      <c r="H18" s="125"/>
+      <c r="I18" s="125"/>
+      <c r="J18" s="114"/>
+      <c r="K18" s="119"/>
+      <c r="L18" s="120"/>
+      <c r="M18" s="120"/>
+      <c r="N18" s="120"/>
+      <c r="O18" s="120"/>
+      <c r="P18" s="120"/>
+      <c r="Q18" s="120"/>
+      <c r="R18" s="121"/>
     </row>
     <row r="19" spans="1:18">
       <c r="A19" s="6">
         <v>15</v>
       </c>
-      <c r="B19" s="107"/>
-      <c r="C19" s="108"/>
-      <c r="D19" s="107"/>
-      <c r="E19" s="108"/>
-      <c r="F19" s="107"/>
-      <c r="G19" s="109"/>
-      <c r="H19" s="109"/>
-      <c r="I19" s="109"/>
-      <c r="J19" s="108"/>
-      <c r="K19" s="110"/>
-      <c r="L19" s="111"/>
-      <c r="M19" s="111"/>
-      <c r="N19" s="111"/>
-      <c r="O19" s="111"/>
-      <c r="P19" s="111"/>
-      <c r="Q19" s="111"/>
-      <c r="R19" s="112"/>
+      <c r="B19" s="115"/>
+      <c r="C19" s="114"/>
+      <c r="D19" s="115"/>
+      <c r="E19" s="114"/>
+      <c r="F19" s="115"/>
+      <c r="G19" s="125"/>
+      <c r="H19" s="125"/>
+      <c r="I19" s="125"/>
+      <c r="J19" s="114"/>
+      <c r="K19" s="119"/>
+      <c r="L19" s="120"/>
+      <c r="M19" s="120"/>
+      <c r="N19" s="120"/>
+      <c r="O19" s="120"/>
+      <c r="P19" s="120"/>
+      <c r="Q19" s="120"/>
+      <c r="R19" s="121"/>
     </row>
     <row r="20" spans="1:18">
       <c r="A20" s="6">
         <v>16</v>
       </c>
-      <c r="B20" s="107"/>
-      <c r="C20" s="108"/>
-      <c r="D20" s="107"/>
-      <c r="E20" s="108"/>
-      <c r="F20" s="107"/>
-      <c r="G20" s="109"/>
-      <c r="H20" s="109"/>
-      <c r="I20" s="109"/>
-      <c r="J20" s="108"/>
-      <c r="K20" s="110"/>
-      <c r="L20" s="111"/>
-      <c r="M20" s="111"/>
-      <c r="N20" s="111"/>
-      <c r="O20" s="111"/>
-      <c r="P20" s="111"/>
-      <c r="Q20" s="111"/>
-      <c r="R20" s="112"/>
+      <c r="B20" s="115"/>
+      <c r="C20" s="114"/>
+      <c r="D20" s="115"/>
+      <c r="E20" s="114"/>
+      <c r="F20" s="115"/>
+      <c r="G20" s="125"/>
+      <c r="H20" s="125"/>
+      <c r="I20" s="125"/>
+      <c r="J20" s="114"/>
+      <c r="K20" s="119"/>
+      <c r="L20" s="120"/>
+      <c r="M20" s="120"/>
+      <c r="N20" s="120"/>
+      <c r="O20" s="120"/>
+      <c r="P20" s="120"/>
+      <c r="Q20" s="120"/>
+      <c r="R20" s="121"/>
     </row>
     <row r="21" spans="1:18">
       <c r="A21" s="6">
         <v>17</v>
       </c>
-      <c r="B21" s="107"/>
-      <c r="C21" s="108"/>
-      <c r="D21" s="107"/>
-      <c r="E21" s="108"/>
-      <c r="F21" s="107"/>
-      <c r="G21" s="109"/>
-      <c r="H21" s="109"/>
-      <c r="I21" s="109"/>
-      <c r="J21" s="108"/>
-      <c r="K21" s="110"/>
-      <c r="L21" s="111"/>
-      <c r="M21" s="111"/>
-      <c r="N21" s="111"/>
-      <c r="O21" s="111"/>
-      <c r="P21" s="111"/>
-      <c r="Q21" s="111"/>
-      <c r="R21" s="112"/>
+      <c r="B21" s="115"/>
+      <c r="C21" s="114"/>
+      <c r="D21" s="115"/>
+      <c r="E21" s="114"/>
+      <c r="F21" s="115"/>
+      <c r="G21" s="125"/>
+      <c r="H21" s="125"/>
+      <c r="I21" s="125"/>
+      <c r="J21" s="114"/>
+      <c r="K21" s="119"/>
+      <c r="L21" s="120"/>
+      <c r="M21" s="120"/>
+      <c r="N21" s="120"/>
+      <c r="O21" s="120"/>
+      <c r="P21" s="120"/>
+      <c r="Q21" s="120"/>
+      <c r="R21" s="121"/>
     </row>
     <row r="22" spans="1:18">
       <c r="A22" s="6">
         <v>18</v>
       </c>
-      <c r="B22" s="107"/>
-      <c r="C22" s="108"/>
-      <c r="D22" s="107"/>
-      <c r="E22" s="108"/>
-      <c r="F22" s="107"/>
-      <c r="G22" s="109"/>
-      <c r="H22" s="109"/>
-      <c r="I22" s="109"/>
-      <c r="J22" s="108"/>
-      <c r="K22" s="110"/>
-      <c r="L22" s="111"/>
-      <c r="M22" s="111"/>
-      <c r="N22" s="111"/>
-      <c r="O22" s="111"/>
-      <c r="P22" s="111"/>
-      <c r="Q22" s="111"/>
-      <c r="R22" s="112"/>
+      <c r="B22" s="115"/>
+      <c r="C22" s="114"/>
+      <c r="D22" s="115"/>
+      <c r="E22" s="114"/>
+      <c r="F22" s="115"/>
+      <c r="G22" s="125"/>
+      <c r="H22" s="125"/>
+      <c r="I22" s="125"/>
+      <c r="J22" s="114"/>
+      <c r="K22" s="119"/>
+      <c r="L22" s="120"/>
+      <c r="M22" s="120"/>
+      <c r="N22" s="120"/>
+      <c r="O22" s="120"/>
+      <c r="P22" s="120"/>
+      <c r="Q22" s="120"/>
+      <c r="R22" s="121"/>
     </row>
     <row r="23" spans="1:18">
       <c r="A23" s="5"/>
@@ -4070,6 +4064,78 @@
     </row>
   </sheetData>
   <mergeCells count="80">
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:J21"/>
+    <mergeCell ref="K21:R21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:J22"/>
+    <mergeCell ref="K22:R22"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:J19"/>
+    <mergeCell ref="K19:R19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:J20"/>
+    <mergeCell ref="K20:R20"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:J17"/>
+    <mergeCell ref="K17:R17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:J18"/>
+    <mergeCell ref="K18:R18"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:J15"/>
+    <mergeCell ref="K15:R15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:J16"/>
+    <mergeCell ref="K16:R16"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="K13:R13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:J14"/>
+    <mergeCell ref="K14:R14"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="F11:J11"/>
+    <mergeCell ref="K11:R11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="F12:J12"/>
+    <mergeCell ref="K12:R12"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="F9:J9"/>
+    <mergeCell ref="K9:R9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="F10:J10"/>
+    <mergeCell ref="K10:R10"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="F7:J7"/>
+    <mergeCell ref="K7:R7"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:J8"/>
+    <mergeCell ref="K8:R8"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:J5"/>
+    <mergeCell ref="K5:R5"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="D6:E6"/>
+    <mergeCell ref="F6:J6"/>
+    <mergeCell ref="K6:R6"/>
     <mergeCell ref="A1:C2"/>
     <mergeCell ref="D1:O2"/>
     <mergeCell ref="Q1:R1"/>
@@ -4078,78 +4144,6 @@
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="F4:J4"/>
     <mergeCell ref="K4:R4"/>
-    <mergeCell ref="B5:C5"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:J5"/>
-    <mergeCell ref="K5:R5"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="D6:E6"/>
-    <mergeCell ref="F6:J6"/>
-    <mergeCell ref="K6:R6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="F7:J7"/>
-    <mergeCell ref="K7:R7"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:J8"/>
-    <mergeCell ref="K8:R8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="F9:J9"/>
-    <mergeCell ref="K9:R9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="F10:J10"/>
-    <mergeCell ref="K10:R10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="F11:J11"/>
-    <mergeCell ref="K11:R11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="K12:R12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="K13:R13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:J14"/>
-    <mergeCell ref="K14:R14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:J15"/>
-    <mergeCell ref="K15:R15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="K16:R16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:J17"/>
-    <mergeCell ref="K17:R17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:J18"/>
-    <mergeCell ref="K18:R18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:J19"/>
-    <mergeCell ref="K19:R19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:J20"/>
-    <mergeCell ref="K20:R20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:J21"/>
-    <mergeCell ref="K21:R21"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:J22"/>
-    <mergeCell ref="K22:R22"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4158,53 +4152,55 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDFF7F1E-AE30-4269-AC6F-F8A3C5E0A4BA}">
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P22"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
     <col min="16" max="16" width="10" style="84" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="87" t="s">
+      <c r="B1" s="87"/>
+      <c r="C1" s="85" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="123"/>
-      <c r="E1" s="123"/>
-      <c r="F1" s="123"/>
-      <c r="G1" s="123"/>
-      <c r="H1" s="123"/>
-      <c r="I1" s="123"/>
-      <c r="J1" s="123"/>
-      <c r="K1" s="123"/>
-      <c r="L1" s="123"/>
+      <c r="D1" s="86"/>
+      <c r="E1" s="86"/>
+      <c r="F1" s="86"/>
+      <c r="G1" s="86"/>
+      <c r="H1" s="86"/>
+      <c r="I1" s="86"/>
+      <c r="J1" s="86"/>
+      <c r="K1" s="86"/>
+      <c r="L1" s="86"/>
       <c r="M1" s="24" t="s">
         <v>2</v>
       </c>
       <c r="N1" s="22" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="O1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="P1" s="83"/>
+      <c r="P1" s="83">
+        <v>46294</v>
+      </c>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" s="89"/>
+      <c r="A2" s="88"/>
       <c r="B2" s="90"/>
-      <c r="C2" s="89"/>
-      <c r="D2" s="124"/>
-      <c r="E2" s="124"/>
-      <c r="F2" s="124"/>
-      <c r="G2" s="124"/>
-      <c r="H2" s="124"/>
-      <c r="I2" s="124"/>
-      <c r="J2" s="124"/>
-      <c r="K2" s="124"/>
-      <c r="L2" s="124"/>
+      <c r="C2" s="88"/>
+      <c r="D2" s="89"/>
+      <c r="E2" s="89"/>
+      <c r="F2" s="89"/>
+      <c r="G2" s="89"/>
+      <c r="H2" s="89"/>
+      <c r="I2" s="89"/>
+      <c r="J2" s="89"/>
+      <c r="K2" s="89"/>
+      <c r="L2" s="89"/>
       <c r="M2" s="27" t="s">
         <v>14</v>
       </c>
@@ -4235,26 +4231,26 @@
       <c r="A4" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="B4" s="138" t="s">
+      <c r="B4" s="136" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="139"/>
-      <c r="D4" s="139"/>
-      <c r="E4" s="139"/>
-      <c r="F4" s="139"/>
-      <c r="G4" s="140"/>
+      <c r="C4" s="137"/>
+      <c r="D4" s="137"/>
+      <c r="E4" s="137"/>
+      <c r="F4" s="137"/>
+      <c r="G4" s="138"/>
       <c r="H4" s="30"/>
       <c r="I4" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="J4" s="138" t="s">
+      <c r="J4" s="136" t="s">
         <v>17</v>
       </c>
-      <c r="K4" s="139"/>
-      <c r="L4" s="139"/>
-      <c r="M4" s="139"/>
-      <c r="N4" s="139"/>
-      <c r="O4" s="140"/>
+      <c r="K4" s="137"/>
+      <c r="L4" s="137"/>
+      <c r="M4" s="137"/>
+      <c r="N4" s="137"/>
+      <c r="O4" s="138"/>
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="16"/>
@@ -4278,7 +4274,7 @@
         <v>18</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C6" s="30"/>
       <c r="D6" s="30"/>
@@ -4286,10 +4282,10 @@
       <c r="F6" s="30"/>
       <c r="G6" s="30"/>
       <c r="I6" s="35" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="J6" s="30" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K6" s="30"/>
       <c r="L6" s="30"/>
@@ -4299,10 +4295,10 @@
     </row>
     <row r="7" spans="1:16">
       <c r="A7" s="81" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C7" s="30"/>
       <c r="D7" s="30"/>
@@ -4310,10 +4306,10 @@
       <c r="F7" s="30"/>
       <c r="G7" s="30"/>
       <c r="I7" s="81" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="J7" s="30" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="K7" s="30"/>
       <c r="L7" s="30"/>
@@ -4323,10 +4319,10 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="81" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="B8" s="34" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C8" s="34"/>
       <c r="D8" s="34"/>
@@ -4334,10 +4330,10 @@
       <c r="F8" s="34"/>
       <c r="G8" s="34"/>
       <c r="I8" s="81" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J8" s="34" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="K8" s="34"/>
       <c r="L8" s="34"/>
@@ -4347,10 +4343,10 @@
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="81" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C9" s="30"/>
       <c r="D9" s="30"/>
@@ -4358,10 +4354,10 @@
       <c r="F9" s="30"/>
       <c r="G9" s="30"/>
       <c r="I9" s="81" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="J9" s="30" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="K9" s="30"/>
       <c r="L9" s="30"/>
@@ -4371,10 +4367,10 @@
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="81" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C10" s="30"/>
       <c r="D10" s="30"/>
@@ -4391,7 +4387,7 @@
         <v>1.5</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C11" s="30"/>
       <c r="D11" s="30"/>
@@ -4399,7 +4395,7 @@
       <c r="F11" s="30"/>
       <c r="G11" s="30"/>
       <c r="I11" s="35" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="J11" s="30"/>
       <c r="K11" s="30"/>
@@ -4417,10 +4413,10 @@
       <c r="F12" s="30"/>
       <c r="G12" s="30"/>
       <c r="I12" s="82" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J12" s="30" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="K12" s="30"/>
       <c r="L12" s="30"/>
@@ -4430,10 +4426,10 @@
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="35" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C13" s="30"/>
       <c r="D13" s="30"/>
@@ -4442,7 +4438,7 @@
       <c r="G13" s="30"/>
       <c r="I13" s="35"/>
       <c r="J13" s="30" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="K13" s="30"/>
       <c r="L13" s="30"/>
@@ -4452,10 +4448,10 @@
     </row>
     <row r="14" spans="1:16">
       <c r="A14" s="82" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C14" s="30"/>
       <c r="D14" s="30"/>
@@ -4463,7 +4459,7 @@
       <c r="F14" s="30"/>
       <c r="G14" s="30"/>
       <c r="J14" s="30" t="s">
-        <v>136</v>
+        <v>183</v>
       </c>
       <c r="K14" s="30"/>
       <c r="L14" s="30"/>
@@ -4488,10 +4484,10 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="35" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="C16" s="30"/>
       <c r="D16" s="30"/>
@@ -4500,7 +4496,7 @@
       <c r="G16" s="30"/>
       <c r="H16" s="7"/>
       <c r="I16" s="16" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="J16" s="30"/>
       <c r="K16" s="30"/>
@@ -4511,10 +4507,10 @@
     </row>
     <row r="17" spans="1:15" ht="26.5">
       <c r="A17" s="82" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="B17" s="30" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C17" s="30"/>
       <c r="D17" s="30"/>
@@ -4523,10 +4519,10 @@
       <c r="G17" s="30"/>
       <c r="H17" s="7"/>
       <c r="I17" s="82" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="J17" s="30" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="K17" s="36"/>
       <c r="L17" s="36"/>
@@ -4536,10 +4532,10 @@
     </row>
     <row r="18" spans="1:15" ht="26.5">
       <c r="A18" s="82" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B18" s="34" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C18" s="34"/>
       <c r="D18" s="34"/>
@@ -4573,17 +4569,13 @@
       <c r="O19" s="36"/>
     </row>
     <row r="20" spans="1:15" ht="26.5">
-      <c r="A20" s="35">
-        <v>3.2</v>
-      </c>
-      <c r="B20" s="34" t="s">
-        <v>20</v>
-      </c>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
+      <c r="A20" s="36"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="16"/>
       <c r="H20" s="7"/>
       <c r="I20" s="7"/>
       <c r="J20" s="36"/>
@@ -4594,19 +4586,15 @@
       <c r="O20" s="36"/>
     </row>
     <row r="21" spans="1:15" ht="26.5">
-      <c r="A21" s="35">
-        <v>3.3</v>
-      </c>
-      <c r="B21" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="30"/>
-      <c r="F21" s="30"/>
-      <c r="G21" s="30"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
+      <c r="A21" s="36"/>
+      <c r="B21" s="37"/>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="37"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="36"/>
       <c r="J21" s="36"/>
       <c r="K21" s="36"/>
       <c r="L21" s="36"/>
@@ -4614,8 +4602,8 @@
       <c r="N21" s="36"/>
       <c r="O21" s="36"/>
     </row>
-    <row r="22" spans="1:15" ht="26.5">
-      <c r="A22" s="36"/>
+    <row r="22" spans="1:15">
+      <c r="A22" s="7"/>
       <c r="B22" s="16"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
@@ -4624,46 +4612,12 @@
       <c r="G22" s="16"/>
       <c r="H22" s="7"/>
       <c r="I22" s="7"/>
-      <c r="J22" s="36"/>
-      <c r="K22" s="36"/>
-      <c r="L22" s="36"/>
-      <c r="M22" s="36"/>
-      <c r="N22" s="36"/>
-      <c r="O22" s="36"/>
-    </row>
-    <row r="23" spans="1:15" ht="26.5">
-      <c r="A23" s="36"/>
-      <c r="B23" s="37"/>
-      <c r="C23" s="36"/>
-      <c r="D23" s="36"/>
-      <c r="E23" s="36"/>
-      <c r="F23" s="36"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="36"/>
-      <c r="I23" s="36"/>
-      <c r="J23" s="36"/>
-      <c r="K23" s="36"/>
-      <c r="L23" s="36"/>
-      <c r="M23" s="36"/>
-      <c r="N23" s="36"/>
-      <c r="O23" s="36"/>
-    </row>
-    <row r="24" spans="1:15">
-      <c r="A24" s="7"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
-      <c r="M24" s="7"/>
-      <c r="N24" s="7"/>
-      <c r="O24" s="7"/>
+      <c r="J22" s="7"/>
+      <c r="K22" s="7"/>
+      <c r="L22" s="7"/>
+      <c r="M22" s="7"/>
+      <c r="N22" s="7"/>
+      <c r="O22" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -4686,28 +4640,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="20">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="91" t="s">
+      <c r="B1" s="87"/>
+      <c r="C1" s="141" t="s">
         <v>18</v>
       </c>
-      <c r="D1" s="92"/>
-      <c r="E1" s="93" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="94"/>
-      <c r="J1" s="94"/>
-      <c r="K1" s="95"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="143" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="144"/>
+      <c r="J1" s="144"/>
+      <c r="K1" s="145"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -4717,17 +4671,17 @@
       </c>
     </row>
     <row r="2" spans="1:18" ht="20">
-      <c r="A2" s="89"/>
+      <c r="A2" s="88"/>
       <c r="B2" s="90"/>
-      <c r="C2" s="91"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="94"/>
-      <c r="K2" s="95"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="142"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="144"/>
+      <c r="G2" s="144"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="144"/>
+      <c r="J2" s="144"/>
+      <c r="K2" s="145"/>
       <c r="L2" s="29" t="s">
         <v>14</v>
       </c>
@@ -4757,7 +4711,7 @@
     <row r="4" spans="1:18">
       <c r="A4" s="8"/>
       <c r="B4" s="34" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -4775,27 +4729,27 @@
     </row>
     <row r="5" spans="1:18" ht="18" customHeight="1">
       <c r="A5" s="8"/>
-      <c r="B5" s="96" t="s">
-        <v>138</v>
-      </c>
-      <c r="C5" s="96"/>
-      <c r="D5" s="96"/>
-      <c r="E5" s="96"/>
-      <c r="F5" s="96"/>
-      <c r="G5" s="96"/>
-      <c r="H5" s="96"/>
-      <c r="I5" s="96"/>
-      <c r="J5" s="96"/>
-      <c r="K5" s="96"/>
-      <c r="L5" s="96"/>
-      <c r="M5" s="96"/>
-      <c r="N5" s="96"/>
+      <c r="B5" s="146" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" s="146"/>
+      <c r="D5" s="146"/>
+      <c r="E5" s="146"/>
+      <c r="F5" s="146"/>
+      <c r="G5" s="146"/>
+      <c r="H5" s="146"/>
+      <c r="I5" s="146"/>
+      <c r="J5" s="146"/>
+      <c r="K5" s="146"/>
+      <c r="L5" s="146"/>
+      <c r="M5" s="146"/>
+      <c r="N5" s="146"/>
       <c r="O5" s="8"/>
     </row>
     <row r="6" spans="1:18">
       <c r="A6" s="34"/>
       <c r="B6" s="34" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C6" s="34"/>
       <c r="D6" s="34"/>
@@ -4831,7 +4785,7 @@
     <row r="8" spans="1:18">
       <c r="A8" s="34"/>
       <c r="B8" s="34" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
@@ -4849,78 +4803,78 @@
     </row>
     <row r="9" spans="1:18" ht="18" customHeight="1">
       <c r="A9" s="34"/>
-      <c r="B9" s="85" t="s">
-        <v>140</v>
-      </c>
-      <c r="C9" s="85"/>
-      <c r="D9" s="85"/>
-      <c r="E9" s="85"/>
-      <c r="F9" s="85"/>
-      <c r="G9" s="85"/>
-      <c r="H9" s="85"/>
-      <c r="I9" s="85"/>
-      <c r="J9" s="85"/>
-      <c r="K9" s="85"/>
-      <c r="L9" s="85"/>
-      <c r="M9" s="85"/>
-      <c r="N9" s="85"/>
+      <c r="B9" s="140" t="s">
+        <v>137</v>
+      </c>
+      <c r="C9" s="140"/>
+      <c r="D9" s="140"/>
+      <c r="E9" s="140"/>
+      <c r="F9" s="140"/>
+      <c r="G9" s="140"/>
+      <c r="H9" s="140"/>
+      <c r="I9" s="140"/>
+      <c r="J9" s="140"/>
+      <c r="K9" s="140"/>
+      <c r="L9" s="140"/>
+      <c r="M9" s="140"/>
+      <c r="N9" s="140"/>
       <c r="O9" s="34"/>
     </row>
     <row r="10" spans="1:18">
       <c r="A10" s="34"/>
-      <c r="B10" s="85" t="s">
-        <v>141</v>
-      </c>
-      <c r="C10" s="85"/>
-      <c r="D10" s="85"/>
-      <c r="E10" s="85"/>
-      <c r="F10" s="85"/>
-      <c r="G10" s="85"/>
-      <c r="H10" s="85"/>
-      <c r="I10" s="85"/>
-      <c r="J10" s="85"/>
-      <c r="K10" s="85"/>
-      <c r="L10" s="85"/>
-      <c r="M10" s="85"/>
-      <c r="N10" s="85"/>
+      <c r="B10" s="140" t="s">
+        <v>138</v>
+      </c>
+      <c r="C10" s="140"/>
+      <c r="D10" s="140"/>
+      <c r="E10" s="140"/>
+      <c r="F10" s="140"/>
+      <c r="G10" s="140"/>
+      <c r="H10" s="140"/>
+      <c r="I10" s="140"/>
+      <c r="J10" s="140"/>
+      <c r="K10" s="140"/>
+      <c r="L10" s="140"/>
+      <c r="M10" s="140"/>
+      <c r="N10" s="140"/>
       <c r="O10" s="34"/>
     </row>
     <row r="11" spans="1:18" ht="18" customHeight="1">
       <c r="A11" s="34"/>
-      <c r="B11" s="85" t="s">
-        <v>142</v>
-      </c>
-      <c r="C11" s="85"/>
-      <c r="D11" s="85"/>
-      <c r="E11" s="85"/>
-      <c r="F11" s="85"/>
-      <c r="G11" s="85"/>
-      <c r="H11" s="85"/>
-      <c r="I11" s="85"/>
-      <c r="J11" s="85"/>
-      <c r="K11" s="85"/>
-      <c r="L11" s="85"/>
-      <c r="M11" s="85"/>
-      <c r="N11" s="85"/>
-      <c r="O11" s="85"/>
+      <c r="B11" s="140" t="s">
+        <v>139</v>
+      </c>
+      <c r="C11" s="140"/>
+      <c r="D11" s="140"/>
+      <c r="E11" s="140"/>
+      <c r="F11" s="140"/>
+      <c r="G11" s="140"/>
+      <c r="H11" s="140"/>
+      <c r="I11" s="140"/>
+      <c r="J11" s="140"/>
+      <c r="K11" s="140"/>
+      <c r="L11" s="140"/>
+      <c r="M11" s="140"/>
+      <c r="N11" s="140"/>
+      <c r="O11" s="140"/>
     </row>
     <row r="12" spans="1:18" ht="18" customHeight="1">
       <c r="A12" s="34"/>
-      <c r="B12" s="85" t="s">
-        <v>143</v>
-      </c>
-      <c r="C12" s="85"/>
-      <c r="D12" s="85"/>
-      <c r="E12" s="85"/>
-      <c r="F12" s="85"/>
-      <c r="G12" s="85"/>
-      <c r="H12" s="85"/>
-      <c r="I12" s="85"/>
-      <c r="J12" s="85"/>
-      <c r="K12" s="85"/>
-      <c r="L12" s="85"/>
-      <c r="M12" s="85"/>
-      <c r="N12" s="85"/>
+      <c r="B12" s="140" t="s">
+        <v>140</v>
+      </c>
+      <c r="C12" s="140"/>
+      <c r="D12" s="140"/>
+      <c r="E12" s="140"/>
+      <c r="F12" s="140"/>
+      <c r="G12" s="140"/>
+      <c r="H12" s="140"/>
+      <c r="I12" s="140"/>
+      <c r="J12" s="140"/>
+      <c r="K12" s="140"/>
+      <c r="L12" s="140"/>
+      <c r="M12" s="140"/>
+      <c r="N12" s="140"/>
       <c r="O12" s="47"/>
       <c r="P12" s="47"/>
       <c r="Q12" s="47"/>
@@ -4949,7 +4903,7 @@
     <row r="14" spans="1:18">
       <c r="A14" s="34"/>
       <c r="B14" s="34" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C14" s="34"/>
       <c r="D14" s="34"/>
@@ -4967,115 +4921,115 @@
     </row>
     <row r="15" spans="1:18" ht="18" customHeight="1">
       <c r="A15" s="34"/>
-      <c r="B15" s="86" t="s">
-        <v>28</v>
-      </c>
-      <c r="C15" s="86"/>
-      <c r="D15" s="86"/>
-      <c r="E15" s="86"/>
-      <c r="F15" s="86"/>
-      <c r="G15" s="86"/>
-      <c r="H15" s="86"/>
-      <c r="I15" s="86"/>
-      <c r="J15" s="86"/>
-      <c r="K15" s="86"/>
-      <c r="L15" s="86"/>
-      <c r="M15" s="86"/>
-      <c r="N15" s="86"/>
-      <c r="O15" s="86"/>
+      <c r="B15" s="139" t="s">
+        <v>26</v>
+      </c>
+      <c r="C15" s="139"/>
+      <c r="D15" s="139"/>
+      <c r="E15" s="139"/>
+      <c r="F15" s="139"/>
+      <c r="G15" s="139"/>
+      <c r="H15" s="139"/>
+      <c r="I15" s="139"/>
+      <c r="J15" s="139"/>
+      <c r="K15" s="139"/>
+      <c r="L15" s="139"/>
+      <c r="M15" s="139"/>
+      <c r="N15" s="139"/>
+      <c r="O15" s="139"/>
     </row>
     <row r="16" spans="1:18" ht="18" customHeight="1">
       <c r="A16" s="34"/>
-      <c r="B16" s="86" t="s">
-        <v>73</v>
-      </c>
-      <c r="C16" s="86"/>
-      <c r="D16" s="86"/>
-      <c r="E16" s="86"/>
-      <c r="F16" s="86"/>
-      <c r="G16" s="86"/>
-      <c r="H16" s="86"/>
-      <c r="I16" s="86"/>
-      <c r="J16" s="86"/>
-      <c r="K16" s="86"/>
-      <c r="L16" s="86"/>
-      <c r="M16" s="86"/>
-      <c r="N16" s="86"/>
-      <c r="O16" s="86"/>
+      <c r="B16" s="139" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="139"/>
+      <c r="D16" s="139"/>
+      <c r="E16" s="139"/>
+      <c r="F16" s="139"/>
+      <c r="G16" s="139"/>
+      <c r="H16" s="139"/>
+      <c r="I16" s="139"/>
+      <c r="J16" s="139"/>
+      <c r="K16" s="139"/>
+      <c r="L16" s="139"/>
+      <c r="M16" s="139"/>
+      <c r="N16" s="139"/>
+      <c r="O16" s="139"/>
     </row>
     <row r="17" spans="1:15" ht="18" customHeight="1">
       <c r="A17" s="34"/>
-      <c r="B17" s="86" t="s">
-        <v>146</v>
-      </c>
-      <c r="C17" s="86"/>
-      <c r="D17" s="86"/>
-      <c r="E17" s="86"/>
-      <c r="F17" s="86"/>
-      <c r="G17" s="86"/>
-      <c r="H17" s="86"/>
-      <c r="I17" s="86"/>
-      <c r="J17" s="86"/>
-      <c r="K17" s="86"/>
-      <c r="L17" s="86"/>
-      <c r="M17" s="86"/>
-      <c r="N17" s="86"/>
-      <c r="O17" s="86"/>
+      <c r="B17" s="139" t="s">
+        <v>143</v>
+      </c>
+      <c r="C17" s="139"/>
+      <c r="D17" s="139"/>
+      <c r="E17" s="139"/>
+      <c r="F17" s="139"/>
+      <c r="G17" s="139"/>
+      <c r="H17" s="139"/>
+      <c r="I17" s="139"/>
+      <c r="J17" s="139"/>
+      <c r="K17" s="139"/>
+      <c r="L17" s="139"/>
+      <c r="M17" s="139"/>
+      <c r="N17" s="139"/>
+      <c r="O17" s="139"/>
     </row>
     <row r="18" spans="1:15" ht="18" customHeight="1">
       <c r="A18" s="34"/>
-      <c r="B18" s="86" t="s">
-        <v>147</v>
-      </c>
-      <c r="C18" s="86"/>
-      <c r="D18" s="86"/>
-      <c r="E18" s="86"/>
-      <c r="F18" s="86"/>
-      <c r="G18" s="86"/>
-      <c r="H18" s="86"/>
-      <c r="I18" s="86"/>
-      <c r="J18" s="86"/>
-      <c r="K18" s="86"/>
-      <c r="L18" s="86"/>
-      <c r="M18" s="86"/>
-      <c r="N18" s="86"/>
-      <c r="O18" s="86"/>
+      <c r="B18" s="139" t="s">
+        <v>144</v>
+      </c>
+      <c r="C18" s="139"/>
+      <c r="D18" s="139"/>
+      <c r="E18" s="139"/>
+      <c r="F18" s="139"/>
+      <c r="G18" s="139"/>
+      <c r="H18" s="139"/>
+      <c r="I18" s="139"/>
+      <c r="J18" s="139"/>
+      <c r="K18" s="139"/>
+      <c r="L18" s="139"/>
+      <c r="M18" s="139"/>
+      <c r="N18" s="139"/>
+      <c r="O18" s="139"/>
     </row>
     <row r="19" spans="1:15" ht="18" customHeight="1">
       <c r="A19" s="34"/>
-      <c r="B19" s="86" t="s">
-        <v>148</v>
-      </c>
-      <c r="C19" s="86"/>
-      <c r="D19" s="86"/>
-      <c r="E19" s="86"/>
-      <c r="F19" s="86"/>
-      <c r="G19" s="86"/>
-      <c r="H19" s="86"/>
-      <c r="I19" s="86"/>
-      <c r="J19" s="86"/>
-      <c r="K19" s="86"/>
-      <c r="L19" s="86"/>
-      <c r="M19" s="86"/>
-      <c r="N19" s="86"/>
-      <c r="O19" s="86"/>
+      <c r="B19" s="139" t="s">
+        <v>145</v>
+      </c>
+      <c r="C19" s="139"/>
+      <c r="D19" s="139"/>
+      <c r="E19" s="139"/>
+      <c r="F19" s="139"/>
+      <c r="G19" s="139"/>
+      <c r="H19" s="139"/>
+      <c r="I19" s="139"/>
+      <c r="J19" s="139"/>
+      <c r="K19" s="139"/>
+      <c r="L19" s="139"/>
+      <c r="M19" s="139"/>
+      <c r="N19" s="139"/>
+      <c r="O19" s="139"/>
     </row>
     <row r="20" spans="1:15">
       <c r="A20" s="34"/>
-      <c r="B20" s="86"/>
-      <c r="C20" s="86"/>
-      <c r="D20" s="86"/>
-      <c r="E20" s="86"/>
-      <c r="F20" s="86"/>
-      <c r="G20" s="86"/>
-      <c r="H20" s="86"/>
-      <c r="I20" s="86"/>
-      <c r="J20" s="86"/>
-      <c r="K20" s="86"/>
-      <c r="L20" s="86"/>
-      <c r="M20" s="86"/>
-      <c r="N20" s="86"/>
-      <c r="O20" s="86"/>
+      <c r="B20" s="139"/>
+      <c r="C20" s="139"/>
+      <c r="D20" s="139"/>
+      <c r="E20" s="139"/>
+      <c r="F20" s="139"/>
+      <c r="G20" s="139"/>
+      <c r="H20" s="139"/>
+      <c r="I20" s="139"/>
+      <c r="J20" s="139"/>
+      <c r="K20" s="139"/>
+      <c r="L20" s="139"/>
+      <c r="M20" s="139"/>
+      <c r="N20" s="139"/>
+      <c r="O20" s="139"/>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" s="34"/>
@@ -5097,7 +5051,7 @@
     <row r="22" spans="1:15">
       <c r="A22" s="34"/>
       <c r="B22" s="41" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C22" s="42"/>
       <c r="D22" s="42"/>
@@ -5116,7 +5070,7 @@
     <row r="23" spans="1:15">
       <c r="A23" s="34"/>
       <c r="B23" s="41" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C23" s="42"/>
       <c r="D23" s="42"/>
@@ -5169,7 +5123,7 @@
     <row r="26" spans="1:15">
       <c r="A26" s="8"/>
       <c r="B26" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
@@ -5188,7 +5142,7 @@
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="44" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C27" s="45"/>
       <c r="D27" s="45"/>
@@ -5207,7 +5161,7 @@
     <row r="28" spans="1:15">
       <c r="A28" s="8"/>
       <c r="B28" s="44" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="C28" s="45"/>
       <c r="D28" s="45"/>
@@ -5226,7 +5180,7 @@
     <row r="29" spans="1:15">
       <c r="A29" s="8"/>
       <c r="B29" s="44" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="C29" s="45"/>
       <c r="D29" s="45"/>
@@ -5261,7 +5215,7 @@
     <row r="31" spans="1:15">
       <c r="A31" s="8"/>
       <c r="B31" s="8" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -5280,7 +5234,7 @@
     <row r="32" spans="1:15">
       <c r="A32" s="8"/>
       <c r="B32" s="46" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -5299,7 +5253,7 @@
     <row r="33" spans="1:15">
       <c r="A33" s="8"/>
       <c r="B33" s="46" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
@@ -5318,7 +5272,7 @@
     <row r="34" spans="1:15">
       <c r="A34" s="8"/>
       <c r="B34" s="46" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C34" s="8"/>
       <c r="D34" s="8"/>
@@ -5337,7 +5291,7 @@
     <row r="35" spans="1:15">
       <c r="A35" s="8"/>
       <c r="B35" s="46" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C35" s="8"/>
       <c r="D35" s="8"/>
@@ -5386,28 +5340,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="91" t="s">
-        <v>22</v>
-      </c>
-      <c r="D1" s="92"/>
-      <c r="E1" s="93" t="s">
-        <v>32</v>
-      </c>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="94"/>
-      <c r="J1" s="94"/>
-      <c r="K1" s="95"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="141" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="142"/>
+      <c r="E1" s="143" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="144"/>
+      <c r="J1" s="144"/>
+      <c r="K1" s="145"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -5417,17 +5371,17 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="89"/>
+      <c r="A2" s="88"/>
       <c r="B2" s="90"/>
-      <c r="C2" s="91"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="94"/>
-      <c r="K2" s="95"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="142"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="144"/>
+      <c r="G2" s="144"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="144"/>
+      <c r="J2" s="144"/>
+      <c r="K2" s="145"/>
       <c r="L2" s="29" t="s">
         <v>14</v>
       </c>
@@ -5457,7 +5411,7 @@
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="34" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -5492,12 +5446,12 @@
     </row>
     <row r="6" spans="1:15" ht="18" customHeight="1">
       <c r="A6" s="34"/>
-      <c r="B6" s="143" t="s">
-        <v>34</v>
-      </c>
-      <c r="C6" s="144"/>
+      <c r="B6" s="149" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" s="150"/>
       <c r="D6" s="74" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E6" s="49"/>
       <c r="F6" s="49"/>
@@ -5513,12 +5467,12 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" s="34"/>
-      <c r="B7" s="141" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="142"/>
+      <c r="B7" s="147" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="148"/>
       <c r="D7" s="17" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="E7" s="53"/>
       <c r="F7" s="53"/>
@@ -5534,12 +5488,12 @@
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="34"/>
-      <c r="B8" s="141" t="s">
-        <v>35</v>
-      </c>
-      <c r="C8" s="142"/>
+      <c r="B8" s="147" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="148"/>
       <c r="D8" s="17" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E8" s="23"/>
       <c r="F8" s="23"/>
@@ -6003,16 +5957,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="91" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" s="92"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="141" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="142"/>
       <c r="E1" s="70" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F1" s="70"/>
       <c r="G1" s="70"/>
@@ -6023,27 +5977,27 @@
         <v>2</v>
       </c>
       <c r="L1" s="26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="M1" s="25" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="148">
+      <c r="N1" s="154">
         <v>46289</v>
       </c>
-      <c r="O1" s="148"/>
+      <c r="O1" s="154"/>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="89"/>
+      <c r="A2" s="88"/>
       <c r="B2" s="90"/>
-      <c r="C2" s="91"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="95"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="142"/>
+      <c r="E2" s="144"/>
+      <c r="F2" s="144"/>
+      <c r="G2" s="144"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="144"/>
+      <c r="J2" s="145"/>
       <c r="K2" s="29" t="s">
         <v>14</v>
       </c>
@@ -6051,8 +6005,8 @@
       <c r="M2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="149"/>
-      <c r="O2" s="149"/>
+      <c r="N2" s="155"/>
+      <c r="O2" s="155"/>
     </row>
     <row r="3" spans="1:15">
       <c r="A3" s="39"/>
@@ -6074,7 +6028,7 @@
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="34" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -6110,12 +6064,12 @@
     <row r="6" spans="1:15" ht="18" customHeight="1">
       <c r="A6" s="34"/>
       <c r="B6" s="48" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C6" s="49"/>
       <c r="D6" s="49"/>
       <c r="E6" s="48" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="F6" s="49"/>
       <c r="G6" s="49"/>
@@ -6123,7 +6077,7 @@
       <c r="I6" s="50"/>
       <c r="J6" s="65"/>
       <c r="K6" s="48" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="L6" s="54"/>
       <c r="M6" s="69"/>
@@ -6133,12 +6087,12 @@
     <row r="7" spans="1:15">
       <c r="A7" s="34"/>
       <c r="B7" s="52" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C7" s="53"/>
       <c r="D7" s="53"/>
       <c r="E7" s="67" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F7" s="23"/>
       <c r="G7" s="53"/>
@@ -6146,7 +6100,7 @@
       <c r="I7" s="53"/>
       <c r="J7" s="54"/>
       <c r="K7" s="68" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L7" s="54"/>
       <c r="M7" s="30"/>
@@ -6156,12 +6110,12 @@
     <row r="8" spans="1:15">
       <c r="A8" s="34"/>
       <c r="B8" s="52" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="C8" s="53"/>
       <c r="D8" s="53"/>
       <c r="E8" s="67" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="F8" s="23"/>
       <c r="G8" s="53"/>
@@ -6169,7 +6123,7 @@
       <c r="I8" s="53"/>
       <c r="J8" s="54"/>
       <c r="K8" s="68" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L8" s="54"/>
       <c r="M8" s="30"/>
@@ -6179,12 +6133,12 @@
     <row r="9" spans="1:15">
       <c r="A9" s="34"/>
       <c r="B9" s="52" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C9" s="53"/>
       <c r="D9" s="53"/>
       <c r="E9" s="67" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F9" s="23"/>
       <c r="G9" s="53"/>
@@ -6192,7 +6146,7 @@
       <c r="I9" s="53"/>
       <c r="J9" s="54"/>
       <c r="K9" s="68" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L9" s="54"/>
       <c r="M9" s="30"/>
@@ -6202,20 +6156,20 @@
     <row r="10" spans="1:15">
       <c r="A10" s="34"/>
       <c r="B10" s="52" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C10" s="23"/>
       <c r="D10" s="23"/>
-      <c r="E10" s="145" t="s">
-        <v>161</v>
-      </c>
-      <c r="F10" s="146"/>
-      <c r="G10" s="146"/>
-      <c r="H10" s="146"/>
-      <c r="I10" s="146"/>
-      <c r="J10" s="147"/>
+      <c r="E10" s="151" t="s">
+        <v>158</v>
+      </c>
+      <c r="F10" s="152"/>
+      <c r="G10" s="152"/>
+      <c r="H10" s="152"/>
+      <c r="I10" s="152"/>
+      <c r="J10" s="153"/>
       <c r="K10" s="68" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="L10" s="54"/>
       <c r="M10" s="30"/>
@@ -6242,7 +6196,7 @@
     <row r="12" spans="1:15">
       <c r="A12" s="34"/>
       <c r="B12" s="34" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C12" s="34"/>
       <c r="D12" s="34"/>
@@ -6250,7 +6204,7 @@
     <row r="13" spans="1:15">
       <c r="A13" s="34"/>
       <c r="B13" s="41" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C13" s="41"/>
       <c r="D13" s="41"/>
@@ -6269,7 +6223,7 @@
     <row r="14" spans="1:15">
       <c r="A14" s="34"/>
       <c r="B14" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C14" s="56"/>
       <c r="D14" s="56"/>
@@ -6277,7 +6231,7 @@
       <c r="F14" s="56"/>
       <c r="G14" s="56"/>
       <c r="H14" s="56" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I14" s="56"/>
       <c r="J14" s="41"/>
@@ -6290,7 +6244,7 @@
     <row r="15" spans="1:15">
       <c r="A15" s="34"/>
       <c r="B15" s="7" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C15" s="56"/>
       <c r="D15" s="56"/>
@@ -6326,7 +6280,7 @@
     <row r="17" spans="1:15">
       <c r="A17" s="34"/>
       <c r="B17" s="7" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="C17" s="56"/>
       <c r="D17" s="56"/>
@@ -6345,7 +6299,7 @@
     <row r="18" spans="1:15">
       <c r="A18" s="34"/>
       <c r="B18" s="56" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C18" s="41"/>
       <c r="D18" s="41"/>
@@ -6364,7 +6318,7 @@
     <row r="19" spans="1:15">
       <c r="A19" s="34"/>
       <c r="B19" s="7" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="C19" s="41"/>
       <c r="D19" s="41"/>
@@ -6400,7 +6354,7 @@
     <row r="21" spans="1:15">
       <c r="A21" s="34"/>
       <c r="B21" s="7" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C21" s="41"/>
       <c r="D21" s="41"/>
@@ -6419,7 +6373,7 @@
     <row r="22" spans="1:15" ht="18" customHeight="1">
       <c r="A22" s="43"/>
       <c r="B22" s="7" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C22" s="43"/>
       <c r="D22" s="43"/>
@@ -6438,7 +6392,7 @@
     <row r="23" spans="1:15" ht="18" customHeight="1">
       <c r="A23" s="8"/>
       <c r="B23" s="56" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
@@ -6473,7 +6427,7 @@
     <row r="25" spans="1:15">
       <c r="A25" s="8"/>
       <c r="B25" s="41" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C25" s="45"/>
       <c r="D25" s="45"/>
@@ -6492,7 +6446,7 @@
     <row r="26" spans="1:15">
       <c r="A26" s="8"/>
       <c r="B26" s="56" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C26" s="45"/>
       <c r="D26" s="45"/>
@@ -6511,7 +6465,7 @@
     <row r="27" spans="1:15">
       <c r="A27" s="8"/>
       <c r="B27" s="56" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C27" s="45"/>
       <c r="D27" s="45"/>
@@ -6636,28 +6590,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="91" t="s">
+      <c r="B1" s="87"/>
+      <c r="C1" s="141" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="92"/>
-      <c r="E1" s="93" t="s">
-        <v>36</v>
-      </c>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="94"/>
-      <c r="J1" s="94"/>
-      <c r="K1" s="95"/>
+      <c r="D1" s="142"/>
+      <c r="E1" s="143" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="144"/>
+      <c r="J1" s="144"/>
+      <c r="K1" s="145"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -6667,17 +6621,17 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="89"/>
+      <c r="A2" s="88"/>
       <c r="B2" s="90"/>
-      <c r="C2" s="91"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="94"/>
-      <c r="K2" s="95"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="142"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="144"/>
+      <c r="G2" s="144"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="144"/>
+      <c r="J2" s="144"/>
+      <c r="K2" s="145"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
@@ -6707,7 +6661,7 @@
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="34" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -6726,7 +6680,7 @@
     <row r="5" spans="1:15">
       <c r="A5" s="8"/>
       <c r="B5" s="30" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C5" s="30"/>
       <c r="D5" s="30"/>
@@ -6762,7 +6716,7 @@
     <row r="7" spans="1:15">
       <c r="A7" s="34"/>
       <c r="B7" s="34" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C7" s="34"/>
       <c r="D7" s="34"/>
@@ -6781,7 +6735,7 @@
     <row r="8" spans="1:15">
       <c r="A8" s="34"/>
       <c r="B8" s="34" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C8" s="34"/>
       <c r="D8" s="34"/>
@@ -6800,7 +6754,7 @@
     <row r="9" spans="1:15">
       <c r="A9" s="34"/>
       <c r="B9" s="34" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C9" s="34"/>
       <c r="D9" s="34"/>
@@ -6836,7 +6790,7 @@
     <row r="11" spans="1:15">
       <c r="A11" s="34"/>
       <c r="B11" s="30" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
@@ -6855,7 +6809,7 @@
     <row r="12" spans="1:15">
       <c r="A12" s="34"/>
       <c r="B12" s="41" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C12" s="41"/>
       <c r="D12" s="41"/>
@@ -7199,28 +7153,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="20">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="91" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" s="92"/>
-      <c r="E1" s="93" t="s">
-        <v>39</v>
-      </c>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="94"/>
-      <c r="J1" s="94"/>
-      <c r="K1" s="95"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="141" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="142"/>
+      <c r="E1" s="143" t="s">
+        <v>37</v>
+      </c>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="144"/>
+      <c r="J1" s="144"/>
+      <c r="K1" s="145"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -7230,17 +7184,17 @@
       </c>
     </row>
     <row r="2" spans="1:15" ht="20">
-      <c r="A2" s="89"/>
+      <c r="A2" s="88"/>
       <c r="B2" s="90"/>
-      <c r="C2" s="91"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="94"/>
-      <c r="K2" s="95"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="142"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="144"/>
+      <c r="G2" s="144"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="144"/>
+      <c r="J2" s="144"/>
+      <c r="K2" s="145"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
@@ -7270,7 +7224,7 @@
     <row r="4" spans="1:15">
       <c r="A4" s="8"/>
       <c r="B4" s="34" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -7289,23 +7243,23 @@
     <row r="5" spans="1:15">
       <c r="A5" s="8"/>
       <c r="B5" s="59" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C5" s="60"/>
       <c r="D5" s="59" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E5" s="60"/>
       <c r="F5" s="59" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G5" s="60"/>
       <c r="H5" s="59" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I5" s="60"/>
       <c r="J5" s="59" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K5" s="53"/>
       <c r="L5" s="61"/>
@@ -7316,11 +7270,11 @@
     <row r="6" spans="1:15">
       <c r="A6" s="8"/>
       <c r="B6" s="52" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C6" s="60"/>
       <c r="D6" s="52" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E6" s="55"/>
       <c r="F6" s="52">
@@ -7328,11 +7282,11 @@
       </c>
       <c r="G6" s="55"/>
       <c r="H6" s="52" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="I6" s="55"/>
       <c r="J6" s="52" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="K6" s="53"/>
       <c r="L6" s="61"/>
@@ -7343,11 +7297,11 @@
     <row r="7" spans="1:15">
       <c r="A7" s="34"/>
       <c r="B7" s="52" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C7" s="55"/>
       <c r="D7" s="52" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E7" s="55"/>
       <c r="F7" s="52">
@@ -7355,11 +7309,11 @@
       </c>
       <c r="G7" s="55"/>
       <c r="H7" s="52" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I7" s="55"/>
       <c r="J7" s="52" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K7" s="53"/>
       <c r="L7" s="61"/>
@@ -7370,11 +7324,11 @@
     <row r="8" spans="1:15">
       <c r="A8" s="34"/>
       <c r="B8" s="52" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C8" s="55"/>
       <c r="D8" s="52" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E8" s="55"/>
       <c r="F8" s="52">
@@ -7382,11 +7336,11 @@
       </c>
       <c r="G8" s="55"/>
       <c r="H8" s="52" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I8" s="55"/>
       <c r="J8" s="52" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K8" s="23"/>
       <c r="L8" s="53"/>
@@ -7397,11 +7351,11 @@
     <row r="9" spans="1:15" ht="36" customHeight="1">
       <c r="A9" s="34"/>
       <c r="B9" s="52" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C9" s="55"/>
       <c r="D9" s="52" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E9" s="55"/>
       <c r="F9" s="52">
@@ -7409,26 +7363,26 @@
       </c>
       <c r="G9" s="55"/>
       <c r="H9" s="52" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I9" s="55"/>
-      <c r="J9" s="153" t="s">
-        <v>97</v>
-      </c>
-      <c r="K9" s="154"/>
-      <c r="L9" s="154"/>
-      <c r="M9" s="155"/>
+      <c r="J9" s="156" t="s">
+        <v>95</v>
+      </c>
+      <c r="K9" s="157"/>
+      <c r="L9" s="157"/>
+      <c r="M9" s="158"/>
       <c r="N9" s="34"/>
       <c r="O9" s="34"/>
     </row>
     <row r="10" spans="1:15">
       <c r="A10" s="34"/>
       <c r="B10" s="52" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C10" s="55"/>
       <c r="D10" s="52" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E10" s="55"/>
       <c r="F10" s="52">
@@ -7436,11 +7390,11 @@
       </c>
       <c r="G10" s="55"/>
       <c r="H10" s="52" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="I10" s="23"/>
       <c r="J10" s="75" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="K10" s="23"/>
       <c r="L10" s="53"/>
@@ -7451,11 +7405,11 @@
     <row r="11" spans="1:15" ht="54" customHeight="1">
       <c r="A11" s="34"/>
       <c r="B11" s="67" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C11" s="55"/>
       <c r="D11" s="52" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E11" s="55"/>
       <c r="F11" s="17">
@@ -7463,38 +7417,38 @@
       </c>
       <c r="G11" s="55"/>
       <c r="H11" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I11" s="23"/>
-      <c r="J11" s="150" t="s">
-        <v>98</v>
-      </c>
-      <c r="K11" s="151"/>
-      <c r="L11" s="151"/>
-      <c r="M11" s="152"/>
+      <c r="J11" s="159" t="s">
+        <v>96</v>
+      </c>
+      <c r="K11" s="160"/>
+      <c r="L11" s="160"/>
+      <c r="M11" s="161"/>
       <c r="N11" s="8"/>
       <c r="O11" s="34"/>
     </row>
     <row r="12" spans="1:15">
       <c r="A12" s="34"/>
       <c r="B12" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C12" s="55"/>
       <c r="D12" s="52" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E12" s="55"/>
       <c r="F12" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G12" s="55"/>
       <c r="H12" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I12" s="55"/>
       <c r="J12" s="17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K12" s="23"/>
       <c r="L12" s="23"/>
@@ -7505,23 +7459,23 @@
     <row r="13" spans="1:15">
       <c r="A13" s="34"/>
       <c r="B13" s="17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C13" s="54"/>
       <c r="D13" s="52" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E13" s="55"/>
       <c r="F13" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G13" s="55"/>
       <c r="H13" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I13" s="55"/>
       <c r="J13" s="17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K13" s="23"/>
       <c r="L13" s="23"/>
@@ -7532,11 +7486,11 @@
     <row r="14" spans="1:15" ht="36" customHeight="1">
       <c r="A14" s="34"/>
       <c r="B14" s="52" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C14" s="73"/>
       <c r="D14" s="52" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E14" s="55"/>
       <c r="F14" s="17">
@@ -7544,15 +7498,15 @@
       </c>
       <c r="G14" s="55"/>
       <c r="H14" s="17" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I14" s="55"/>
-      <c r="J14" s="145" t="s">
-        <v>92</v>
-      </c>
-      <c r="K14" s="146"/>
-      <c r="L14" s="146"/>
-      <c r="M14" s="147"/>
+      <c r="J14" s="151" t="s">
+        <v>90</v>
+      </c>
+      <c r="K14" s="152"/>
+      <c r="L14" s="152"/>
+      <c r="M14" s="153"/>
       <c r="N14" s="41"/>
       <c r="O14" s="41"/>
     </row>
@@ -7593,7 +7547,7 @@
     <row r="17" spans="1:15">
       <c r="A17" s="34"/>
       <c r="B17" s="41" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="C17" s="41"/>
       <c r="D17" s="41"/>
@@ -7612,23 +7566,23 @@
     <row r="18" spans="1:15">
       <c r="A18" s="34"/>
       <c r="B18" s="59" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C18" s="60"/>
       <c r="D18" s="59" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E18" s="60"/>
       <c r="F18" s="59" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G18" s="60"/>
       <c r="H18" s="59" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I18" s="60"/>
       <c r="J18" s="59" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="K18" s="53"/>
       <c r="L18" s="61"/>
@@ -7639,11 +7593,11 @@
     <row r="19" spans="1:15">
       <c r="A19" s="34"/>
       <c r="B19" s="52" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C19" s="55"/>
       <c r="D19" s="52" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E19" s="55"/>
       <c r="F19" s="52">
@@ -7651,11 +7605,11 @@
       </c>
       <c r="G19" s="55"/>
       <c r="H19" s="52" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I19" s="55"/>
       <c r="J19" s="52" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K19" s="53"/>
       <c r="L19" s="61"/>
@@ -7666,23 +7620,23 @@
     <row r="20" spans="1:15">
       <c r="A20" s="34"/>
       <c r="B20" s="52" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C20" s="55"/>
       <c r="D20" s="52" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E20" s="55"/>
       <c r="F20" s="52" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G20" s="55"/>
       <c r="H20" s="52" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I20" s="55"/>
       <c r="J20" s="52" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="K20" s="23"/>
       <c r="L20" s="53"/>
@@ -7693,11 +7647,11 @@
     <row r="21" spans="1:15" ht="36" customHeight="1">
       <c r="A21" s="34"/>
       <c r="B21" s="52" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C21" s="55"/>
       <c r="D21" s="52" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E21" s="55"/>
       <c r="F21" s="52">
@@ -7705,7 +7659,7 @@
       </c>
       <c r="G21" s="55"/>
       <c r="H21" s="52" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="I21" s="55"/>
       <c r="J21" s="52"/>
@@ -7718,11 +7672,11 @@
     <row r="22" spans="1:15" ht="18" customHeight="1">
       <c r="A22" s="43"/>
       <c r="B22" s="52" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="C22" s="55"/>
       <c r="D22" s="52" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E22" s="55"/>
       <c r="F22" s="52">
@@ -7730,11 +7684,11 @@
       </c>
       <c r="G22" s="55"/>
       <c r="H22" s="52" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I22" s="23"/>
       <c r="J22" s="17" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="K22" s="23"/>
       <c r="L22" s="53"/>
@@ -7745,23 +7699,23 @@
     <row r="23" spans="1:15">
       <c r="A23" s="8"/>
       <c r="B23" s="52" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C23" s="55"/>
       <c r="D23" s="52" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E23" s="55"/>
       <c r="F23" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G23" s="55"/>
       <c r="H23" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I23" s="55"/>
       <c r="J23" s="17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K23" s="23"/>
       <c r="L23" s="23"/>
@@ -7772,23 +7726,23 @@
     <row r="24" spans="1:15" ht="18" customHeight="1">
       <c r="A24" s="8"/>
       <c r="B24" s="52" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C24" s="54"/>
       <c r="D24" s="52" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E24" s="55"/>
       <c r="F24" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="G24" s="55"/>
       <c r="H24" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I24" s="55"/>
       <c r="J24" s="17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="K24" s="23"/>
       <c r="L24" s="23"/>
@@ -7799,11 +7753,11 @@
     <row r="25" spans="1:15" ht="36" customHeight="1">
       <c r="A25" s="8"/>
       <c r="B25" s="52" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C25" s="73"/>
       <c r="D25" s="52" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E25" s="55"/>
       <c r="F25" s="17">
@@ -7811,15 +7765,15 @@
       </c>
       <c r="G25" s="55"/>
       <c r="H25" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I25" s="55"/>
-      <c r="J25" s="145" t="s">
-        <v>92</v>
-      </c>
-      <c r="K25" s="146"/>
-      <c r="L25" s="146"/>
-      <c r="M25" s="147"/>
+      <c r="J25" s="151" t="s">
+        <v>90</v>
+      </c>
+      <c r="K25" s="152"/>
+      <c r="L25" s="152"/>
+      <c r="M25" s="153"/>
       <c r="N25" s="56"/>
       <c r="O25" s="56"/>
     </row>
@@ -7983,28 +7937,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="20">
-      <c r="A1" s="87" t="s">
+      <c r="A1" s="85" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="88"/>
-      <c r="C1" s="91" t="s">
-        <v>57</v>
-      </c>
-      <c r="D1" s="92"/>
-      <c r="E1" s="93" t="s">
-        <v>47</v>
-      </c>
-      <c r="F1" s="94"/>
-      <c r="G1" s="94"/>
-      <c r="H1" s="94"/>
-      <c r="I1" s="94"/>
-      <c r="J1" s="94"/>
-      <c r="K1" s="95"/>
+      <c r="B1" s="87"/>
+      <c r="C1" s="141" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="142"/>
+      <c r="E1" s="143" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" s="144"/>
+      <c r="G1" s="144"/>
+      <c r="H1" s="144"/>
+      <c r="I1" s="144"/>
+      <c r="J1" s="144"/>
+      <c r="K1" s="145"/>
       <c r="L1" s="25" t="s">
         <v>2</v>
       </c>
       <c r="M1" s="26" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N1" s="25" t="s">
         <v>3</v>
@@ -8014,17 +7968,17 @@
       </c>
     </row>
     <row r="2" spans="1:16" ht="20">
-      <c r="A2" s="89"/>
+      <c r="A2" s="88"/>
       <c r="B2" s="90"/>
-      <c r="C2" s="91"/>
-      <c r="D2" s="92"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="94"/>
-      <c r="H2" s="94"/>
-      <c r="I2" s="94"/>
-      <c r="J2" s="94"/>
-      <c r="K2" s="95"/>
+      <c r="C2" s="141"/>
+      <c r="D2" s="142"/>
+      <c r="E2" s="143"/>
+      <c r="F2" s="144"/>
+      <c r="G2" s="144"/>
+      <c r="H2" s="144"/>
+      <c r="I2" s="144"/>
+      <c r="J2" s="144"/>
+      <c r="K2" s="145"/>
       <c r="L2" s="25" t="s">
         <v>14</v>
       </c>
@@ -8074,21 +8028,21 @@
         <v>4</v>
       </c>
       <c r="C5" s="59" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D5" s="50"/>
       <c r="E5" s="64"/>
       <c r="F5" s="50"/>
       <c r="G5" s="60"/>
       <c r="H5" s="59" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="I5" s="64"/>
       <c r="J5" s="50"/>
       <c r="K5" s="50"/>
       <c r="L5" s="65"/>
       <c r="M5" s="59" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="N5" s="61"/>
       <c r="O5" s="55"/>
@@ -8099,24 +8053,24 @@
         <v>1</v>
       </c>
       <c r="C6" s="75" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="D6" s="77"/>
       <c r="E6" s="78"/>
       <c r="F6" s="77"/>
       <c r="G6" s="76"/>
       <c r="H6" s="75" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="I6" s="78"/>
       <c r="J6" s="77"/>
       <c r="K6" s="77"/>
       <c r="L6" s="79"/>
-      <c r="M6" s="150" t="s">
-        <v>182</v>
-      </c>
-      <c r="N6" s="151"/>
-      <c r="O6" s="152"/>
+      <c r="M6" s="159" t="s">
+        <v>179</v>
+      </c>
+      <c r="N6" s="160"/>
+      <c r="O6" s="161"/>
       <c r="P6" s="80"/>
     </row>
     <row r="7" spans="1:16">
@@ -8132,9 +8086,9 @@
       <c r="J7" s="77"/>
       <c r="K7" s="77"/>
       <c r="L7" s="79"/>
-      <c r="M7" s="156"/>
-      <c r="N7" s="157"/>
-      <c r="O7" s="158"/>
+      <c r="M7" s="162"/>
+      <c r="N7" s="163"/>
+      <c r="O7" s="164"/>
       <c r="P7" s="80"/>
     </row>
     <row r="8" spans="1:16">
